--- a/FRETE.xlsx
+++ b/FRETE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\logis\OneDrive\Área de Trabalho\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\logis\OneDrive\Área de Trabalho\FRETE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{330AD680-C9DF-4221-BEA9-5E4830632632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{247001B6-CD4E-4A4F-B5E1-86A48889EC5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="FRETE ABRIL" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FRETE ABRIL'!$A$1:$Z$163</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FRETE ABRIL'!$A$1:$AA$163</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="220">
   <si>
     <t>Empresa</t>
   </si>
@@ -693,13 +693,17 @@
   </si>
   <si>
     <t>Índice Logístico</t>
+  </si>
+  <si>
+    <t>C. Transferencia</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
+    <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
@@ -761,7 +765,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -780,6 +784,11 @@
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="5" applyFont="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Moeda" xfId="2" builtinId="4"/>
@@ -1099,7 +1108,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10D4F1C6-370D-4261-953A-B02E0B54CF5A}">
-  <dimension ref="A1:Z171"/>
+  <dimension ref="A1:AB171"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -1122,13 +1131,15 @@
     <col min="19" max="19" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="18.28515625" customWidth="1"/>
     <col min="23" max="23" width="18.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.5703125" style="12" customWidth="1"/>
+    <col min="25" max="25" width="19.85546875" customWidth="1"/>
+    <col min="26" max="26" width="12.28515625" customWidth="1"/>
+    <col min="27" max="27" width="19.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1198,17 +1209,20 @@
       <c r="W1" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2</v>
       </c>
@@ -1278,20 +1292,28 @@
         <f>H2*0.17</f>
         <v>10.701500000000001</v>
       </c>
-      <c r="X2" s="8">
-        <f>S2+V2+W2</f>
-        <v>24.103937675374787</v>
-      </c>
-      <c r="Y2" s="9">
-        <f t="shared" ref="Y2:Y33" si="1">X2/J2</f>
-        <v>8.914178134384167E-3</v>
-      </c>
-      <c r="Z2" s="8">
-        <f t="shared" ref="Z2:Z33" si="2">J2-X2</f>
-        <v>2679.8960623246253</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="X2" s="12">
+        <f>IFERROR(IF(D2="TRANSFERENCIA",0,H2*(SUMIF(D:D,"TRANSFERENCIA",M:M)+SUMIF(D:D,"TRANSFERENCIA",O:O))/(SUMIF(D:D,"BONIFICAÇÃO",H:H)+SUMIF(D:D,"VENDA",H:H))),0)</f>
+        <v>7.8788635432294152</v>
+      </c>
+      <c r="Y2" s="8">
+        <f>S2+V2+W2+X2</f>
+        <v>31.982801218604202</v>
+      </c>
+      <c r="Z2" s="9">
+        <f t="shared" ref="Z2:Z33" si="1">Y2/J2</f>
+        <v>1.1827959030548891E-2</v>
+      </c>
+      <c r="AA2" s="8">
+        <f>J2-Y2</f>
+        <v>2672.017198781396</v>
+      </c>
+      <c r="AB2">
+        <f>IF(E2="TRANSFERENCIA",0,IFERROR(I2/(SUMIF(E:E,"BONIFICAÇÃO",I:I)+SUMIF(E:E,"VENDA",I:I))*(SUMIF(E:E,"TRANSFERENCIA",N:N)+SUMIF(E:E,"TRANSFERENCIA",P:P)),0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1342,11 +1364,11 @@
         <v>17</v>
       </c>
       <c r="S3" s="8">
-        <f t="shared" ref="S3:S33" si="3">SUM(M3+O3+P3)</f>
+        <f t="shared" ref="S3:S33" si="2">SUM(M3+O3+P3)</f>
         <v>7.3765002416446741</v>
       </c>
       <c r="T3" s="8">
-        <f t="shared" ref="T3:T33" si="4">SUM(M3+O3+P3)/H3</f>
+        <f t="shared" ref="T3:T33" si="3">SUM(M3+O3+P3)/H3</f>
         <v>7.6838544183798693E-2</v>
       </c>
       <c r="U3" s="8">
@@ -1361,20 +1383,24 @@
         <f>H3*0.17</f>
         <v>16.32</v>
       </c>
-      <c r="X3" s="8">
-        <f t="shared" ref="X3:X66" si="5">S3+V3+W3</f>
-        <v>36.758983587545345</v>
-      </c>
-      <c r="Y3" s="9">
+      <c r="X3" s="12">
+        <f t="shared" ref="X3:X66" si="4">IFERROR(IF(D3="TRANSFERENCIA",0,H3*(SUMIF(D:D,"TRANSFERENCIA",M:M)+SUMIF(D:D,"TRANSFERENCIA",O:O))/(SUMIF(D:D,"BONIFICAÇÃO",H:H)+SUMIF(D:D,"VENDA",H:H))),0)</f>
+        <v>12.015423354249783</v>
+      </c>
+      <c r="Y3" s="8">
+        <f>S3+V3+W3+X3</f>
+        <v>48.774406941795128</v>
+      </c>
+      <c r="Z3" s="9">
         <f t="shared" si="1"/>
-        <v>5.0122697084111024E-2</v>
-      </c>
-      <c r="Z3" s="8">
-        <f t="shared" si="2"/>
-        <v>696.62101641245465</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+        <v>6.6506322700094253E-2</v>
+      </c>
+      <c r="AA3" s="8">
+        <f>J3-Y3</f>
+        <v>684.60559305820482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1424,11 +1450,11 @@
         <v>206</v>
       </c>
       <c r="S4" s="8">
+        <f t="shared" si="2"/>
+        <v>237.03629184376626</v>
+      </c>
+      <c r="T4" s="8">
         <f t="shared" si="3"/>
-        <v>237.03629184376626</v>
-      </c>
-      <c r="T4" s="8">
-        <f t="shared" si="4"/>
         <v>0.27665300168506801</v>
       </c>
       <c r="U4" s="8">
@@ -1436,20 +1462,23 @@
         <v>0.29394381429038474</v>
       </c>
       <c r="V4" s="8"/>
-      <c r="X4" s="8">
-        <f t="shared" si="5"/>
-        <v>237.03629184376626</v>
-      </c>
-      <c r="Y4" s="9">
+      <c r="X4" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y4" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="9">
         <f t="shared" si="1"/>
-        <v>3.6193609499255819E-2</v>
-      </c>
-      <c r="Z4" s="8">
-        <f t="shared" si="2"/>
-        <v>6312.083708156234</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="8">
+        <f>J4-Y4</f>
+        <v>6549.12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -1492,7 +1521,7 @@
         <v>127.34</v>
       </c>
       <c r="P5" s="7">
-        <f t="shared" ref="P5:P10" si="6">0.0768385441837987*H5</f>
+        <f t="shared" ref="P5:P10" si="5">0.0768385441837987*H5</f>
         <v>7.526335402803082</v>
       </c>
       <c r="Q5" t="s">
@@ -1502,11 +1531,11 @@
         <v>129</v>
       </c>
       <c r="S5" s="8">
+        <f t="shared" si="2"/>
+        <v>134.86633540280309</v>
+      </c>
+      <c r="T5" s="8">
         <f t="shared" si="3"/>
-        <v>134.86633540280309</v>
-      </c>
-      <c r="T5" s="8">
-        <f t="shared" si="4"/>
         <v>1.3768895906360703</v>
       </c>
       <c r="U5" s="8">
@@ -1514,27 +1543,31 @@
         <v>1.4659384282913379</v>
       </c>
       <c r="V5" s="8">
-        <f t="shared" ref="V5:V10" si="7">H5*0.136067534853132</f>
+        <f t="shared" ref="V5:V10" si="6">H5*0.136067534853132</f>
         <v>13.32781503886428</v>
       </c>
       <c r="W5" s="4">
-        <f t="shared" ref="W5:W10" si="8">H5*0.17</f>
+        <f t="shared" ref="W5:W10" si="7">H5*0.17</f>
         <v>16.651500000000002</v>
       </c>
-      <c r="X5" s="8">
-        <f t="shared" si="5"/>
-        <v>164.84565044166737</v>
-      </c>
-      <c r="Y5" s="9">
+      <c r="X5" s="12">
+        <f t="shared" si="4"/>
+        <v>12.259486641132982</v>
+      </c>
+      <c r="Y5" s="8">
+        <f t="shared" ref="Y3:Y66" si="8">S5+V5+W5+X5</f>
+        <v>177.10513708280035</v>
+      </c>
+      <c r="Z5" s="9">
         <f t="shared" si="1"/>
-        <v>4.1387308672274005E-2</v>
-      </c>
-      <c r="Z5" s="8">
-        <f t="shared" si="2"/>
-        <v>3818.1543495583328</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.4465261632638801E-2</v>
+      </c>
+      <c r="AA5" s="8">
+        <f>J5-Y5</f>
+        <v>3805.8948629171996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2</v>
       </c>
@@ -1577,7 +1610,7 @@
         <v>112.19</v>
       </c>
       <c r="P6" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>6.6311663630618272</v>
       </c>
       <c r="Q6" t="s">
@@ -1587,11 +1620,11 @@
         <v>129</v>
       </c>
       <c r="S6" s="8">
+        <f t="shared" si="2"/>
+        <v>118.82116636306182</v>
+      </c>
+      <c r="T6" s="8">
         <f t="shared" si="3"/>
-        <v>118.82116636306182</v>
-      </c>
-      <c r="T6" s="8">
-        <f t="shared" si="4"/>
         <v>1.3768385441837987</v>
       </c>
       <c r="U6" s="8">
@@ -1599,27 +1632,31 @@
         <v>1.4852645795382728</v>
       </c>
       <c r="V6" s="8">
+        <f t="shared" si="6"/>
+        <v>11.742628257825292</v>
+      </c>
+      <c r="W6" s="4">
         <f t="shared" si="7"/>
-        <v>11.742628257825292</v>
-      </c>
-      <c r="W6" s="4">
+        <v>14.671000000000001</v>
+      </c>
+      <c r="X6" s="12">
+        <f t="shared" si="4"/>
+        <v>10.801364952830795</v>
+      </c>
+      <c r="Y6" s="8">
         <f t="shared" si="8"/>
-        <v>14.671000000000001</v>
-      </c>
-      <c r="X6" s="8">
-        <f t="shared" si="5"/>
-        <v>145.2347946208871</v>
-      </c>
-      <c r="Y6" s="9">
+        <v>156.0361595737179</v>
+      </c>
+      <c r="Z6" s="9">
         <f t="shared" si="1"/>
-        <v>4.2691003709843356E-2</v>
-      </c>
-      <c r="Z6" s="8">
-        <f t="shared" si="2"/>
-        <v>3256.765205379113</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.5866008105149292E-2</v>
+      </c>
+      <c r="AA6" s="8">
+        <f>J6-Y6</f>
+        <v>3245.9638404262823</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2</v>
       </c>
@@ -1662,7 +1699,7 @@
         <v>765.77</v>
       </c>
       <c r="P7" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45.261744451466619</v>
       </c>
       <c r="Q7" t="s">
@@ -1672,11 +1709,11 @@
         <v>17</v>
       </c>
       <c r="S7" s="8">
+        <f t="shared" si="2"/>
+        <v>811.03174445146658</v>
+      </c>
+      <c r="T7" s="8">
         <f t="shared" si="3"/>
-        <v>811.03174445146658</v>
-      </c>
-      <c r="T7" s="8">
-        <f t="shared" si="4"/>
         <v>1.376847032427581</v>
       </c>
       <c r="U7" s="8">
@@ -1684,27 +1721,31 @@
         <v>1.4628999719543048</v>
       </c>
       <c r="V7" s="8">
+        <f t="shared" si="6"/>
+        <v>80.150581405237403</v>
+      </c>
+      <c r="W7" s="4">
         <f t="shared" si="7"/>
-        <v>80.150581405237403</v>
-      </c>
-      <c r="W7" s="4">
+        <v>100.13849999999999</v>
+      </c>
+      <c r="X7" s="12">
+        <f t="shared" si="4"/>
+        <v>73.725886737717019</v>
+      </c>
+      <c r="Y7" s="8">
         <f t="shared" si="8"/>
-        <v>100.13849999999999</v>
-      </c>
-      <c r="X7" s="8">
-        <f t="shared" si="5"/>
-        <v>991.320825856704</v>
-      </c>
-      <c r="Y7" s="9">
+        <v>1065.046712594421</v>
+      </c>
+      <c r="Z7" s="9">
         <f t="shared" si="1"/>
-        <v>3.9260028596157882E-2</v>
-      </c>
-      <c r="Z7" s="8">
-        <f t="shared" si="2"/>
-        <v>24258.809174143298</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.2179850661934054E-2</v>
+      </c>
+      <c r="AA7" s="8">
+        <f>J7-Y7</f>
+        <v>24185.083287405581</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1</v>
       </c>
@@ -1747,7 +1788,7 @@
         <v>130.06</v>
       </c>
       <c r="P8" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.6876963455890595</v>
       </c>
       <c r="Q8" t="s">
@@ -1757,11 +1798,11 @@
         <v>129</v>
       </c>
       <c r="S8" s="8">
+        <f t="shared" si="2"/>
+        <v>137.74769634558905</v>
+      </c>
+      <c r="T8" s="8">
         <f t="shared" si="3"/>
-        <v>137.74769634558905</v>
-      </c>
-      <c r="T8" s="8">
-        <f t="shared" si="4"/>
         <v>1.3767885691713049</v>
       </c>
       <c r="U8" s="8">
@@ -1769,27 +1810,31 @@
         <v>1.4748147360341439</v>
       </c>
       <c r="V8" s="8">
+        <f t="shared" si="6"/>
+        <v>13.613556862055857</v>
+      </c>
+      <c r="W8" s="4">
         <f t="shared" si="7"/>
-        <v>13.613556862055857</v>
-      </c>
-      <c r="W8" s="4">
+        <v>17.008500000000002</v>
+      </c>
+      <c r="X8" s="12">
+        <f t="shared" si="4"/>
+        <v>12.522324027007194</v>
+      </c>
+      <c r="Y8" s="8">
         <f t="shared" si="8"/>
-        <v>17.008500000000002</v>
-      </c>
-      <c r="X8" s="8">
-        <f t="shared" si="5"/>
-        <v>168.36975320764489</v>
-      </c>
-      <c r="Y8" s="9">
+        <v>180.89207723465208</v>
+      </c>
+      <c r="Z8" s="9">
         <f t="shared" si="1"/>
-        <v>3.9592284515470547E-2</v>
-      </c>
-      <c r="Z8" s="8">
-        <f t="shared" si="2"/>
-        <v>4084.2202467923553</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.2536919203274258E-2</v>
+      </c>
+      <c r="AA8" s="8">
+        <f>J8-Y8</f>
+        <v>4071.6979227653483</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1</v>
       </c>
@@ -1832,7 +1877,7 @@
         <v>120.9</v>
       </c>
       <c r="P9" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.1459846090932784</v>
       </c>
       <c r="Q9" t="s">
@@ -1842,11 +1887,11 @@
         <v>138</v>
       </c>
       <c r="S9" s="8">
+        <f t="shared" si="2"/>
+        <v>128.0459846090933</v>
+      </c>
+      <c r="T9" s="8">
         <f t="shared" si="3"/>
-        <v>128.0459846090933</v>
-      </c>
-      <c r="T9" s="8">
-        <f t="shared" si="4"/>
         <v>1.3768385441837989</v>
       </c>
       <c r="U9" s="8">
@@ -1854,27 +1899,31 @@
         <v>1.4889067977801547</v>
       </c>
       <c r="V9" s="8">
+        <f t="shared" si="6"/>
+        <v>12.654280741341276</v>
+      </c>
+      <c r="W9" s="4">
         <f t="shared" si="7"/>
-        <v>12.654280741341276</v>
-      </c>
-      <c r="W9" s="4">
+        <v>15.81</v>
+      </c>
+      <c r="X9" s="12">
+        <f t="shared" si="4"/>
+        <v>11.639941374429478</v>
+      </c>
+      <c r="Y9" s="8">
         <f t="shared" si="8"/>
-        <v>15.81</v>
-      </c>
-      <c r="X9" s="8">
-        <f t="shared" si="5"/>
-        <v>156.51026535043457</v>
-      </c>
-      <c r="Y9" s="9">
+        <v>168.15020672486403</v>
+      </c>
+      <c r="Z9" s="9">
         <f t="shared" si="1"/>
-        <v>3.9944939665514226E-2</v>
-      </c>
-      <c r="Z9" s="8">
-        <f t="shared" si="2"/>
-        <v>3761.6397346495655</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.2915714488946065E-2</v>
+      </c>
+      <c r="AA9" s="8">
+        <f>J9-Y9</f>
+        <v>3749.9997932751362</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1</v>
       </c>
@@ -1917,7 +1966,7 @@
         <v>120.9</v>
       </c>
       <c r="P10" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.1459846090932784</v>
       </c>
       <c r="Q10" t="s">
@@ -1927,11 +1976,11 @@
         <v>138</v>
       </c>
       <c r="S10" s="8">
+        <f t="shared" si="2"/>
+        <v>128.0459846090933</v>
+      </c>
+      <c r="T10" s="8">
         <f t="shared" si="3"/>
-        <v>128.0459846090933</v>
-      </c>
-      <c r="T10" s="8">
-        <f t="shared" si="4"/>
         <v>1.3768385441837989</v>
       </c>
       <c r="U10" s="8">
@@ -1939,27 +1988,31 @@
         <v>1.4889067977801547</v>
       </c>
       <c r="V10" s="8">
+        <f t="shared" si="6"/>
+        <v>12.654280741341276</v>
+      </c>
+      <c r="W10" s="4">
         <f t="shared" si="7"/>
-        <v>12.654280741341276</v>
-      </c>
-      <c r="W10" s="4">
+        <v>15.81</v>
+      </c>
+      <c r="X10" s="12">
+        <f t="shared" si="4"/>
+        <v>11.639941374429478</v>
+      </c>
+      <c r="Y10" s="8">
         <f t="shared" si="8"/>
-        <v>15.81</v>
-      </c>
-      <c r="X10" s="8">
-        <f t="shared" si="5"/>
-        <v>156.51026535043457</v>
-      </c>
-      <c r="Y10" s="9">
+        <v>168.15020672486403</v>
+      </c>
+      <c r="Z10" s="9">
         <f t="shared" si="1"/>
-        <v>4.0073296126186646E-2</v>
-      </c>
-      <c r="Z10" s="8">
-        <f t="shared" si="2"/>
-        <v>3749.0897346495653</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.3053617043441225E-2</v>
+      </c>
+      <c r="AA10" s="8">
+        <f>J10-Y10</f>
+        <v>3737.449793275136</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1</v>
       </c>
@@ -2009,11 +2062,11 @@
         <v>206</v>
       </c>
       <c r="S11" s="8">
+        <f t="shared" si="2"/>
+        <v>747.73773295440185</v>
+      </c>
+      <c r="T11" s="8">
         <f t="shared" si="3"/>
-        <v>747.73773295440185</v>
-      </c>
-      <c r="T11" s="8">
-        <f t="shared" si="4"/>
         <v>0.27665300168506801</v>
       </c>
       <c r="U11" s="8">
@@ -2021,20 +2074,23 @@
         <v>0.30457748796513312</v>
       </c>
       <c r="V11" s="8"/>
-      <c r="X11" s="8">
-        <f t="shared" si="5"/>
-        <v>747.73773295440185</v>
-      </c>
-      <c r="Y11" s="9">
+      <c r="X11" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="9">
         <f t="shared" si="1"/>
-        <v>3.6746866474336573E-2</v>
-      </c>
-      <c r="Z11" s="8">
-        <f t="shared" si="2"/>
-        <v>19600.602267045597</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="8">
+        <f>J11-Y11</f>
+        <v>20348.34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>1</v>
       </c>
@@ -2084,11 +2140,11 @@
         <v>206</v>
       </c>
       <c r="S12" s="8">
+        <f t="shared" si="2"/>
+        <v>115.22597520183082</v>
+      </c>
+      <c r="T12" s="8">
         <f t="shared" si="3"/>
-        <v>115.22597520183082</v>
-      </c>
-      <c r="T12" s="8">
-        <f t="shared" si="4"/>
         <v>0.27665300168506801</v>
       </c>
       <c r="U12" s="8">
@@ -2096,20 +2152,23 @@
         <v>0.29394381429038474</v>
       </c>
       <c r="V12" s="8"/>
-      <c r="X12" s="8">
-        <f t="shared" si="5"/>
-        <v>115.22597520183082</v>
-      </c>
-      <c r="Y12" s="9">
+      <c r="X12" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="9">
         <f t="shared" si="1"/>
-        <v>3.6257386784717058E-2</v>
-      </c>
-      <c r="Z12" s="8">
-        <f t="shared" si="2"/>
-        <v>3062.7740247981692</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="8">
+        <f>J12-Y12</f>
+        <v>3178</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2</v>
       </c>
@@ -2159,11 +2218,11 @@
         <v>17</v>
       </c>
       <c r="S13" s="8">
+        <f t="shared" si="2"/>
+        <v>859.84682713347729</v>
+      </c>
+      <c r="T13" s="8">
         <f t="shared" si="3"/>
-        <v>859.84682713347729</v>
-      </c>
-      <c r="T13" s="8">
-        <f t="shared" si="4"/>
         <v>0.21881838074398199</v>
       </c>
       <c r="U13" s="8">
@@ -2171,20 +2230,24 @@
         <v>0.22795515035351996</v>
       </c>
       <c r="V13" s="8"/>
-      <c r="X13" s="8">
-        <f t="shared" si="5"/>
-        <v>859.84682713347729</v>
-      </c>
-      <c r="Y13" s="9">
+      <c r="X13" s="12">
+        <f t="shared" si="4"/>
+        <v>491.8188132346304</v>
+      </c>
+      <c r="Y13" s="8">
+        <f t="shared" si="8"/>
+        <v>1351.6656403681077</v>
+      </c>
+      <c r="Z13" s="9">
         <f t="shared" si="1"/>
-        <v>1.9712576735324751E-2</v>
-      </c>
-      <c r="Z13" s="8">
-        <f t="shared" si="2"/>
-        <v>42759.353172866518</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>3.0987859483165847E-2</v>
+      </c>
+      <c r="AA13" s="8">
+        <f>J13-Y13</f>
+        <v>42267.534359631893</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2</v>
       </c>
@@ -2234,11 +2297,11 @@
         <v>17</v>
       </c>
       <c r="S14" s="8">
+        <f t="shared" si="2"/>
+        <v>240.15317286652024</v>
+      </c>
+      <c r="T14" s="8">
         <f t="shared" si="3"/>
-        <v>240.15317286652024</v>
-      </c>
-      <c r="T14" s="8">
-        <f t="shared" si="4"/>
         <v>0.21881838074398199</v>
       </c>
       <c r="U14" s="8">
@@ -2246,20 +2309,24 @@
         <v>0.23452458287746117</v>
       </c>
       <c r="V14" s="8"/>
-      <c r="X14" s="8">
-        <f t="shared" si="5"/>
-        <v>240.15317286652024</v>
-      </c>
-      <c r="Y14" s="9">
+      <c r="X14" s="12">
+        <f t="shared" si="4"/>
+        <v>137.36382428426185</v>
+      </c>
+      <c r="Y14" s="8">
+        <f t="shared" si="8"/>
+        <v>377.51699715078212</v>
+      </c>
+      <c r="Z14" s="9">
         <f t="shared" si="1"/>
-        <v>1.6416800961583228E-2</v>
-      </c>
-      <c r="Z14" s="8">
-        <f t="shared" si="2"/>
-        <v>14388.34682713348</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+        <v>2.5806951987611997E-2</v>
+      </c>
+      <c r="AA14" s="8">
+        <f>J14-Y14</f>
+        <v>14250.983002849218</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>1</v>
       </c>
@@ -2310,11 +2377,11 @@
         <v>17</v>
       </c>
       <c r="S15" s="8">
+        <f t="shared" si="2"/>
+        <v>1.713499535298711</v>
+      </c>
+      <c r="T15" s="8">
         <f t="shared" si="3"/>
-        <v>1.713499535298711</v>
-      </c>
-      <c r="T15" s="8">
-        <f t="shared" si="4"/>
         <v>7.6838544183798693E-2</v>
       </c>
       <c r="U15" s="8">
@@ -2329,20 +2396,24 @@
         <f>H15*0.17</f>
         <v>3.7910000000000004</v>
       </c>
-      <c r="X15" s="8">
-        <f t="shared" si="5"/>
-        <v>8.5388055625235548</v>
-      </c>
-      <c r="Y15" s="9">
+      <c r="X15" s="12">
+        <f t="shared" si="4"/>
+        <v>2.7910827166642727</v>
+      </c>
+      <c r="Y15" s="8">
+        <f t="shared" si="8"/>
+        <v>11.329888279187827</v>
+      </c>
+      <c r="Z15" s="9">
         <f t="shared" si="1"/>
-        <v>4.0426122348847432E-2</v>
-      </c>
-      <c r="Z15" s="8">
-        <f t="shared" si="2"/>
-        <v>202.68119443747645</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+        <v>5.364022478547404E-2</v>
+      </c>
+      <c r="AA15" s="8">
+        <f>J15-Y15</f>
+        <v>199.89011172081217</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2</v>
       </c>
@@ -2393,11 +2464,11 @@
         <v>17</v>
       </c>
       <c r="S16" s="8">
+        <f t="shared" si="2"/>
+        <v>22.436854901669218</v>
+      </c>
+      <c r="T16" s="8">
         <f t="shared" si="3"/>
-        <v>22.436854901669218</v>
-      </c>
-      <c r="T16" s="8">
-        <f t="shared" si="4"/>
         <v>7.6838544183798693E-2</v>
       </c>
       <c r="U16" s="8">
@@ -2412,20 +2483,24 @@
         <f>H16*0.17</f>
         <v>49.64</v>
       </c>
-      <c r="X16" s="8">
-        <f t="shared" si="5"/>
-        <v>111.80857507878376</v>
-      </c>
-      <c r="Y16" s="9">
+      <c r="X16" s="12">
+        <f t="shared" si="4"/>
+        <v>36.546912702509758</v>
+      </c>
+      <c r="Y16" s="8">
+        <f t="shared" si="8"/>
+        <v>148.3554877812935</v>
+      </c>
+      <c r="Z16" s="9">
         <f t="shared" si="1"/>
-        <v>2.8884014280417925E-2</v>
-      </c>
-      <c r="Z16" s="8">
-        <f t="shared" si="2"/>
-        <v>3759.1414249212162</v>
-      </c>
-    </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+        <v>3.8325343334657772E-2</v>
+      </c>
+      <c r="AA16" s="8">
+        <f>J16-Y16</f>
+        <v>3722.5945122187063</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2</v>
       </c>
@@ -2476,11 +2551,11 @@
         <v>17</v>
       </c>
       <c r="S17" s="8">
+        <f t="shared" si="2"/>
+        <v>2.1476373099371733</v>
+      </c>
+      <c r="T17" s="8">
         <f t="shared" si="3"/>
-        <v>2.1476373099371733</v>
-      </c>
-      <c r="T17" s="8">
-        <f t="shared" si="4"/>
         <v>7.6838544183798693E-2</v>
       </c>
       <c r="U17" s="8">
@@ -2495,20 +2570,24 @@
         <f>H17*0.17</f>
         <v>4.7515000000000001</v>
       </c>
-      <c r="X17" s="8">
-        <f t="shared" si="5"/>
-        <v>10.702224909082213</v>
-      </c>
-      <c r="Y17" s="9">
+      <c r="X17" s="12">
+        <f t="shared" si="4"/>
+        <v>3.4982404453258482</v>
+      </c>
+      <c r="Y17" s="8">
+        <f t="shared" si="8"/>
+        <v>14.200465354408061</v>
+      </c>
+      <c r="Z17" s="9">
         <f t="shared" si="1"/>
-        <v>5.0240469951564233E-2</v>
-      </c>
-      <c r="Z17" s="8">
-        <f t="shared" si="2"/>
-        <v>202.31777509091779</v>
-      </c>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+        <v>6.6662592030833065E-2</v>
+      </c>
+      <c r="AA17" s="8">
+        <f>J17-Y17</f>
+        <v>198.81953464559194</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>1</v>
       </c>
@@ -2558,11 +2637,11 @@
         <v>206</v>
       </c>
       <c r="S18" s="8">
+        <f t="shared" si="2"/>
+        <v>1026.3571367042823</v>
+      </c>
+      <c r="T18" s="8">
         <f t="shared" si="3"/>
-        <v>1026.3571367042823</v>
-      </c>
-      <c r="T18" s="8">
-        <f t="shared" si="4"/>
         <v>0.189508140236024</v>
       </c>
       <c r="U18" s="8">
@@ -2570,20 +2649,23 @@
         <v>0.20364228902862744</v>
       </c>
       <c r="V18" s="8"/>
-      <c r="X18" s="8">
-        <f t="shared" si="5"/>
-        <v>1026.3571367042823</v>
-      </c>
-      <c r="Y18" s="9">
+      <c r="X18" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="9">
         <f t="shared" si="1"/>
-        <v>2.4920750856487057E-2</v>
-      </c>
-      <c r="Z18" s="8">
-        <f t="shared" si="2"/>
-        <v>40158.482863295714</v>
-      </c>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="8">
+        <f>J18-Y18</f>
+        <v>41184.839999999997</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2</v>
       </c>
@@ -2637,11 +2719,11 @@
         <v>65</v>
       </c>
       <c r="S19" s="8">
+        <f t="shared" si="2"/>
+        <v>549.536178942378</v>
+      </c>
+      <c r="T19" s="8">
         <f t="shared" si="3"/>
-        <v>549.536178942378</v>
-      </c>
-      <c r="T19" s="8">
-        <f t="shared" si="4"/>
         <v>6.1572681113991932</v>
       </c>
       <c r="U19" s="8">
@@ -2656,20 +2738,24 @@
         <f t="shared" ref="W19:W44" si="12">H19*0.17</f>
         <v>15.172500000000001</v>
       </c>
-      <c r="X19" s="8">
-        <f t="shared" si="5"/>
-        <v>576.85270642802004</v>
-      </c>
-      <c r="Y19" s="9">
+      <c r="X19" s="12">
+        <f t="shared" si="4"/>
+        <v>11.170588899654096</v>
+      </c>
+      <c r="Y19" s="8">
+        <f t="shared" si="8"/>
+        <v>588.02329532767419</v>
+      </c>
+      <c r="Z19" s="9">
         <f t="shared" si="1"/>
-        <v>0.17499475380051571</v>
-      </c>
-      <c r="Z19" s="8">
-        <f t="shared" si="2"/>
-        <v>2719.5472935719799</v>
-      </c>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.17838347752932721</v>
+      </c>
+      <c r="AA19" s="8">
+        <f>J19-Y19</f>
+        <v>2708.376704672326</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2</v>
       </c>
@@ -2723,11 +2809,11 @@
         <v>65</v>
       </c>
       <c r="S20" s="8">
+        <f t="shared" si="2"/>
+        <v>549.57617894237796</v>
+      </c>
+      <c r="T20" s="8">
         <f t="shared" si="3"/>
-        <v>549.57617894237796</v>
-      </c>
-      <c r="T20" s="8">
-        <f t="shared" si="4"/>
         <v>6.1577162906709013</v>
       </c>
       <c r="U20" s="8">
@@ -2742,20 +2828,24 @@
         <f t="shared" si="12"/>
         <v>15.172500000000001</v>
       </c>
-      <c r="X20" s="8">
-        <f t="shared" si="5"/>
-        <v>576.89270642802001</v>
-      </c>
-      <c r="Y20" s="9">
+      <c r="X20" s="12">
+        <f t="shared" si="4"/>
+        <v>11.170588899654096</v>
+      </c>
+      <c r="Y20" s="8">
+        <f t="shared" si="8"/>
+        <v>588.06329532767415</v>
+      </c>
+      <c r="Z20" s="9">
         <f t="shared" si="1"/>
-        <v>0.17470479586566731</v>
-      </c>
-      <c r="Z20" s="8">
-        <f t="shared" si="2"/>
-        <v>2725.2072935719798</v>
-      </c>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.17808767006682844</v>
+      </c>
+      <c r="AA20" s="8">
+        <f>J20-Y20</f>
+        <v>2714.0367046723259</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2</v>
       </c>
@@ -2809,11 +2899,11 @@
         <v>65</v>
       </c>
       <c r="S21" s="8">
+        <f t="shared" si="2"/>
+        <v>647.75715999367878</v>
+      </c>
+      <c r="T21" s="8">
         <f t="shared" si="3"/>
-        <v>647.75715999367878</v>
-      </c>
-      <c r="T21" s="8">
-        <f t="shared" si="4"/>
         <v>5.7298289251983974</v>
       </c>
       <c r="U21" s="8">
@@ -2828,20 +2918,24 @@
         <f t="shared" si="12"/>
         <v>19.218500000000002</v>
       </c>
-      <c r="X21" s="8">
-        <f t="shared" si="5"/>
-        <v>682.35809480882529</v>
-      </c>
-      <c r="Y21" s="9">
+      <c r="X21" s="12">
+        <f t="shared" si="4"/>
+        <v>14.14941260622852</v>
+      </c>
+      <c r="Y21" s="8">
+        <f t="shared" si="8"/>
+        <v>696.50750741505385</v>
+      </c>
+      <c r="Z21" s="9">
         <f t="shared" si="1"/>
-        <v>0.153423366754466</v>
-      </c>
-      <c r="Z21" s="8">
-        <f t="shared" si="2"/>
-        <v>3765.191905191175</v>
-      </c>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.15660476159122524</v>
+      </c>
+      <c r="AA21" s="8">
+        <f>J21-Y21</f>
+        <v>3751.0424925849466</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2</v>
       </c>
@@ -2895,11 +2989,11 @@
         <v>65</v>
       </c>
       <c r="S22" s="8">
+        <f t="shared" si="2"/>
+        <v>550.87617894237803</v>
+      </c>
+      <c r="T22" s="8">
         <f t="shared" si="3"/>
-        <v>550.87617894237803</v>
-      </c>
-      <c r="T22" s="8">
-        <f t="shared" si="4"/>
         <v>6.1722821170014344</v>
       </c>
       <c r="U22" s="8">
@@ -2914,20 +3008,24 @@
         <f t="shared" si="12"/>
         <v>15.172500000000001</v>
       </c>
-      <c r="X22" s="8">
-        <f t="shared" si="5"/>
-        <v>578.19270642802007</v>
-      </c>
-      <c r="Y22" s="9">
+      <c r="X22" s="12">
+        <f t="shared" si="4"/>
+        <v>11.170588899654096</v>
+      </c>
+      <c r="Y22" s="8">
+        <f t="shared" si="8"/>
+        <v>589.36329532767422</v>
+      </c>
+      <c r="Z22" s="9">
         <f t="shared" si="1"/>
-        <v>0.1642709585703587</v>
-      </c>
-      <c r="Z22" s="8">
-        <f t="shared" si="2"/>
-        <v>2941.5572935719802</v>
-      </c>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.1674446467299309</v>
+      </c>
+      <c r="AA22" s="8">
+        <f>J22-Y22</f>
+        <v>2930.3867046723258</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2</v>
       </c>
@@ -2981,11 +3079,11 @@
         <v>65</v>
       </c>
       <c r="S23" s="8">
+        <f t="shared" si="2"/>
+        <v>519.93294315390244</v>
+      </c>
+      <c r="T23" s="8">
         <f t="shared" si="3"/>
-        <v>519.93294315390244</v>
-      </c>
-      <c r="T23" s="8">
-        <f t="shared" si="4"/>
         <v>7.2819739937521346</v>
       </c>
       <c r="U23" s="8">
@@ -3000,20 +3098,24 @@
         <f t="shared" si="12"/>
         <v>12.138000000000002</v>
       </c>
-      <c r="X23" s="8">
-        <f t="shared" si="5"/>
-        <v>541.78616514241605</v>
-      </c>
-      <c r="Y23" s="9">
+      <c r="X23" s="12">
+        <f t="shared" si="4"/>
+        <v>8.9364711197232776</v>
+      </c>
+      <c r="Y23" s="8">
+        <f t="shared" si="8"/>
+        <v>550.7226362621393</v>
+      </c>
+      <c r="Z23" s="9">
         <f t="shared" si="1"/>
-        <v>0.20553344656389078</v>
-      </c>
-      <c r="Z23" s="8">
-        <f t="shared" si="2"/>
-        <v>2094.2138348575841</v>
-      </c>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.20892361011462038</v>
+      </c>
+      <c r="AA23" s="8">
+        <f>J23-Y23</f>
+        <v>2085.2773637378605</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2</v>
       </c>
@@ -3067,11 +3169,11 @@
         <v>65</v>
       </c>
       <c r="S24" s="8">
+        <f t="shared" si="2"/>
+        <v>500.19745262825199</v>
+      </c>
+      <c r="T24" s="8">
         <f t="shared" si="3"/>
-        <v>500.19745262825199</v>
-      </c>
-      <c r="T24" s="8">
-        <f t="shared" si="4"/>
         <v>8.4066798761050752</v>
       </c>
       <c r="U24" s="8">
@@ -3086,20 +3188,24 @@
         <f t="shared" si="12"/>
         <v>10.115</v>
       </c>
-      <c r="X24" s="8">
-        <f t="shared" si="5"/>
-        <v>518.40847095201332</v>
-      </c>
-      <c r="Y24" s="9">
+      <c r="X24" s="12">
+        <f t="shared" si="4"/>
+        <v>7.4470592664360629</v>
+      </c>
+      <c r="Y24" s="8">
+        <f t="shared" si="8"/>
+        <v>525.85553021844942</v>
+      </c>
+      <c r="Z24" s="9">
         <f t="shared" si="1"/>
-        <v>0.23589755685839703</v>
-      </c>
-      <c r="Z24" s="8">
-        <f t="shared" si="2"/>
-        <v>1679.1915290479865</v>
-      </c>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.23928628058720852</v>
+      </c>
+      <c r="AA24" s="8">
+        <f>J24-Y24</f>
+        <v>1671.7444697815504</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2</v>
       </c>
@@ -3153,11 +3259,11 @@
         <v>65</v>
       </c>
       <c r="S25" s="8">
+        <f t="shared" si="2"/>
+        <v>646.1171599936788</v>
+      </c>
+      <c r="T25" s="8">
         <f t="shared" si="3"/>
-        <v>646.1171599936788</v>
-      </c>
-      <c r="T25" s="8">
-        <f t="shared" si="4"/>
         <v>5.7153220698246692</v>
       </c>
       <c r="U25" s="8">
@@ -3172,20 +3278,24 @@
         <f t="shared" si="12"/>
         <v>19.218500000000002</v>
       </c>
-      <c r="X25" s="8">
-        <f t="shared" si="5"/>
-        <v>680.7180948088253</v>
-      </c>
-      <c r="Y25" s="9">
+      <c r="X25" s="12">
+        <f t="shared" si="4"/>
+        <v>14.14941260622852</v>
+      </c>
+      <c r="Y25" s="8">
+        <f t="shared" si="8"/>
+        <v>694.86750741505386</v>
+      </c>
+      <c r="Z25" s="9">
         <f t="shared" si="1"/>
-        <v>0.16311657596300808</v>
-      </c>
-      <c r="Z25" s="8">
-        <f t="shared" si="2"/>
-        <v>3492.4819051911745</v>
-      </c>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.16650711861762049</v>
+      </c>
+      <c r="AA25" s="8">
+        <f>J25-Y25</f>
+        <v>3478.3324925849461</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2</v>
       </c>
@@ -3237,11 +3347,11 @@
         <v>65</v>
       </c>
       <c r="S26" s="8">
+        <f t="shared" si="2"/>
+        <v>3657.147522159486</v>
+      </c>
+      <c r="T26" s="8">
         <f t="shared" si="3"/>
-        <v>3657.147522159486</v>
-      </c>
-      <c r="T26" s="8">
-        <f t="shared" si="4"/>
         <v>1.4566826743246579</v>
       </c>
       <c r="U26" s="8">
@@ -3256,20 +3366,24 @@
         <f t="shared" si="12"/>
         <v>426.80200000000002</v>
       </c>
-      <c r="X26" s="8">
-        <f t="shared" si="5"/>
-        <v>4425.5606751617588</v>
-      </c>
-      <c r="Y26" s="9">
+      <c r="X26" s="12">
+        <f t="shared" si="4"/>
+        <v>314.22835284561984</v>
+      </c>
+      <c r="Y26" s="8">
+        <f t="shared" si="8"/>
+        <v>4739.7890280073789</v>
+      </c>
+      <c r="Z26" s="9">
         <f t="shared" si="1"/>
-        <v>5.2924160916443738E-2</v>
-      </c>
-      <c r="Z26" s="8">
-        <f t="shared" si="2"/>
-        <v>79195.239324838243</v>
-      </c>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+        <v>5.668193832165417E-2</v>
+      </c>
+      <c r="AA26" s="8">
+        <f>J26-Y26</f>
+        <v>78881.010971992626</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2</v>
       </c>
@@ -3323,11 +3437,11 @@
         <v>65</v>
       </c>
       <c r="S27" s="8">
+        <f t="shared" si="2"/>
+        <v>519.93294315390244</v>
+      </c>
+      <c r="T27" s="8">
         <f t="shared" si="3"/>
-        <v>519.93294315390244</v>
-      </c>
-      <c r="T27" s="8">
-        <f t="shared" si="4"/>
         <v>7.2819739937521346</v>
       </c>
       <c r="U27" s="8">
@@ -3342,20 +3456,24 @@
         <f t="shared" si="12"/>
         <v>12.138000000000002</v>
       </c>
-      <c r="X27" s="8">
-        <f t="shared" si="5"/>
-        <v>541.78616514241605</v>
-      </c>
-      <c r="Y27" s="9">
+      <c r="X27" s="12">
+        <f t="shared" si="4"/>
+        <v>8.9364711197232776</v>
+      </c>
+      <c r="Y27" s="8">
+        <f t="shared" si="8"/>
+        <v>550.7226362621393</v>
+      </c>
+      <c r="Z27" s="9">
         <f t="shared" si="1"/>
-        <v>0.20553344656389078</v>
-      </c>
-      <c r="Z27" s="8">
-        <f t="shared" si="2"/>
-        <v>2094.2138348575841</v>
-      </c>
-    </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.20892361011462038</v>
+      </c>
+      <c r="AA27" s="8">
+        <f>J27-Y27</f>
+        <v>2085.2773637378605</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2</v>
       </c>
@@ -3409,11 +3527,11 @@
         <v>65</v>
       </c>
       <c r="S28" s="8">
+        <f t="shared" si="2"/>
+        <v>550.87617894237803</v>
+      </c>
+      <c r="T28" s="8">
         <f t="shared" si="3"/>
-        <v>550.87617894237803</v>
-      </c>
-      <c r="T28" s="8">
-        <f t="shared" si="4"/>
         <v>6.1722821170014344</v>
       </c>
       <c r="U28" s="8">
@@ -3428,20 +3546,24 @@
         <f t="shared" si="12"/>
         <v>15.172500000000001</v>
       </c>
-      <c r="X28" s="8">
-        <f t="shared" si="5"/>
-        <v>578.19270642802007</v>
-      </c>
-      <c r="Y28" s="9">
+      <c r="X28" s="12">
+        <f t="shared" si="4"/>
+        <v>11.170588899654096</v>
+      </c>
+      <c r="Y28" s="8">
+        <f t="shared" si="8"/>
+        <v>589.36329532767422</v>
+      </c>
+      <c r="Z28" s="9">
         <f t="shared" si="1"/>
-        <v>0.1642709585703587</v>
-      </c>
-      <c r="Z28" s="8">
-        <f t="shared" si="2"/>
-        <v>2941.5572935719802</v>
-      </c>
-    </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.1674446467299309</v>
+      </c>
+      <c r="AA28" s="8">
+        <f>J28-Y28</f>
+        <v>2930.3867046723258</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2</v>
       </c>
@@ -3495,11 +3617,11 @@
         <v>65</v>
       </c>
       <c r="S29" s="8">
+        <f t="shared" si="2"/>
+        <v>698.73265051932924</v>
+      </c>
+      <c r="T29" s="8">
         <f t="shared" si="3"/>
-        <v>698.73265051932924</v>
-      </c>
-      <c r="T29" s="8">
-        <f t="shared" si="4"/>
         <v>5.5920980433719825</v>
       </c>
       <c r="U29" s="8">
@@ -3514,20 +3636,24 @@
         <f t="shared" si="12"/>
         <v>21.241500000000002</v>
       </c>
-      <c r="X29" s="8">
-        <f t="shared" si="5"/>
-        <v>736.97578899922803</v>
-      </c>
-      <c r="Y29" s="9">
+      <c r="X29" s="12">
+        <f t="shared" si="4"/>
+        <v>15.638824459515734</v>
+      </c>
+      <c r="Y29" s="8">
+        <f t="shared" si="8"/>
+        <v>752.61461345874375</v>
+      </c>
+      <c r="Z29" s="9">
         <f t="shared" si="1"/>
-        <v>0.15951856904745196</v>
-      </c>
-      <c r="Z29" s="8">
-        <f t="shared" si="2"/>
-        <v>3883.0242110007721</v>
-      </c>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.16290359598674106</v>
+      </c>
+      <c r="AA29" s="8">
+        <f>J29-Y29</f>
+        <v>3867.3853865412561</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2</v>
       </c>
@@ -3581,11 +3707,11 @@
         <v>65</v>
       </c>
       <c r="S30" s="8">
+        <f t="shared" si="2"/>
+        <v>500.25745262825194</v>
+      </c>
+      <c r="T30" s="8">
         <f t="shared" si="3"/>
-        <v>500.25745262825194</v>
-      </c>
-      <c r="T30" s="8">
-        <f t="shared" si="4"/>
         <v>8.4076882794664183</v>
       </c>
       <c r="U30" s="8">
@@ -3600,20 +3726,24 @@
         <f t="shared" si="12"/>
         <v>10.115</v>
       </c>
-      <c r="X30" s="8">
-        <f t="shared" si="5"/>
-        <v>518.46847095201326</v>
-      </c>
-      <c r="Y30" s="9">
+      <c r="X30" s="12">
+        <f t="shared" si="4"/>
+        <v>7.4470592664360629</v>
+      </c>
+      <c r="Y30" s="8">
+        <f t="shared" si="8"/>
+        <v>525.91553021844936</v>
+      </c>
+      <c r="Z30" s="9">
         <f t="shared" si="1"/>
-        <v>0.23502650541795705</v>
-      </c>
-      <c r="Z30" s="8">
-        <f t="shared" si="2"/>
-        <v>1687.5315290479866</v>
-      </c>
-    </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.23840232557499971</v>
+      </c>
+      <c r="AA30" s="8">
+        <f>J30-Y30</f>
+        <v>1680.0844697815505</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>4</v>
       </c>
@@ -3663,11 +3793,11 @@
         <v>46</v>
       </c>
       <c r="S31" s="8">
+        <f t="shared" si="2"/>
+        <v>7200</v>
+      </c>
+      <c r="T31" s="8">
         <f t="shared" si="3"/>
-        <v>7200</v>
-      </c>
-      <c r="T31" s="8">
-        <f t="shared" si="4"/>
         <v>2.2825259954349479</v>
       </c>
       <c r="U31" s="8">
@@ -3682,20 +3812,24 @@
         <f t="shared" si="12"/>
         <v>536.24800000000005</v>
       </c>
-      <c r="X31" s="8">
-        <f t="shared" si="5"/>
-        <v>8165.4594319407188</v>
-      </c>
-      <c r="Y31" s="9">
-        <f t="shared" si="1"/>
-        <v>6.8995097795498034E-2</v>
-      </c>
-      <c r="Z31" s="8">
-        <f t="shared" si="2"/>
-        <v>110182.94056805928</v>
-      </c>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="X31" s="12">
+        <f t="shared" si="4"/>
+        <v>394.80678571505746</v>
+      </c>
+      <c r="Y31" s="8">
+        <f t="shared" si="8"/>
+        <v>8560.2662176557769</v>
+      </c>
+      <c r="Z31" s="9">
+        <f>Y31/J31</f>
+        <v>7.2331068418802255E-2</v>
+      </c>
+      <c r="AA31" s="8">
+        <f>J31-Y31</f>
+        <v>109788.13378234422</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2</v>
       </c>
@@ -3748,11 +3882,11 @@
         <v>128</v>
       </c>
       <c r="S32" s="8">
+        <f t="shared" si="2"/>
+        <v>227.86677906241869</v>
+      </c>
+      <c r="T32" s="8">
         <f t="shared" si="3"/>
-        <v>227.86677906241869</v>
-      </c>
-      <c r="T32" s="8">
-        <f t="shared" si="4"/>
         <v>1.3768385441837987</v>
       </c>
       <c r="U32" s="8">
@@ -3767,20 +3901,24 @@
         <f t="shared" si="12"/>
         <v>28.135000000000002</v>
       </c>
-      <c r="X32" s="8">
-        <f t="shared" si="5"/>
-        <v>278.52095608061205</v>
-      </c>
-      <c r="Y32" s="9">
+      <c r="X32" s="12">
+        <f t="shared" si="4"/>
+        <v>20.714089220086866</v>
+      </c>
+      <c r="Y32" s="8">
+        <f t="shared" si="8"/>
+        <v>299.23504530069891</v>
+      </c>
+      <c r="Z32" s="9">
         <f t="shared" si="1"/>
-        <v>4.1477432029875215E-2</v>
-      </c>
-      <c r="Z32" s="8">
-        <f t="shared" si="2"/>
-        <v>6436.4790439193875</v>
-      </c>
-    </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.4562180982978247E-2</v>
+      </c>
+      <c r="AA32" s="8">
+        <f>J32-Y32</f>
+        <v>6415.7649546993007</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2</v>
       </c>
@@ -3833,11 +3971,11 @@
         <v>138</v>
       </c>
       <c r="S33" s="8">
+        <f t="shared" si="2"/>
+        <v>251.27303431354326</v>
+      </c>
+      <c r="T33" s="8">
         <f t="shared" si="3"/>
-        <v>251.27303431354326</v>
-      </c>
-      <c r="T33" s="8">
-        <f t="shared" si="4"/>
         <v>1.3768385441837987</v>
       </c>
       <c r="U33" s="8">
@@ -3852,20 +3990,24 @@
         <f t="shared" si="12"/>
         <v>31.025000000000002</v>
       </c>
-      <c r="X33" s="8">
-        <f t="shared" si="5"/>
-        <v>307.13035942423983</v>
-      </c>
-      <c r="Y33" s="9">
+      <c r="X33" s="12">
+        <f t="shared" si="4"/>
+        <v>22.841820439068599</v>
+      </c>
+      <c r="Y33" s="8">
+        <f t="shared" si="8"/>
+        <v>329.97217986330844</v>
+      </c>
+      <c r="Z33" s="9">
         <f t="shared" si="1"/>
-        <v>4.0911439607875084E-2</v>
-      </c>
-      <c r="Z33" s="8">
-        <f t="shared" si="2"/>
-        <v>7200.0696405757599</v>
-      </c>
-    </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.3954094717512313E-2</v>
+      </c>
+      <c r="AA33" s="8">
+        <f>J33-Y33</f>
+        <v>7177.2278201366917</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2</v>
       </c>
@@ -3937,20 +4079,24 @@
         <f t="shared" si="12"/>
         <v>50.575000000000003</v>
       </c>
-      <c r="X34" s="8">
-        <f t="shared" si="5"/>
-        <v>500.66455851348684</v>
-      </c>
-      <c r="Y34" s="9">
-        <f t="shared" ref="Y34:Y65" si="17">X34/J34</f>
-        <v>4.1206959548435132E-2</v>
-      </c>
-      <c r="Z34" s="8">
-        <f t="shared" ref="Z34:Z65" si="18">J34-X34</f>
-        <v>11649.335441486513</v>
-      </c>
-    </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="X34" s="12">
+        <f t="shared" si="4"/>
+        <v>37.235296332180319</v>
+      </c>
+      <c r="Y34" s="8">
+        <f t="shared" si="8"/>
+        <v>537.89985484566716</v>
+      </c>
+      <c r="Z34" s="9">
+        <f t="shared" ref="Z34:Z65" si="17">Y34/J34</f>
+        <v>4.4271592991412936E-2</v>
+      </c>
+      <c r="AA34" s="8">
+        <f t="shared" ref="AA34:AA65" si="18">J34-Y34</f>
+        <v>11612.100145154332</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2</v>
       </c>
@@ -4022,20 +4168,24 @@
         <f t="shared" si="12"/>
         <v>25.925000000000001</v>
       </c>
-      <c r="X35" s="8">
-        <f t="shared" si="5"/>
-        <v>256.64317705313192</v>
-      </c>
-      <c r="Y35" s="9">
+      <c r="X35" s="12">
+        <f t="shared" si="4"/>
+        <v>19.08700064086554</v>
+      </c>
+      <c r="Y35" s="8">
+        <f t="shared" si="8"/>
+        <v>275.73017769399746</v>
+      </c>
+      <c r="Z35" s="9">
         <f t="shared" si="17"/>
-        <v>4.0100496414551864E-2</v>
-      </c>
-      <c r="Z35" s="8">
+        <v>4.3082840264687103E-2</v>
+      </c>
+      <c r="AA35" s="8">
         <f t="shared" si="18"/>
-        <v>6143.3568229468683</v>
-      </c>
-    </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
+        <v>6124.2698223060024</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>1</v>
       </c>
@@ -4107,20 +4257,24 @@
         <f t="shared" si="12"/>
         <v>25.925000000000001</v>
       </c>
-      <c r="X36" s="8">
-        <f t="shared" si="5"/>
-        <v>256.64317705313192</v>
-      </c>
-      <c r="Y36" s="9">
+      <c r="X36" s="12">
+        <f t="shared" si="4"/>
+        <v>19.08700064086554</v>
+      </c>
+      <c r="Y36" s="8">
+        <f t="shared" si="8"/>
+        <v>275.73017769399746</v>
+      </c>
+      <c r="Z36" s="9">
         <f t="shared" si="17"/>
-        <v>3.9688112124508144E-2</v>
-      </c>
-      <c r="Z36" s="8">
+        <v>4.2639786235830431E-2</v>
+      </c>
+      <c r="AA36" s="8">
         <f t="shared" si="18"/>
-        <v>6209.8568229468683</v>
-      </c>
-    </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
+        <v>6190.7698223060024</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>1</v>
       </c>
@@ -4192,20 +4346,24 @@
         <f t="shared" si="12"/>
         <v>38.25</v>
       </c>
-      <c r="X37" s="8">
-        <f t="shared" si="5"/>
-        <v>378.65386778330941</v>
-      </c>
-      <c r="Y37" s="9">
+      <c r="X37" s="12">
+        <f t="shared" si="4"/>
+        <v>28.161148486522929</v>
+      </c>
+      <c r="Y37" s="8">
+        <f t="shared" si="8"/>
+        <v>406.81501626983231</v>
+      </c>
+      <c r="Z37" s="9">
         <f t="shared" si="17"/>
-        <v>3.9400427431044431E-2</v>
-      </c>
-      <c r="Z37" s="8">
+        <v>4.2330705930016685E-2</v>
+      </c>
+      <c r="AA37" s="8">
         <f t="shared" si="18"/>
-        <v>9231.746132216691</v>
-      </c>
-    </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
+        <v>9203.5849837301666</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>1</v>
       </c>
@@ -4277,20 +4435,24 @@
         <f t="shared" si="12"/>
         <v>5.6950000000000003</v>
       </c>
-      <c r="X38" s="8">
-        <f t="shared" si="5"/>
-        <v>56.377353647737174</v>
-      </c>
-      <c r="Y38" s="9">
+      <c r="X38" s="12">
+        <f t="shared" si="4"/>
+        <v>4.1928821079934133</v>
+      </c>
+      <c r="Y38" s="8">
+        <f t="shared" si="8"/>
+        <v>60.570235755730586</v>
+      </c>
+      <c r="Z38" s="9">
         <f t="shared" si="17"/>
-        <v>4.1157361401472609E-2</v>
-      </c>
-      <c r="Z38" s="8">
+        <v>4.4218306143765942E-2</v>
+      </c>
+      <c r="AA38" s="8">
         <f t="shared" si="18"/>
-        <v>1313.4226463522627</v>
-      </c>
-    </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
+        <v>1309.2297642442693</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>1</v>
       </c>
@@ -4362,20 +4524,24 @@
         <f t="shared" si="12"/>
         <v>18.02</v>
       </c>
-      <c r="X39" s="8">
-        <f t="shared" si="5"/>
-        <v>178.3880443779147</v>
-      </c>
-      <c r="Y39" s="9">
+      <c r="X39" s="12">
+        <f t="shared" si="4"/>
+        <v>13.267029953650802</v>
+      </c>
+      <c r="Y39" s="8">
+        <f t="shared" si="8"/>
+        <v>191.65507433156549</v>
+      </c>
+      <c r="Z39" s="9">
         <f t="shared" si="17"/>
-        <v>3.9521466729715023E-2</v>
-      </c>
-      <c r="Z39" s="8">
+        <v>4.2460747132411436E-2</v>
+      </c>
+      <c r="AA39" s="8">
         <f t="shared" si="18"/>
-        <v>4335.3119556220854</v>
-      </c>
-    </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4322.0449256684342</v>
+      </c>
+    </row>
+    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>1</v>
       </c>
@@ -4447,20 +4613,24 @@
         <f t="shared" si="12"/>
         <v>13.0985</v>
       </c>
-      <c r="X40" s="8">
-        <f t="shared" si="5"/>
-        <v>129.66291338979551</v>
-      </c>
-      <c r="Y40" s="9">
+      <c r="X40" s="12">
+        <f t="shared" si="4"/>
+        <v>9.6436288483848518</v>
+      </c>
+      <c r="Y40" s="8">
+        <f t="shared" si="8"/>
+        <v>139.30654223818036</v>
+      </c>
+      <c r="Z40" s="9">
         <f t="shared" si="17"/>
-        <v>3.7302656061414662E-2</v>
-      </c>
-      <c r="Z40" s="8">
+        <v>4.0077026625137839E-2</v>
+      </c>
+      <c r="AA40" s="8">
         <f t="shared" si="18"/>
-        <v>3346.3070866102044</v>
-      </c>
-    </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
+        <v>3336.6634577618192</v>
+      </c>
+    </row>
+    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>1</v>
       </c>
@@ -4532,20 +4702,24 @@
         <f t="shared" si="12"/>
         <v>15.81</v>
       </c>
-      <c r="X41" s="8">
-        <f t="shared" si="5"/>
-        <v>156.51026535043457</v>
-      </c>
-      <c r="Y41" s="9">
+      <c r="X41" s="12">
+        <f t="shared" si="4"/>
+        <v>11.639941374429478</v>
+      </c>
+      <c r="Y41" s="8">
+        <f t="shared" si="8"/>
+        <v>168.15020672486403</v>
+      </c>
+      <c r="Z41" s="9">
         <f t="shared" si="17"/>
-        <v>4.0073296126186646E-2</v>
-      </c>
-      <c r="Z41" s="8">
+        <v>4.3053617043441225E-2</v>
+      </c>
+      <c r="AA41" s="8">
         <f t="shared" si="18"/>
-        <v>3749.0897346495653</v>
-      </c>
-    </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
+        <v>3737.449793275136</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>1</v>
       </c>
@@ -4617,20 +4791,24 @@
         <f t="shared" si="12"/>
         <v>16.8215</v>
       </c>
-      <c r="X42" s="8">
-        <f t="shared" si="5"/>
-        <v>166.52855652070429</v>
-      </c>
-      <c r="Y42" s="9">
+      <c r="X42" s="12">
+        <f t="shared" si="4"/>
+        <v>12.384647301073084</v>
+      </c>
+      <c r="Y42" s="8">
+        <f t="shared" si="8"/>
+        <v>178.91320382177736</v>
+      </c>
+      <c r="Z42" s="9">
         <f t="shared" si="17"/>
-        <v>3.9894341609659316E-2</v>
-      </c>
-      <c r="Z42" s="8">
+        <v>4.2861264283265303E-2</v>
+      </c>
+      <c r="AA42" s="8">
         <f t="shared" si="18"/>
-        <v>4007.7114434792957</v>
-      </c>
-    </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
+        <v>3995.3267961782226</v>
+      </c>
+    </row>
+    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>1</v>
       </c>
@@ -4702,20 +4880,24 @@
         <f t="shared" si="12"/>
         <v>10.752500000000001</v>
       </c>
-      <c r="X43" s="8">
-        <f t="shared" si="5"/>
-        <v>106.43880949908586</v>
-      </c>
-      <c r="Y43" s="9">
+      <c r="X43" s="12">
+        <f t="shared" si="4"/>
+        <v>7.9164117412114452</v>
+      </c>
+      <c r="Y43" s="8">
+        <f t="shared" si="8"/>
+        <v>114.35522124029731</v>
+      </c>
+      <c r="Z43" s="9">
         <f t="shared" si="17"/>
-        <v>4.0352886794967534E-2</v>
-      </c>
-      <c r="Z43" s="8">
+        <v>4.3354142336238889E-2</v>
+      </c>
+      <c r="AA43" s="8">
         <f t="shared" si="18"/>
-        <v>2531.2611905009139</v>
-      </c>
-    </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
+        <v>2523.3447787597024</v>
+      </c>
+    </row>
+    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>1</v>
       </c>
@@ -4787,20 +4969,24 @@
         <f t="shared" si="12"/>
         <v>20.91</v>
       </c>
-      <c r="X44" s="8">
-        <f t="shared" si="5"/>
-        <v>206.9974477215425</v>
-      </c>
-      <c r="Y44" s="9">
+      <c r="X44" s="12">
+        <f t="shared" si="4"/>
+        <v>15.394761172632535</v>
+      </c>
+      <c r="Y44" s="8">
+        <f t="shared" si="8"/>
+        <v>222.39220889417504</v>
+      </c>
+      <c r="Z44" s="9">
         <f t="shared" si="17"/>
-        <v>0.11920382823008494</v>
-      </c>
-      <c r="Z44" s="8">
+        <v>0.12806922481668589</v>
+      </c>
+      <c r="AA44" s="8">
         <f t="shared" si="18"/>
-        <v>1529.5025522784574</v>
-      </c>
-    </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
+        <v>1514.1077911058251</v>
+      </c>
+    </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>1</v>
       </c>
@@ -4862,20 +5048,23 @@
         <v>0.21161742326356014</v>
       </c>
       <c r="V45" s="8"/>
-      <c r="X45" s="8">
-        <f t="shared" si="5"/>
-        <v>10.157636316650887</v>
-      </c>
-      <c r="Y45" s="9">
+      <c r="X45" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="9">
         <f t="shared" si="17"/>
-        <v>2.5313088907124422E-2</v>
-      </c>
-      <c r="Z45" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="8">
         <f t="shared" si="18"/>
-        <v>391.12236368334908</v>
-      </c>
-    </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
+        <v>401.28</v>
+      </c>
+    </row>
+    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>1</v>
       </c>
@@ -4937,20 +5126,23 @@
         <v>0.21161742326356012</v>
       </c>
       <c r="V46" s="8"/>
-      <c r="X46" s="8">
-        <f t="shared" si="5"/>
-        <v>63.485226979068038</v>
-      </c>
-      <c r="Y46" s="9">
+      <c r="X46" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="9">
         <f t="shared" si="17"/>
-        <v>2.5313088907124418E-2</v>
-      </c>
-      <c r="Z46" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="8">
         <f t="shared" si="18"/>
-        <v>2444.5147730209319</v>
-      </c>
-    </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2</v>
       </c>
@@ -5019,20 +5211,24 @@
         <f>H47*0.17</f>
         <v>25.287500000000001</v>
       </c>
-      <c r="X47" s="8">
-        <f t="shared" si="5"/>
-        <v>708.00054580940332</v>
-      </c>
-      <c r="Y47" s="9">
+      <c r="X47" s="12">
+        <f t="shared" si="4"/>
+        <v>18.617648166090159</v>
+      </c>
+      <c r="Y47" s="8">
+        <f t="shared" si="8"/>
+        <v>726.61819397549345</v>
+      </c>
+      <c r="Z47" s="9">
         <f t="shared" si="17"/>
-        <v>0.10564964720944928</v>
-      </c>
-      <c r="Z47" s="8">
+        <v>0.10842782015332519</v>
+      </c>
+      <c r="AA47" s="8">
         <f t="shared" si="18"/>
-        <v>5993.3994541905959</v>
-      </c>
-    </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
+        <v>5974.7818060245063</v>
+      </c>
+    </row>
+    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2</v>
       </c>
@@ -5101,20 +5297,24 @@
         <f>H48*0.17</f>
         <v>10.115</v>
       </c>
-      <c r="X48" s="8">
-        <f t="shared" si="5"/>
-        <v>279.26901832376143</v>
-      </c>
-      <c r="Y48" s="9">
+      <c r="X48" s="12">
+        <f t="shared" si="4"/>
+        <v>7.4470592664360629</v>
+      </c>
+      <c r="Y48" s="8">
+        <f t="shared" si="8"/>
+        <v>286.71607759019747</v>
+      </c>
+      <c r="Z48" s="9">
         <f t="shared" si="17"/>
-        <v>0.10641252031845809</v>
-      </c>
-      <c r="Z48" s="8">
+        <v>0.10925014387677087</v>
+      </c>
+      <c r="AA48" s="8">
         <f t="shared" si="18"/>
-        <v>2345.1309816762387</v>
-      </c>
-    </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
+        <v>2337.6839224098026</v>
+      </c>
+    </row>
+    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2</v>
       </c>
@@ -5186,20 +5386,24 @@
         <f>H49*0.17</f>
         <v>24.786000000000005</v>
       </c>
-      <c r="X49" s="8">
-        <f t="shared" si="5"/>
-        <v>245.36770632358451</v>
-      </c>
-      <c r="Y49" s="9">
+      <c r="X49" s="12">
+        <f t="shared" si="4"/>
+        <v>18.248424219266859</v>
+      </c>
+      <c r="Y49" s="8">
+        <f t="shared" si="8"/>
+        <v>263.61613054285135</v>
+      </c>
+      <c r="Z49" s="9">
         <f t="shared" si="17"/>
-        <v>4.3155839877372128E-2</v>
-      </c>
-      <c r="Z49" s="8">
+        <v>4.6365414949091105E-2</v>
+      </c>
+      <c r="AA49" s="8">
         <f t="shared" si="18"/>
-        <v>5440.2522936764153</v>
-      </c>
-    </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
+        <v>5422.0038694571485</v>
+      </c>
+    </row>
+    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2</v>
       </c>
@@ -5271,20 +5475,24 @@
         <f>H50*0.17</f>
         <v>37.765500000000003</v>
       </c>
-      <c r="X50" s="8">
-        <f t="shared" si="5"/>
-        <v>373.86258545805413</v>
-      </c>
-      <c r="Y50" s="9">
+      <c r="X50" s="12">
+        <f t="shared" si="4"/>
+        <v>27.804440605693635</v>
+      </c>
+      <c r="Y50" s="8">
+        <f t="shared" si="8"/>
+        <v>401.66702606374776</v>
+      </c>
+      <c r="Z50" s="9">
         <f t="shared" si="17"/>
-        <v>3.6864224265974938E-2</v>
-      </c>
-      <c r="Z50" s="8">
+        <v>3.960584424600707E-2</v>
+      </c>
+      <c r="AA50" s="8">
         <f t="shared" si="18"/>
-        <v>9767.7474145419474</v>
-      </c>
-    </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
+        <v>9739.9429739362531</v>
+      </c>
+    </row>
+    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2</v>
       </c>
@@ -5356,20 +5564,24 @@
         <f>H51*0.17</f>
         <v>20.23</v>
       </c>
-      <c r="X51" s="8">
-        <f t="shared" si="5"/>
-        <v>200.26582340539474</v>
-      </c>
-      <c r="Y51" s="9">
+      <c r="X51" s="12">
+        <f t="shared" si="4"/>
+        <v>14.894118532872126</v>
+      </c>
+      <c r="Y51" s="8">
+        <f t="shared" si="8"/>
+        <v>215.15994193826685</v>
+      </c>
+      <c r="Z51" s="9">
         <f t="shared" si="17"/>
-        <v>3.5926631757421515E-2</v>
-      </c>
-      <c r="Z51" s="8">
+        <v>3.8598558014148299E-2</v>
+      </c>
+      <c r="AA51" s="8">
         <f t="shared" si="18"/>
-        <v>5374.034176594605</v>
-      </c>
-    </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
+        <v>5359.1400580617337</v>
+      </c>
+    </row>
+    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>1</v>
       </c>
@@ -5431,20 +5643,23 @@
         <v>0.22928130732032681</v>
       </c>
       <c r="V52" s="8"/>
-      <c r="X52" s="8">
-        <f t="shared" si="5"/>
-        <v>1100</v>
-      </c>
-      <c r="Y52" s="9">
+      <c r="X52" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="9">
         <f t="shared" si="17"/>
-        <v>2.8102230806176357E-2</v>
-      </c>
-      <c r="Z52" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="8">
         <f t="shared" si="18"/>
-        <v>38042.800000000003</v>
-      </c>
-    </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
+        <v>39142.800000000003</v>
+      </c>
+    </row>
+    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>1</v>
       </c>
@@ -5516,20 +5731,24 @@
         <f t="shared" ref="W53:W68" si="23">H53*0.17</f>
         <v>16.447500000000002</v>
       </c>
-      <c r="X53" s="8">
-        <f t="shared" si="5"/>
-        <v>162.82616314682303</v>
-      </c>
-      <c r="Y53" s="9">
+      <c r="X53" s="12">
+        <f t="shared" si="4"/>
+        <v>12.10929384920486</v>
+      </c>
+      <c r="Y53" s="8">
+        <f t="shared" si="8"/>
+        <v>174.93545699602788</v>
+      </c>
+      <c r="Z53" s="9">
         <f t="shared" si="17"/>
-        <v>4.0630358863836064E-2</v>
-      </c>
-      <c r="Z53" s="8">
+        <v>4.3652016717661356E-2</v>
+      </c>
+      <c r="AA53" s="8">
         <f t="shared" si="18"/>
-        <v>3844.6738368531769</v>
-      </c>
-    </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
+        <v>3832.5645430039722</v>
+      </c>
+    </row>
+    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>1</v>
       </c>
@@ -5601,20 +5820,24 @@
         <f t="shared" si="23"/>
         <v>10.752500000000001</v>
       </c>
-      <c r="X54" s="8">
-        <f t="shared" si="5"/>
-        <v>106.43880949908586</v>
-      </c>
-      <c r="Y54" s="9">
+      <c r="X54" s="12">
+        <f t="shared" si="4"/>
+        <v>7.9164117412114452</v>
+      </c>
+      <c r="Y54" s="8">
+        <f t="shared" si="8"/>
+        <v>114.35522124029731</v>
+      </c>
+      <c r="Z54" s="9">
         <f t="shared" si="17"/>
-        <v>4.0161799641198329E-2</v>
-      </c>
-      <c r="Z54" s="8">
+        <v>4.3148843030015024E-2</v>
+      </c>
+      <c r="AA54" s="8">
         <f t="shared" si="18"/>
-        <v>2543.8111905009141</v>
-      </c>
-    </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.25">
+        <v>2535.8947787597026</v>
+      </c>
+    </row>
+    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>1</v>
       </c>
@@ -5686,20 +5909,24 @@
         <f t="shared" si="23"/>
         <v>7.718</v>
       </c>
-      <c r="X55" s="8">
-        <f t="shared" si="5"/>
-        <v>76.403935988276658</v>
-      </c>
-      <c r="Y55" s="9">
+      <c r="X55" s="12">
+        <f t="shared" si="4"/>
+        <v>5.6822939612806254</v>
+      </c>
+      <c r="Y55" s="8">
+        <f t="shared" si="8"/>
+        <v>82.086229949557278</v>
+      </c>
+      <c r="Z55" s="9">
         <f t="shared" si="17"/>
-        <v>4.0706214297734987E-2</v>
-      </c>
-      <c r="Z55" s="8">
+        <v>4.373360644316196E-2</v>
+      </c>
+      <c r="AA55" s="8">
         <f t="shared" si="18"/>
-        <v>1800.5560640117233</v>
-      </c>
-    </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
+        <v>1794.8737700504428</v>
+      </c>
+    </row>
+    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>1</v>
       </c>
@@ -5771,20 +5998,24 @@
         <f t="shared" si="23"/>
         <v>25.925000000000001</v>
       </c>
-      <c r="X56" s="8">
-        <f t="shared" si="5"/>
-        <v>256.64317705313192</v>
-      </c>
-      <c r="Y56" s="9">
+      <c r="X56" s="12">
+        <f t="shared" si="4"/>
+        <v>19.08700064086554</v>
+      </c>
+      <c r="Y56" s="8">
+        <f t="shared" si="8"/>
+        <v>275.73017769399746</v>
+      </c>
+      <c r="Z56" s="9">
         <f t="shared" si="17"/>
-        <v>3.9688112124508144E-2</v>
-      </c>
-      <c r="Z56" s="8">
+        <v>4.2639786235830431E-2</v>
+      </c>
+      <c r="AA56" s="8">
         <f t="shared" si="18"/>
-        <v>6209.8568229468683</v>
-      </c>
-    </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.25">
+        <v>6190.7698223060024</v>
+      </c>
+    </row>
+    <row r="57" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>1</v>
       </c>
@@ -5856,20 +6087,24 @@
         <f t="shared" si="23"/>
         <v>10.752500000000001</v>
       </c>
-      <c r="X57" s="8">
-        <f t="shared" si="5"/>
-        <v>106.43880949908586</v>
-      </c>
-      <c r="Y57" s="9">
+      <c r="X57" s="12">
+        <f t="shared" si="4"/>
+        <v>7.9164117412114452</v>
+      </c>
+      <c r="Y57" s="8">
+        <f t="shared" si="8"/>
+        <v>114.35522124029731</v>
+      </c>
+      <c r="Z57" s="9">
         <f t="shared" si="17"/>
-        <v>4.0161799641198329E-2</v>
-      </c>
-      <c r="Z57" s="8">
+        <v>4.3148843030015024E-2</v>
+      </c>
+      <c r="AA57" s="8">
         <f t="shared" si="18"/>
-        <v>2543.8111905009141</v>
-      </c>
-    </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
+        <v>2535.8947787597026</v>
+      </c>
+    </row>
+    <row r="58" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>1</v>
       </c>
@@ -5941,20 +6176,24 @@
         <f t="shared" si="23"/>
         <v>15.555000000000001</v>
       </c>
-      <c r="X58" s="8">
-        <f t="shared" si="5"/>
-        <v>153.98590623187917</v>
-      </c>
-      <c r="Y58" s="9">
+      <c r="X58" s="12">
+        <f t="shared" si="4"/>
+        <v>11.452200384519324</v>
+      </c>
+      <c r="Y58" s="8">
+        <f t="shared" si="8"/>
+        <v>165.4381066163985</v>
+      </c>
+      <c r="Z58" s="9">
         <f t="shared" si="17"/>
-        <v>3.9688112124508151E-2</v>
-      </c>
-      <c r="Z58" s="8">
+        <v>4.2639786235830431E-2</v>
+      </c>
+      <c r="AA58" s="8">
         <f t="shared" si="18"/>
-        <v>3725.9140937681209</v>
-      </c>
-    </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.25">
+        <v>3714.4618933836018</v>
+      </c>
+    </row>
+    <row r="59" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>1</v>
       </c>
@@ -6026,20 +6265,24 @@
         <f t="shared" si="23"/>
         <v>10.752500000000001</v>
       </c>
-      <c r="X59" s="8">
-        <f t="shared" si="5"/>
-        <v>106.43880949908586</v>
-      </c>
-      <c r="Y59" s="9">
+      <c r="X59" s="12">
+        <f t="shared" si="4"/>
+        <v>7.9164117412114452</v>
+      </c>
+      <c r="Y59" s="8">
+        <f t="shared" si="8"/>
+        <v>114.35522124029731</v>
+      </c>
+      <c r="Z59" s="9">
         <f t="shared" si="17"/>
-        <v>4.0352886794967534E-2</v>
-      </c>
-      <c r="Z59" s="8">
+        <v>4.3354142336238889E-2</v>
+      </c>
+      <c r="AA59" s="8">
         <f t="shared" si="18"/>
-        <v>2531.2611905009139</v>
-      </c>
-    </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.25">
+        <v>2523.3447787597024</v>
+      </c>
+    </row>
+    <row r="60" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>1</v>
       </c>
@@ -6111,20 +6354,24 @@
         <f t="shared" si="23"/>
         <v>5.6950000000000003</v>
       </c>
-      <c r="X60" s="8">
-        <f t="shared" si="5"/>
-        <v>56.377353647737174</v>
-      </c>
-      <c r="Y60" s="9">
+      <c r="X60" s="12">
+        <f t="shared" si="4"/>
+        <v>4.1928821079934133</v>
+      </c>
+      <c r="Y60" s="8">
+        <f t="shared" si="8"/>
+        <v>60.570235755730586</v>
+      </c>
+      <c r="Z60" s="9">
         <f t="shared" si="17"/>
-        <v>4.1157361401472609E-2</v>
-      </c>
-      <c r="Z60" s="8">
+        <v>4.4218306143765942E-2</v>
+      </c>
+      <c r="AA60" s="8">
         <f t="shared" si="18"/>
-        <v>1313.4226463522627</v>
-      </c>
-    </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.25">
+        <v>1309.2297642442693</v>
+      </c>
+    </row>
+    <row r="61" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>1</v>
       </c>
@@ -6196,20 +6443,24 @@
         <f t="shared" si="23"/>
         <v>16.447500000000002</v>
       </c>
-      <c r="X61" s="8">
-        <f t="shared" si="5"/>
-        <v>162.82616314682303</v>
-      </c>
-      <c r="Y61" s="9">
+      <c r="X61" s="12">
+        <f t="shared" si="4"/>
+        <v>12.10929384920486</v>
+      </c>
+      <c r="Y61" s="8">
+        <f t="shared" si="8"/>
+        <v>174.93545699602788</v>
+      </c>
+      <c r="Z61" s="9">
         <f t="shared" si="17"/>
-        <v>4.0630358863836064E-2</v>
-      </c>
-      <c r="Z61" s="8">
+        <v>4.3652016717661356E-2</v>
+      </c>
+      <c r="AA61" s="8">
         <f t="shared" si="18"/>
-        <v>3844.6738368531769</v>
-      </c>
-    </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.25">
+        <v>3832.5645430039722</v>
+      </c>
+    </row>
+    <row r="62" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>1</v>
       </c>
@@ -6281,20 +6532,24 @@
         <f t="shared" si="23"/>
         <v>12.9625</v>
       </c>
-      <c r="X62" s="8">
-        <f t="shared" si="5"/>
-        <v>128.31658852656597</v>
-      </c>
-      <c r="Y62" s="9">
+      <c r="X62" s="12">
+        <f t="shared" si="4"/>
+        <v>9.54350032043277</v>
+      </c>
+      <c r="Y62" s="8">
+        <f t="shared" si="8"/>
+        <v>137.86008884699874</v>
+      </c>
+      <c r="Z62" s="9">
         <f t="shared" si="17"/>
-        <v>3.9686565692899085E-2</v>
-      </c>
-      <c r="Z62" s="8">
+        <v>4.2638239804221365E-2</v>
+      </c>
+      <c r="AA62" s="8">
         <f t="shared" si="18"/>
-        <v>3104.9334114734338</v>
-      </c>
-    </row>
-    <row r="63" spans="1:26" x14ac:dyDescent="0.25">
+        <v>3095.3899111530013</v>
+      </c>
+    </row>
+    <row r="63" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>1</v>
       </c>
@@ -6366,20 +6621,24 @@
         <f t="shared" si="23"/>
         <v>73.355000000000004</v>
       </c>
-      <c r="X63" s="8">
-        <f t="shared" si="5"/>
-        <v>726.17397310443573</v>
-      </c>
-      <c r="Y63" s="9">
+      <c r="X63" s="12">
+        <f t="shared" si="4"/>
+        <v>54.006824764153968</v>
+      </c>
+      <c r="Y63" s="8">
+        <f t="shared" si="8"/>
+        <v>780.18079786858971</v>
+      </c>
+      <c r="Z63" s="9">
         <f t="shared" si="17"/>
-        <v>3.9771612999048987E-2</v>
-      </c>
-      <c r="Z63" s="8">
+        <v>4.2729497216029144E-2</v>
+      </c>
+      <c r="AA63" s="8">
         <f t="shared" si="18"/>
-        <v>17532.426026895562</v>
-      </c>
-    </row>
-    <row r="64" spans="1:26" x14ac:dyDescent="0.25">
+        <v>17478.419202131408</v>
+      </c>
+    </row>
+    <row r="64" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>1</v>
       </c>
@@ -6451,20 +6710,24 @@
         <f t="shared" si="23"/>
         <v>15.81</v>
       </c>
-      <c r="X64" s="8">
-        <f t="shared" si="5"/>
-        <v>156.51026535043457</v>
-      </c>
-      <c r="Y64" s="9">
+      <c r="X64" s="12">
+        <f t="shared" si="4"/>
+        <v>11.639941374429478</v>
+      </c>
+      <c r="Y64" s="8">
+        <f t="shared" si="8"/>
+        <v>168.15020672486403</v>
+      </c>
+      <c r="Z64" s="9">
         <f t="shared" si="17"/>
-        <v>3.9817402841843583E-2</v>
-      </c>
-      <c r="Z64" s="8">
+        <v>4.2778692529285886E-2</v>
+      </c>
+      <c r="AA64" s="8">
         <f t="shared" si="18"/>
-        <v>3774.1897346495653</v>
-      </c>
-    </row>
-    <row r="65" spans="1:26" x14ac:dyDescent="0.25">
+        <v>3762.5497932751359</v>
+      </c>
+    </row>
+    <row r="65" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>1</v>
       </c>
@@ -6536,20 +6799,24 @@
         <f t="shared" si="23"/>
         <v>16.005500000000001</v>
       </c>
-      <c r="X65" s="8">
-        <f t="shared" si="5"/>
-        <v>158.45060734132704</v>
-      </c>
-      <c r="Y65" s="9">
+      <c r="X65" s="12">
+        <f t="shared" si="4"/>
+        <v>11.783876133360595</v>
+      </c>
+      <c r="Y65" s="8">
+        <f t="shared" si="8"/>
+        <v>170.23448347468764</v>
+      </c>
+      <c r="Z65" s="9">
         <f t="shared" si="17"/>
-        <v>4.0145279328826972E-2</v>
-      </c>
-      <c r="Z65" s="8">
+        <v>4.3130859547721306E-2</v>
+      </c>
+      <c r="AA65" s="8">
         <f t="shared" si="18"/>
-        <v>3788.4793926586726</v>
-      </c>
-    </row>
-    <row r="66" spans="1:26" x14ac:dyDescent="0.25">
+        <v>3776.6955165253121</v>
+      </c>
+    </row>
+    <row r="66" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>1</v>
       </c>
@@ -6621,20 +6888,24 @@
         <f t="shared" si="23"/>
         <v>25.925000000000001</v>
       </c>
-      <c r="X66" s="8">
-        <f t="shared" si="5"/>
-        <v>256.64317705313192</v>
-      </c>
-      <c r="Y66" s="9">
-        <f t="shared" ref="Y66:Y97" si="27">X66/J66</f>
-        <v>3.9688112124508144E-2</v>
-      </c>
-      <c r="Z66" s="8">
-        <f t="shared" ref="Z66:Z97" si="28">J66-X66</f>
-        <v>6209.8568229468683</v>
-      </c>
-    </row>
-    <row r="67" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="X66" s="12">
+        <f t="shared" si="4"/>
+        <v>19.08700064086554</v>
+      </c>
+      <c r="Y66" s="8">
+        <f t="shared" si="8"/>
+        <v>275.73017769399746</v>
+      </c>
+      <c r="Z66" s="9">
+        <f t="shared" ref="Z66:Z97" si="27">Y66/J66</f>
+        <v>4.2639786235830431E-2</v>
+      </c>
+      <c r="AA66" s="8">
+        <f t="shared" ref="AA66:AA97" si="28">J66-Y66</f>
+        <v>6190.7698223060024</v>
+      </c>
+    </row>
+    <row r="67" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>2</v>
       </c>
@@ -6704,20 +6975,24 @@
         <f t="shared" si="23"/>
         <v>25.287500000000001</v>
       </c>
-      <c r="X67" s="8">
-        <f t="shared" ref="X67:X130" si="29">S67+V67+W67</f>
-        <v>250.33227925674342</v>
-      </c>
-      <c r="Y67" s="9">
+      <c r="X67" s="12">
+        <f t="shared" ref="X67:X130" si="29">IFERROR(IF(D67="TRANSFERENCIA",0,H67*(SUMIF(D:D,"TRANSFERENCIA",M:M)+SUMIF(D:D,"TRANSFERENCIA",O:O))/(SUMIF(D:D,"BONIFICAÇÃO",H:H)+SUMIF(D:D,"VENDA",H:H))),0)</f>
+        <v>18.617648166090159</v>
+      </c>
+      <c r="Y67" s="8">
+        <f t="shared" ref="Y67:Y130" si="30">S67+V67+W67+X67</f>
+        <v>268.94992742283358</v>
+      </c>
+      <c r="Z67" s="9">
         <f t="shared" si="27"/>
-        <v>4.6144198941335195E-2</v>
-      </c>
-      <c r="Z67" s="8">
+        <v>4.9576023488079921E-2</v>
+      </c>
+      <c r="AA67" s="8">
         <f t="shared" si="28"/>
-        <v>5174.6677207432567</v>
-      </c>
-    </row>
-    <row r="68" spans="1:26" x14ac:dyDescent="0.25">
+        <v>5156.0500725771662</v>
+      </c>
+    </row>
+    <row r="68" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>1</v>
       </c>
@@ -6789,20 +7064,24 @@
         <f t="shared" si="23"/>
         <v>10.4975</v>
       </c>
-      <c r="X68" s="8">
+      <c r="X68" s="12">
         <f t="shared" si="29"/>
-        <v>103.91945038053048</v>
-      </c>
-      <c r="Y68" s="9">
+        <v>7.7286707513012924</v>
+      </c>
+      <c r="Y68" s="8">
+        <f t="shared" si="30"/>
+        <v>111.64812113183177</v>
+      </c>
+      <c r="Z68" s="9">
         <f t="shared" si="27"/>
-        <v>0.53511560443115591</v>
-      </c>
-      <c r="Z68" s="8">
+        <v>0.57491308512786699</v>
+      </c>
+      <c r="AA68" s="8">
         <f t="shared" si="28"/>
-        <v>90.280549619469511</v>
-      </c>
-    </row>
-    <row r="69" spans="1:26" x14ac:dyDescent="0.25">
+        <v>82.551878868168217</v>
+      </c>
+    </row>
+    <row r="69" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>2</v>
       </c>
@@ -6867,20 +7146,24 @@
       <c r="W69" s="4">
         <v>0</v>
       </c>
-      <c r="X69" s="8">
+      <c r="X69" s="12">
         <f t="shared" si="29"/>
-        <v>1055.5108115206187</v>
-      </c>
-      <c r="Y69" s="9">
+        <v>685.94299680172844</v>
+      </c>
+      <c r="Y69" s="8">
+        <f t="shared" si="30"/>
+        <v>1741.4538083223472</v>
+      </c>
+      <c r="Z69" s="9">
         <f t="shared" si="27"/>
-        <v>1.7510132905119755E-2</v>
-      </c>
-      <c r="Z69" s="8">
+        <v>2.8889412878605625E-2</v>
+      </c>
+      <c r="AA69" s="8">
         <f t="shared" si="28"/>
-        <v>59224.489188479383</v>
-      </c>
-    </row>
-    <row r="70" spans="1:26" x14ac:dyDescent="0.25">
+        <v>58538.546191677655</v>
+      </c>
+    </row>
+    <row r="70" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>2</v>
       </c>
@@ -6945,20 +7228,24 @@
       <c r="W70" s="4">
         <v>0</v>
       </c>
-      <c r="X70" s="8">
+      <c r="X70" s="12">
         <f t="shared" si="29"/>
-        <v>44.489188479383806</v>
-      </c>
-      <c r="Y70" s="9">
+        <v>28.91211244616354</v>
+      </c>
+      <c r="Y70" s="8">
+        <f t="shared" si="30"/>
+        <v>73.401300925547346</v>
+      </c>
+      <c r="Z70" s="9">
         <f t="shared" si="27"/>
-        <v>1.4669828363960764E-2</v>
-      </c>
-      <c r="Z70" s="8">
+        <v>2.4203284507385285E-2</v>
+      </c>
+      <c r="AA70" s="8">
         <f t="shared" si="28"/>
-        <v>2988.2108115206161</v>
-      </c>
-    </row>
-    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
+        <v>2959.2986990744525</v>
+      </c>
+    </row>
+    <row r="71" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>1</v>
       </c>
@@ -7020,20 +7307,23 @@
         <v>0.2141911363813381</v>
       </c>
       <c r="V71" s="8"/>
-      <c r="X71" s="8">
+      <c r="X71" s="12">
         <f t="shared" si="29"/>
-        <v>1100</v>
-      </c>
-      <c r="Y71" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="9">
         <f t="shared" si="27"/>
-        <v>2.6328972856504464E-2</v>
-      </c>
-      <c r="Z71" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="8">
         <f t="shared" si="28"/>
-        <v>40679.07</v>
-      </c>
-    </row>
-    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
+        <v>41779.07</v>
+      </c>
+    </row>
+    <row r="72" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>1</v>
       </c>
@@ -7074,7 +7364,7 @@
         <v>122.39500000000001</v>
       </c>
       <c r="P72" s="7">
-        <f t="shared" ref="P72:P95" si="30">0.0768385441837987*H72</f>
+        <f t="shared" ref="P72:P95" si="31">0.0768385441837987*H72</f>
         <v>7.2343489349046477</v>
       </c>
       <c r="Q72" t="s">
@@ -7096,27 +7386,31 @@
         <v>1.4697205094660393</v>
       </c>
       <c r="V72" s="8">
-        <f t="shared" ref="V72:V98" si="31">H72*0.136067534853132</f>
+        <f t="shared" ref="V72:V98" si="32">H72*0.136067534853132</f>
         <v>12.810758406422378</v>
       </c>
       <c r="W72" s="4">
-        <f t="shared" ref="W72:W98" si="32">H72*0.17</f>
+        <f t="shared" ref="W72:W98" si="33">H72*0.17</f>
         <v>16.005500000000001</v>
       </c>
-      <c r="X72" s="8">
+      <c r="X72" s="12">
         <f t="shared" si="29"/>
-        <v>158.44560734132705</v>
-      </c>
-      <c r="Y72" s="9">
+        <v>11.783876133360595</v>
+      </c>
+      <c r="Y72" s="8">
+        <f t="shared" si="30"/>
+        <v>170.22948347468764</v>
+      </c>
+      <c r="Z72" s="9">
         <f t="shared" si="27"/>
-        <v>4.0144012521460236E-2</v>
-      </c>
-      <c r="Z72" s="8">
+        <v>4.3129592740354564E-2</v>
+      </c>
+      <c r="AA72" s="8">
         <f t="shared" si="28"/>
-        <v>3788.4843926586727</v>
-      </c>
-    </row>
-    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
+        <v>3776.7005165253122</v>
+      </c>
+    </row>
+    <row r="73" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>2</v>
       </c>
@@ -7159,7 +7453,7 @@
         <v>353.27500000000003</v>
       </c>
       <c r="P73" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>20.880874381947294</v>
       </c>
       <c r="Q73" t="s">
@@ -7181,27 +7475,31 @@
         <v>1.4615463843044818</v>
       </c>
       <c r="V73" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>36.976352596338621</v>
       </c>
       <c r="W73" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>46.197500000000005</v>
       </c>
-      <c r="X73" s="8">
+      <c r="X73" s="12">
         <f t="shared" si="29"/>
-        <v>457.32972697828598</v>
-      </c>
-      <c r="Y73" s="9">
+        <v>34.012409338722691</v>
+      </c>
+      <c r="Y73" s="8">
+        <f t="shared" si="30"/>
+        <v>491.34213631700868</v>
+      </c>
+      <c r="Z73" s="9">
         <f t="shared" si="27"/>
-        <v>3.8599414841053496E-2</v>
-      </c>
-      <c r="Z73" s="8">
+        <v>4.14701206368117E-2</v>
+      </c>
+      <c r="AA73" s="8">
         <f t="shared" si="28"/>
-        <v>11390.770273021715</v>
-      </c>
-    </row>
-    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
+        <v>11356.757863682991</v>
+      </c>
+    </row>
+    <row r="74" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>2</v>
       </c>
@@ -7244,7 +7542,7 @@
         <v>253.82500000000002</v>
       </c>
       <c r="P74" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>15.002725751886695</v>
       </c>
       <c r="Q74" t="s">
@@ -7266,27 +7564,31 @@
         <v>1.4690039658573044</v>
       </c>
       <c r="V74" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>26.567186180074025</v>
       </c>
       <c r="W74" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>33.192500000000003</v>
       </c>
-      <c r="X74" s="8">
+      <c r="X74" s="12">
         <f t="shared" si="29"/>
-        <v>328.58741193196073</v>
-      </c>
-      <c r="Y74" s="9">
+        <v>24.437618853304897</v>
+      </c>
+      <c r="Y74" s="8">
+        <f t="shared" si="30"/>
+        <v>353.02503078526564</v>
+      </c>
+      <c r="Z74" s="9">
         <f t="shared" si="27"/>
-        <v>4.2126591273328295E-2</v>
-      </c>
-      <c r="Z74" s="8">
+        <v>4.525961933144431E-2</v>
+      </c>
+      <c r="AA74" s="8">
         <f t="shared" si="28"/>
-        <v>7471.4125880680394</v>
-      </c>
-    </row>
-    <row r="75" spans="1:26" x14ac:dyDescent="0.25">
+        <v>7446.9749692147343</v>
+      </c>
+    </row>
+    <row r="75" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>2</v>
       </c>
@@ -7329,7 +7631,7 @@
         <v>321.75</v>
       </c>
       <c r="P75" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>19.017539685490178</v>
       </c>
       <c r="Q75" t="s">
@@ -7351,27 +7653,31 @@
         <v>1.481597998632566</v>
       </c>
       <c r="V75" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>33.676714876150172</v>
       </c>
       <c r="W75" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>42.075000000000003</v>
       </c>
-      <c r="X75" s="8">
+      <c r="X75" s="12">
         <f t="shared" si="29"/>
-        <v>416.51925456164037</v>
-      </c>
-      <c r="Y75" s="9">
+        <v>30.97726333517522</v>
+      </c>
+      <c r="Y75" s="8">
+        <f t="shared" si="30"/>
+        <v>447.49651789681559</v>
+      </c>
+      <c r="Z75" s="9">
         <f t="shared" si="27"/>
-        <v>4.1610315141023015E-2</v>
-      </c>
-      <c r="Z75" s="8">
+        <v>4.4704946842838718E-2</v>
+      </c>
+      <c r="AA75" s="8">
         <f t="shared" si="28"/>
-        <v>9593.480745438359</v>
-      </c>
-    </row>
-    <row r="76" spans="1:26" x14ac:dyDescent="0.25">
+        <v>9562.5034821031841</v>
+      </c>
+    </row>
+    <row r="76" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>2</v>
       </c>
@@ -7414,7 +7720,7 @@
         <v>154.70000000000002</v>
       </c>
       <c r="P76" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>9.1437867578720446</v>
       </c>
       <c r="Q76" t="s">
@@ -7436,27 +7742,31 @@
         <v>1.4628909531952863</v>
       </c>
       <c r="V76" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>16.192036647522709</v>
       </c>
       <c r="W76" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>20.23</v>
       </c>
-      <c r="X76" s="8">
+      <c r="X76" s="12">
         <f t="shared" si="29"/>
-        <v>200.26582340539477</v>
-      </c>
-      <c r="Y76" s="9">
+        <v>14.894118532872126</v>
+      </c>
+      <c r="Y76" s="8">
+        <f t="shared" si="30"/>
+        <v>215.15994193826688</v>
+      </c>
+      <c r="Z76" s="9">
         <f t="shared" si="27"/>
-        <v>4.0609515037087048E-2</v>
-      </c>
-      <c r="Z76" s="8">
+        <v>4.3629715489864523E-2</v>
+      </c>
+      <c r="AA76" s="8">
         <f t="shared" si="28"/>
-        <v>4731.2341765946048</v>
-      </c>
-    </row>
-    <row r="77" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4716.3400580617335</v>
+      </c>
+    </row>
+    <row r="77" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>2</v>
       </c>
@@ -7499,7 +7809,7 @@
         <v>214.76</v>
       </c>
       <c r="P77" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>12.693727499163543</v>
       </c>
       <c r="Q77" t="s">
@@ -7521,27 +7831,31 @@
         <v>1.476972256488075</v>
       </c>
       <c r="V77" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>22.478356757737405</v>
       </c>
       <c r="W77" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>28.084</v>
       </c>
-      <c r="X77" s="8">
+      <c r="X77" s="12">
         <f t="shared" si="29"/>
-        <v>278.01608425690091</v>
-      </c>
-      <c r="Y77" s="9">
+        <v>20.676541022104836</v>
+      </c>
+      <c r="Y77" s="8">
+        <f t="shared" si="30"/>
+        <v>298.69262527900577</v>
+      </c>
+      <c r="Z77" s="9">
         <f t="shared" si="27"/>
-        <v>4.0920824883264782E-2</v>
-      </c>
-      <c r="Z77" s="8">
+        <v>4.396417799219985E-2</v>
+      </c>
+      <c r="AA77" s="8">
         <f t="shared" si="28"/>
-        <v>6515.9839157430988</v>
-      </c>
-    </row>
-    <row r="78" spans="1:26" x14ac:dyDescent="0.25">
+        <v>6495.3073747209946</v>
+      </c>
+    </row>
+    <row r="78" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>2</v>
       </c>
@@ -7584,7 +7898,7 @@
         <v>198.57500000000002</v>
       </c>
       <c r="P78" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>11.737087624075251</v>
       </c>
       <c r="Q78" t="s">
@@ -7606,27 +7920,31 @@
         <v>1.4605006085005228</v>
       </c>
       <c r="V78" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>20.784315948815912</v>
       </c>
       <c r="W78" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>25.967500000000001</v>
       </c>
-      <c r="X78" s="8">
+      <c r="X78" s="12">
         <f t="shared" si="29"/>
-        <v>257.06390357289115</v>
-      </c>
-      <c r="Y78" s="9">
+        <v>19.118290805850567</v>
+      </c>
+      <c r="Y78" s="8">
+        <f t="shared" si="30"/>
+        <v>276.18219437874171</v>
+      </c>
+      <c r="Z78" s="9">
         <f t="shared" si="27"/>
-        <v>4.5634535792528297E-2</v>
-      </c>
-      <c r="Z78" s="8">
+        <v>4.9028455802087964E-2</v>
+      </c>
+      <c r="AA78" s="8">
         <f t="shared" si="28"/>
-        <v>5376.0360964271094</v>
-      </c>
-    </row>
-    <row r="79" spans="1:26" x14ac:dyDescent="0.25">
+        <v>5356.9178056212586</v>
+      </c>
+    </row>
+    <row r="79" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>2</v>
       </c>
@@ -7669,7 +7987,7 @@
         <v>314.60000000000002</v>
       </c>
       <c r="P79" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>18.594927692479285</v>
       </c>
       <c r="Q79" t="s">
@@ -7691,27 +8009,31 @@
         <v>1.4613812618091198</v>
       </c>
       <c r="V79" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>32.928343434457943</v>
       </c>
       <c r="W79" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>41.14</v>
       </c>
-      <c r="X79" s="8">
+      <c r="X79" s="12">
         <f t="shared" si="29"/>
-        <v>407.26327112693724</v>
-      </c>
-      <c r="Y79" s="9">
+        <v>30.288879705504662</v>
+      </c>
+      <c r="Y79" s="8">
+        <f t="shared" si="30"/>
+        <v>437.5521508324419</v>
+      </c>
+      <c r="Z79" s="9">
         <f t="shared" si="27"/>
-        <v>4.5251474569659694E-2</v>
-      </c>
-      <c r="Z79" s="8">
+        <v>4.8616905648049102E-2</v>
+      </c>
+      <c r="AA79" s="8">
         <f t="shared" si="28"/>
-        <v>8592.736728873062</v>
-      </c>
-    </row>
-    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
+        <v>8562.4478491675582</v>
+      </c>
+    </row>
+    <row r="80" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>2</v>
       </c>
@@ -7754,7 +8076,7 @@
         <v>77.350000000000009</v>
       </c>
       <c r="P80" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>4.5718933789360223</v>
       </c>
       <c r="Q80" t="s">
@@ -7776,27 +8098,31 @@
         <v>1.4628909531952863</v>
       </c>
       <c r="V80" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>8.0960183237613546</v>
       </c>
       <c r="W80" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>10.115</v>
       </c>
-      <c r="X80" s="8">
+      <c r="X80" s="12">
         <f t="shared" si="29"/>
-        <v>100.13291170269738</v>
-      </c>
-      <c r="Y80" s="9">
+        <v>7.4470592664360629</v>
+      </c>
+      <c r="Y80" s="8">
+        <f t="shared" si="30"/>
+        <v>107.57997096913344</v>
+      </c>
+      <c r="Z80" s="9">
         <f t="shared" si="27"/>
-        <v>3.7224130744497166E-2</v>
-      </c>
-      <c r="Z80" s="8">
+        <v>3.9992554263618377E-2</v>
+      </c>
+      <c r="AA80" s="8">
         <f t="shared" si="28"/>
-        <v>2589.8670882973024</v>
-      </c>
-    </row>
-    <row r="81" spans="1:26" x14ac:dyDescent="0.25">
+        <v>2582.4200290308668</v>
+      </c>
+    </row>
+    <row r="81" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>2</v>
       </c>
@@ -7839,7 +8165,7 @@
         <v>129.155</v>
       </c>
       <c r="P81" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>7.6339093646603997</v>
       </c>
       <c r="Q81" t="s">
@@ -7861,27 +8187,31 @@
         <v>1.4868359713550046</v>
       </c>
       <c r="V81" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>13.518309587658663</v>
       </c>
       <c r="W81" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>16.889500000000002</v>
       </c>
-      <c r="X81" s="8">
+      <c r="X81" s="12">
         <f t="shared" si="29"/>
-        <v>167.19671895231909</v>
-      </c>
-      <c r="Y81" s="9">
+        <v>12.434711565049124</v>
+      </c>
+      <c r="Y81" s="8">
+        <f t="shared" si="30"/>
+        <v>179.63143051736822</v>
+      </c>
+      <c r="Z81" s="9">
         <f t="shared" si="27"/>
-        <v>4.2794143576227052E-2</v>
-      </c>
-      <c r="Z81" s="8">
+        <v>4.5976818663262919E-2</v>
+      </c>
+      <c r="AA81" s="8">
         <f t="shared" si="28"/>
-        <v>3739.8032810476807</v>
-      </c>
-    </row>
-    <row r="82" spans="1:26" x14ac:dyDescent="0.25">
+        <v>3727.3685694826318</v>
+      </c>
+    </row>
+    <row r="82" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>2</v>
       </c>
@@ -7924,7 +8254,7 @@
         <v>120.9</v>
       </c>
       <c r="P82" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>7.1459846090932784</v>
       </c>
       <c r="Q82" t="s">
@@ -7946,27 +8276,31 @@
         <v>1.4889067977801547</v>
       </c>
       <c r="V82" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>12.654280741341276</v>
       </c>
       <c r="W82" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>15.81</v>
       </c>
-      <c r="X82" s="8">
+      <c r="X82" s="12">
         <f t="shared" si="29"/>
-        <v>156.51026535043457</v>
-      </c>
-      <c r="Y82" s="9">
+        <v>11.639941374429478</v>
+      </c>
+      <c r="Y82" s="8">
+        <f t="shared" si="30"/>
+        <v>168.15020672486403</v>
+      </c>
+      <c r="Z82" s="9">
         <f t="shared" si="27"/>
-        <v>3.9423240642426846E-2</v>
-      </c>
-      <c r="Z82" s="8">
+        <v>4.2355215799713859E-2</v>
+      </c>
+      <c r="AA82" s="8">
         <f t="shared" si="28"/>
-        <v>3813.4897346495654</v>
-      </c>
-    </row>
-    <row r="83" spans="1:26" x14ac:dyDescent="0.25">
+        <v>3801.8497932751361</v>
+      </c>
+    </row>
+    <row r="83" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>1</v>
       </c>
@@ -8009,7 +8343,7 @@
         <v>105.88500000000001</v>
       </c>
       <c r="P83" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>6.2584994237704041</v>
       </c>
       <c r="Q83" t="s">
@@ -8031,27 +8365,31 @@
         <v>1.4716994675035486</v>
       </c>
       <c r="V83" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>11.082700713787602</v>
       </c>
       <c r="W83" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>13.846500000000001</v>
       </c>
-      <c r="X83" s="8">
+      <c r="X83" s="12">
         <f t="shared" si="29"/>
-        <v>137.072700137558</v>
-      </c>
-      <c r="Y83" s="9">
+        <v>10.194335752121301</v>
+      </c>
+      <c r="Y83" s="8">
+        <f t="shared" si="30"/>
+        <v>147.26703588967931</v>
+      </c>
+      <c r="Z83" s="9">
         <f t="shared" si="27"/>
-        <v>3.9514061891044581E-2</v>
-      </c>
-      <c r="Z83" s="8">
+        <v>4.2452791582975678E-2</v>
+      </c>
+      <c r="AA83" s="8">
         <f t="shared" si="28"/>
-        <v>3331.887299862442</v>
-      </c>
-    </row>
-    <row r="84" spans="1:26" x14ac:dyDescent="0.25">
+        <v>3321.6929641103206</v>
+      </c>
+    </row>
+    <row r="84" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>1</v>
       </c>
@@ -8094,7 +8432,7 @@
         <v>159.57500000000002</v>
       </c>
       <c r="P84" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>9.43193129856129</v>
       </c>
       <c r="Q84" t="s">
@@ -8116,27 +8454,31 @@
         <v>1.4825169412154502</v>
       </c>
       <c r="V84" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>16.702289903221953</v>
       </c>
       <c r="W84" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>20.867500000000003</v>
       </c>
-      <c r="X84" s="8">
+      <c r="X84" s="12">
         <f t="shared" si="29"/>
-        <v>206.57672120178327</v>
-      </c>
-      <c r="Y84" s="9">
+        <v>15.363471007647508</v>
+      </c>
+      <c r="Y84" s="8">
+        <f t="shared" si="30"/>
+        <v>221.94019220943079</v>
+      </c>
+      <c r="Z84" s="9">
         <f t="shared" si="27"/>
-        <v>3.9833152630958678E-2</v>
-      </c>
-      <c r="Z84" s="8">
+        <v>4.2795613657683744E-2</v>
+      </c>
+      <c r="AA84" s="8">
         <f t="shared" si="28"/>
-        <v>4979.4732787982166</v>
-      </c>
-    </row>
-    <row r="85" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4964.109807790569</v>
+      </c>
+    </row>
+    <row r="85" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>1</v>
       </c>
@@ -8179,7 +8521,7 @@
         <v>120.9</v>
       </c>
       <c r="P85" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>7.1459846090932784</v>
       </c>
       <c r="Q85" t="s">
@@ -8201,27 +8543,31 @@
         <v>1.4889067977801547</v>
       </c>
       <c r="V85" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>12.654280741341276</v>
       </c>
       <c r="W85" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>15.81</v>
       </c>
-      <c r="X85" s="8">
+      <c r="X85" s="12">
         <f t="shared" si="29"/>
-        <v>156.51026535043457</v>
-      </c>
-      <c r="Y85" s="9">
+        <v>11.639941374429478</v>
+      </c>
+      <c r="Y85" s="8">
+        <f t="shared" si="30"/>
+        <v>168.15020672486403</v>
+      </c>
+      <c r="Z85" s="9">
         <f t="shared" si="27"/>
-        <v>3.9944939665514226E-2</v>
-      </c>
-      <c r="Z85" s="8">
+        <v>4.2915714488946065E-2</v>
+      </c>
+      <c r="AA85" s="8">
         <f t="shared" si="28"/>
-        <v>3761.6397346495655</v>
-      </c>
-    </row>
-    <row r="86" spans="1:26" x14ac:dyDescent="0.25">
+        <v>3749.9997932751362</v>
+      </c>
+    </row>
+    <row r="86" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>1</v>
       </c>
@@ -8264,7 +8610,7 @@
         <v>137.80000000000001</v>
       </c>
       <c r="P86" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>8.1448856834826611</v>
       </c>
       <c r="Q86" t="s">
@@ -8286,27 +8632,31 @@
         <v>1.4741907644796231</v>
       </c>
       <c r="V86" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>14.423158694431992</v>
       </c>
       <c r="W86" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>18.02</v>
       </c>
-      <c r="X86" s="8">
+      <c r="X86" s="12">
         <f t="shared" si="29"/>
-        <v>178.3880443779147</v>
-      </c>
-      <c r="Y86" s="9">
+        <v>13.267029953650802</v>
+      </c>
+      <c r="Y86" s="8">
+        <f t="shared" si="30"/>
+        <v>191.65507433156549</v>
+      </c>
+      <c r="Z86" s="9">
         <f t="shared" si="27"/>
-        <v>3.9521466729715023E-2</v>
-      </c>
-      <c r="Z86" s="8">
+        <v>4.2460747132411436E-2</v>
+      </c>
+      <c r="AA86" s="8">
         <f t="shared" si="28"/>
-        <v>4335.3119556220854</v>
-      </c>
-    </row>
-    <row r="87" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4322.0449256684342</v>
+      </c>
+    </row>
+    <row r="87" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>1</v>
       </c>
@@ -8349,7 +8699,7 @@
         <v>142.155</v>
       </c>
       <c r="P87" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>8.4022948064983858</v>
       </c>
       <c r="Q87" t="s">
@@ -8371,27 +8721,31 @@
         <v>1.4760519098676312</v>
       </c>
       <c r="V87" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>14.878984936189983</v>
       </c>
       <c r="W87" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>18.589500000000001</v>
       </c>
-      <c r="X87" s="8">
+      <c r="X87" s="12">
         <f t="shared" si="29"/>
-        <v>184.02577974268837</v>
-      </c>
-      <c r="Y87" s="9">
+        <v>13.686318164450142</v>
+      </c>
+      <c r="Y87" s="8">
+        <f t="shared" si="30"/>
+        <v>197.71209790713851</v>
+      </c>
+      <c r="Z87" s="9">
         <f t="shared" si="27"/>
-        <v>3.9676718794576342E-2</v>
-      </c>
-      <c r="Z87" s="8">
+        <v>4.2627545564082617E-2</v>
+      </c>
+      <c r="AA87" s="8">
         <f t="shared" si="28"/>
-        <v>4454.1042202573117</v>
-      </c>
-    </row>
-    <row r="88" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4440.4179020928614</v>
+      </c>
+    </row>
+    <row r="88" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>1</v>
       </c>
@@ -8434,7 +8788,7 @@
         <v>145.535</v>
       </c>
       <c r="P88" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>8.6020750213762636</v>
       </c>
       <c r="Q88" t="s">
@@ -8456,27 +8810,31 @@
         <v>1.4735858032636355</v>
       </c>
       <c r="V88" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>15.232760526808129</v>
       </c>
       <c r="W88" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>19.031500000000001</v>
       </c>
-      <c r="X88" s="8">
+      <c r="X88" s="12">
         <f t="shared" si="29"/>
-        <v>188.40133554818439</v>
-      </c>
-      <c r="Y88" s="9">
+        <v>14.011735880294408</v>
+      </c>
+      <c r="Y88" s="8">
+        <f t="shared" si="30"/>
+        <v>202.41307142847879</v>
+      </c>
+      <c r="Z88" s="9">
         <f t="shared" si="27"/>
-        <v>3.956132918996115E-2</v>
-      </c>
-      <c r="Z88" s="8">
+        <v>4.2503574233342736E-2</v>
+      </c>
+      <c r="AA88" s="8">
         <f t="shared" si="28"/>
-        <v>4573.8586644518155</v>
-      </c>
-    </row>
-    <row r="89" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4559.8469285715219</v>
+      </c>
+    </row>
+    <row r="89" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>1</v>
       </c>
@@ -8519,7 +8877,7 @@
         <v>120.9</v>
       </c>
       <c r="P89" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>7.1459846090932784</v>
       </c>
       <c r="Q89" t="s">
@@ -8541,27 +8899,31 @@
         <v>1.4889067977801547</v>
       </c>
       <c r="V89" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>12.654280741341276</v>
       </c>
       <c r="W89" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>15.81</v>
       </c>
-      <c r="X89" s="8">
+      <c r="X89" s="12">
         <f t="shared" si="29"/>
-        <v>156.51026535043457</v>
-      </c>
-      <c r="Y89" s="9">
+        <v>11.639941374429478</v>
+      </c>
+      <c r="Y89" s="8">
+        <f t="shared" si="30"/>
+        <v>168.15020672486403</v>
+      </c>
+      <c r="Z89" s="9">
         <f t="shared" si="27"/>
-        <v>3.9944939665514226E-2</v>
-      </c>
-      <c r="Z89" s="8">
+        <v>4.2915714488946065E-2</v>
+      </c>
+      <c r="AA89" s="8">
         <f t="shared" si="28"/>
-        <v>3761.6397346495655</v>
-      </c>
-    </row>
-    <row r="90" spans="1:26" x14ac:dyDescent="0.25">
+        <v>3749.9997932751362</v>
+      </c>
+    </row>
+    <row r="90" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>1</v>
       </c>
@@ -8604,7 +8966,7 @@
         <v>120.9</v>
       </c>
       <c r="P90" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>7.1459846090932784</v>
       </c>
       <c r="Q90" t="s">
@@ -8626,27 +8988,31 @@
         <v>1.4889067977801547</v>
       </c>
       <c r="V90" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>12.654280741341276</v>
       </c>
       <c r="W90" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>15.81</v>
       </c>
-      <c r="X90" s="8">
+      <c r="X90" s="12">
         <f t="shared" si="29"/>
-        <v>156.51026535043457</v>
-      </c>
-      <c r="Y90" s="9">
+        <v>11.639941374429478</v>
+      </c>
+      <c r="Y90" s="8">
+        <f t="shared" si="30"/>
+        <v>168.15020672486403</v>
+      </c>
+      <c r="Z90" s="9">
         <f t="shared" si="27"/>
-        <v>3.9817402841843583E-2</v>
-      </c>
-      <c r="Z90" s="8">
+        <v>4.2778692529285886E-2</v>
+      </c>
+      <c r="AA90" s="8">
         <f t="shared" si="28"/>
-        <v>3774.1897346495653</v>
-      </c>
-    </row>
-    <row r="91" spans="1:26" x14ac:dyDescent="0.25">
+        <v>3762.5497932751359</v>
+      </c>
+    </row>
+    <row r="91" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>1</v>
       </c>
@@ -8689,7 +9055,7 @@
         <v>120.9</v>
       </c>
       <c r="P91" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>7.1459846090932784</v>
       </c>
       <c r="Q91" t="s">
@@ -8711,27 +9077,31 @@
         <v>1.4889067977801547</v>
       </c>
       <c r="V91" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>12.654280741341276</v>
       </c>
       <c r="W91" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>15.81</v>
       </c>
-      <c r="X91" s="8">
+      <c r="X91" s="12">
         <f t="shared" si="29"/>
-        <v>156.51026535043457</v>
-      </c>
-      <c r="Y91" s="9">
+        <v>11.639941374429478</v>
+      </c>
+      <c r="Y91" s="8">
+        <f t="shared" si="30"/>
+        <v>168.15020672486403</v>
+      </c>
+      <c r="Z91" s="9">
         <f t="shared" si="27"/>
-        <v>3.9817402841843583E-2</v>
-      </c>
-      <c r="Z91" s="8">
+        <v>4.2778692529285886E-2</v>
+      </c>
+      <c r="AA91" s="8">
         <f t="shared" si="28"/>
-        <v>3774.1897346495653</v>
-      </c>
-    </row>
-    <row r="92" spans="1:26" x14ac:dyDescent="0.25">
+        <v>3762.5497932751359</v>
+      </c>
+    </row>
+    <row r="92" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>1</v>
       </c>
@@ -8774,7 +9144,7 @@
         <v>181.35</v>
       </c>
       <c r="P92" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>10.718976913639917</v>
       </c>
       <c r="Q92" t="s">
@@ -8796,27 +9166,31 @@
         <v>1.4889067977801544</v>
       </c>
       <c r="V92" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>18.981421112011915</v>
       </c>
       <c r="W92" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>23.715000000000003</v>
       </c>
-      <c r="X92" s="8">
+      <c r="X92" s="12">
         <f t="shared" si="29"/>
-        <v>234.76539802565182</v>
-      </c>
-      <c r="Y92" s="9">
+        <v>17.459912061644214</v>
+      </c>
+      <c r="Y92" s="8">
+        <f t="shared" si="30"/>
+        <v>252.22531008729604</v>
+      </c>
+      <c r="Z92" s="9">
         <f t="shared" si="27"/>
-        <v>3.9987633692273282E-2</v>
-      </c>
-      <c r="Z92" s="8">
+        <v>4.2961583744929872E-2</v>
+      </c>
+      <c r="AA92" s="8">
         <f t="shared" si="28"/>
-        <v>5636.184601974348</v>
-      </c>
-    </row>
-    <row r="93" spans="1:26" x14ac:dyDescent="0.25">
+        <v>5618.724689912704</v>
+      </c>
+    </row>
+    <row r="93" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>1</v>
       </c>
@@ -8859,7 +9233,7 @@
         <v>198.25</v>
       </c>
       <c r="P93" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>11.717877988029301</v>
       </c>
       <c r="Q93" t="s">
@@ -8881,27 +9255,31 @@
         <v>1.4786470280847135</v>
       </c>
       <c r="V93" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>20.750299065102631</v>
       </c>
       <c r="W93" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>25.925000000000001</v>
       </c>
-      <c r="X93" s="8">
+      <c r="X93" s="12">
         <f t="shared" si="29"/>
-        <v>256.64317705313192</v>
-      </c>
-      <c r="Y93" s="9">
+        <v>19.08700064086554</v>
+      </c>
+      <c r="Y93" s="8">
+        <f t="shared" si="30"/>
+        <v>275.73017769399746</v>
+      </c>
+      <c r="Z93" s="9">
         <f t="shared" si="27"/>
-        <v>3.9688112124508144E-2</v>
-      </c>
-      <c r="Z93" s="8">
+        <v>4.2639786235830431E-2</v>
+      </c>
+      <c r="AA93" s="8">
         <f t="shared" si="28"/>
-        <v>6209.8568229468683</v>
-      </c>
-    </row>
-    <row r="94" spans="1:26" x14ac:dyDescent="0.25">
+        <v>6190.7698223060024</v>
+      </c>
+    </row>
+    <row r="94" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>1</v>
       </c>
@@ -8944,7 +9322,7 @@
         <v>43.550000000000004</v>
       </c>
       <c r="P94" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>2.574091230157256</v>
       </c>
       <c r="Q94" t="s">
@@ -8966,27 +9344,31 @@
         <v>1.5374697076719088</v>
       </c>
       <c r="V94" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>4.5582624175799218</v>
       </c>
       <c r="W94" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>5.6950000000000003</v>
       </c>
-      <c r="X94" s="8">
+      <c r="X94" s="12">
         <f t="shared" si="29"/>
-        <v>56.377353647737188</v>
-      </c>
-      <c r="Y94" s="9">
+        <v>4.1928821079934133</v>
+      </c>
+      <c r="Y94" s="8">
+        <f t="shared" si="30"/>
+        <v>60.5702357557306</v>
+      </c>
+      <c r="Z94" s="9">
         <f t="shared" si="27"/>
-        <v>4.1157361401472616E-2</v>
-      </c>
-      <c r="Z94" s="8">
+        <v>4.4218306143765949E-2</v>
+      </c>
+      <c r="AA94" s="8">
         <f t="shared" si="28"/>
-        <v>1313.4226463522627</v>
-      </c>
-    </row>
-    <row r="95" spans="1:26" x14ac:dyDescent="0.25">
+        <v>1309.2297642442693</v>
+      </c>
+    </row>
+    <row r="95" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>1</v>
       </c>
@@ -9029,7 +9411,7 @@
         <v>74.945000000000007</v>
       </c>
       <c r="P95" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>4.4297420721959941</v>
       </c>
       <c r="Q95" t="s">
@@ -9051,27 +9433,31 @@
         <v>1.4753669530147957</v>
       </c>
       <c r="V95" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>7.84429338428306</v>
       </c>
       <c r="W95" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>9.8005000000000013</v>
       </c>
-      <c r="X95" s="8">
+      <c r="X95" s="12">
         <f t="shared" si="29"/>
-        <v>97.019535456479062</v>
-      </c>
-      <c r="Y95" s="9">
+        <v>7.2155120455468751</v>
+      </c>
+      <c r="Y95" s="8">
+        <f t="shared" si="30"/>
+        <v>104.23504750202594</v>
+      </c>
+      <c r="Z95" s="9">
         <f t="shared" si="27"/>
-        <v>3.9646577169182858E-2</v>
-      </c>
-      <c r="Z95" s="8">
+        <v>4.2595162253444237E-2</v>
+      </c>
+      <c r="AA95" s="8">
         <f t="shared" si="28"/>
-        <v>2350.0904645435212</v>
-      </c>
-    </row>
-    <row r="96" spans="1:26" x14ac:dyDescent="0.25">
+        <v>2342.8749524979744</v>
+      </c>
+    </row>
+    <row r="96" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>2</v>
       </c>
@@ -9133,27 +9519,31 @@
         <v>4.6617499999999996</v>
       </c>
       <c r="V96" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>40.480091618806767</v>
       </c>
       <c r="W96" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>50.575000000000003</v>
       </c>
-      <c r="X96" s="8">
+      <c r="X96" s="12">
         <f t="shared" si="29"/>
-        <v>1396.3450916188067</v>
-      </c>
-      <c r="Y96" s="9">
+        <v>37.235296332180319</v>
+      </c>
+      <c r="Y96" s="8">
+        <f t="shared" si="30"/>
+        <v>1433.580387950987</v>
+      </c>
+      <c r="Z96" s="9">
         <f t="shared" si="27"/>
-        <v>0.10641252031845806</v>
-      </c>
-      <c r="Z96" s="8">
+        <v>0.10925014387677084</v>
+      </c>
+      <c r="AA96" s="8">
         <f t="shared" si="28"/>
-        <v>11725.654908381193</v>
-      </c>
-    </row>
-    <row r="97" spans="1:26" x14ac:dyDescent="0.25">
+        <v>11688.419612049012</v>
+      </c>
+    </row>
+    <row r="97" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>2</v>
       </c>
@@ -9196,7 +9586,7 @@
         <v>2784.6</v>
       </c>
       <c r="P97" s="7">
-        <f t="shared" ref="P97:P98" si="33">0.0768385441837987*H97</f>
+        <f t="shared" ref="P97:P98" si="34">0.0768385441837987*H97</f>
         <v>164.58816164169681</v>
       </c>
       <c r="Q97" t="s">
@@ -9218,27 +9608,31 @@
         <v>1.4628909531952861</v>
       </c>
       <c r="V97" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>291.45665965540877</v>
       </c>
       <c r="W97" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>364.14000000000004</v>
       </c>
-      <c r="X97" s="8">
+      <c r="X97" s="12">
         <f t="shared" si="29"/>
-        <v>3604.7848212971053</v>
-      </c>
-      <c r="Y97" s="9">
+        <v>268.09413359169827</v>
+      </c>
+      <c r="Y97" s="8">
+        <f t="shared" si="30"/>
+        <v>3872.8789548888035</v>
+      </c>
+      <c r="Z97" s="9">
         <f t="shared" si="27"/>
-        <v>3.9793709693874885E-2</v>
-      </c>
-      <c r="Z97" s="8">
+        <v>4.2753237280583965E-2</v>
+      </c>
+      <c r="AA97" s="8">
         <f t="shared" si="28"/>
-        <v>86982.015178702903</v>
-      </c>
-    </row>
-    <row r="98" spans="1:26" x14ac:dyDescent="0.25">
+        <v>86713.921045111201</v>
+      </c>
+    </row>
+    <row r="98" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>1</v>
       </c>
@@ -9279,7 +9673,7 @@
         <v>8.254999999999999</v>
       </c>
       <c r="P98" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0.48792475556712167</v>
       </c>
       <c r="Q98" t="s">
@@ -9289,39 +9683,43 @@
         <v>91</v>
       </c>
       <c r="S98" s="8">
-        <f t="shared" ref="S98:S129" si="34">SUM(M98+O98+P98)</f>
+        <f t="shared" ref="S98:S129" si="35">SUM(M98+O98+P98)</f>
         <v>8.7429247555671203</v>
       </c>
       <c r="T98" s="8">
-        <f t="shared" ref="T98:T129" si="35">SUM(M98+O98+P98)/H98</f>
+        <f t="shared" ref="T98:T129" si="36">SUM(M98+O98+P98)/H98</f>
         <v>1.3768385441837985</v>
       </c>
       <c r="U98" s="8">
-        <f t="shared" ref="U98:U129" si="36">SUM(M98+O98+P98)/I98</f>
+        <f t="shared" ref="U98:U129" si="37">SUM(M98+O98+P98)/I98</f>
         <v>1.4571541259278533</v>
       </c>
       <c r="V98" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.86402884631738819</v>
       </c>
       <c r="W98" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>1.0795000000000001</v>
       </c>
-      <c r="X98" s="8">
+      <c r="X98" s="12">
         <f t="shared" si="29"/>
-        <v>10.686453601884509</v>
-      </c>
-      <c r="Y98" s="9">
-        <f t="shared" ref="Y98:Y129" si="37">X98/J98</f>
-        <v>0.21993112990089542</v>
-      </c>
-      <c r="Z98" s="8">
-        <f t="shared" ref="Z98:Z129" si="38">J98-X98</f>
-        <v>37.903546398115495</v>
-      </c>
-    </row>
-    <row r="99" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.79477019061964704</v>
+      </c>
+      <c r="Y98" s="8">
+        <f t="shared" si="30"/>
+        <v>11.481223792504156</v>
+      </c>
+      <c r="Z98" s="9">
+        <f t="shared" ref="Z98:Z129" si="38">Y98/J98</f>
+        <v>0.23628779157242552</v>
+      </c>
+      <c r="AA98" s="8">
+        <f t="shared" ref="AA98:AA129" si="39">J98-Y98</f>
+        <v>37.10877620749585</v>
+      </c>
+    </row>
+    <row r="99" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>1</v>
       </c>
@@ -9371,32 +9769,35 @@
         <v>206</v>
       </c>
       <c r="S99" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1100</v>
       </c>
       <c r="T99" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.25352632064165204</v>
       </c>
       <c r="U99" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.27346857597454255</v>
       </c>
       <c r="V99" s="8"/>
-      <c r="X99" s="8">
+      <c r="X99" s="12">
         <f t="shared" si="29"/>
-        <v>1100</v>
-      </c>
-      <c r="Y99" s="9">
-        <f t="shared" si="37"/>
-        <v>3.3415718267826376E-2</v>
-      </c>
-      <c r="Z99" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="9">
         <f t="shared" si="38"/>
-        <v>31818.639999999999</v>
-      </c>
-    </row>
-    <row r="100" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="8">
+        <f t="shared" si="39"/>
+        <v>32918.639999999999</v>
+      </c>
+    </row>
+    <row r="100" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>2</v>
       </c>
@@ -9446,35 +9847,39 @@
         <v>17</v>
       </c>
       <c r="S100" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1059.6445362737456</v>
       </c>
       <c r="T100" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.28111010379990597</v>
       </c>
       <c r="U100" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.292235117560327</v>
       </c>
       <c r="V100" s="8"/>
       <c r="W100" s="4">
         <v>0</v>
       </c>
-      <c r="X100" s="8">
+      <c r="X100" s="12">
         <f t="shared" si="29"/>
-        <v>1059.6445362737456</v>
-      </c>
-      <c r="Y100" s="9">
-        <f t="shared" si="37"/>
-        <v>2.550852502295925E-2</v>
-      </c>
-      <c r="Z100" s="8">
+        <v>471.7931076442141</v>
+      </c>
+      <c r="Y100" s="8">
+        <f t="shared" si="30"/>
+        <v>1531.4376439179598</v>
+      </c>
+      <c r="Z100" s="9">
         <f t="shared" si="38"/>
-        <v>40481.15546372626</v>
-      </c>
-    </row>
-    <row r="101" spans="1:26" x14ac:dyDescent="0.25">
+        <v>3.6865867867685739E-2</v>
+      </c>
+      <c r="AA100" s="8">
+        <f t="shared" si="39"/>
+        <v>40009.362356082042</v>
+      </c>
+    </row>
+    <row r="101" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>2</v>
       </c>
@@ -9524,35 +9929,39 @@
         <v>17</v>
       </c>
       <c r="S101" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>142.17143499680245</v>
       </c>
       <c r="T101" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.28111010379990597</v>
       </c>
       <c r="U101" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.29867948528740007</v>
       </c>
       <c r="V101" s="8"/>
       <c r="W101" s="4">
         <v>0</v>
       </c>
-      <c r="X101" s="8">
+      <c r="X101" s="12">
         <f t="shared" si="29"/>
-        <v>142.17143499680245</v>
-      </c>
-      <c r="Y101" s="9">
-        <f t="shared" si="37"/>
-        <v>2.0809331683787187E-2</v>
-      </c>
-      <c r="Z101" s="8">
+        <v>63.300003764706538</v>
+      </c>
+      <c r="Y101" s="8">
+        <f t="shared" si="30"/>
+        <v>205.47143876150898</v>
+      </c>
+      <c r="Z101" s="9">
         <f t="shared" si="38"/>
-        <v>6689.9285650031979</v>
-      </c>
-    </row>
-    <row r="102" spans="1:26" x14ac:dyDescent="0.25">
+        <v>3.0074419104156695E-2</v>
+      </c>
+      <c r="AA101" s="8">
+        <f t="shared" si="39"/>
+        <v>6626.6285612384918</v>
+      </c>
+    </row>
+    <row r="102" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>1</v>
       </c>
@@ -9602,32 +10011,35 @@
         <v>206</v>
       </c>
       <c r="S102" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>798.18402872945308</v>
       </c>
       <c r="T102" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.28111010379990597</v>
       </c>
       <c r="U102" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.30567709433572809</v>
       </c>
       <c r="V102" s="8"/>
-      <c r="X102" s="8">
+      <c r="X102" s="12">
         <f t="shared" si="29"/>
-        <v>798.18402872945308</v>
-      </c>
-      <c r="Y102" s="9">
-        <f t="shared" si="37"/>
-        <v>3.7171865277441839E-2</v>
-      </c>
-      <c r="Z102" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="9">
         <f t="shared" si="38"/>
-        <v>20674.615971270545</v>
-      </c>
-    </row>
-    <row r="103" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="8">
+        <f t="shared" si="39"/>
+        <v>21472.799999999999</v>
+      </c>
+    </row>
+    <row r="103" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>4</v>
       </c>
@@ -9679,15 +10091,15 @@
         <v>46</v>
       </c>
       <c r="S103" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>8332.6</v>
       </c>
       <c r="T103" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.5992246276677415</v>
       </c>
       <c r="U103" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.7641852981029811</v>
       </c>
       <c r="V103" s="8">
@@ -9698,20 +10110,24 @@
         <f>H103*0.17</f>
         <v>885.76800000000003</v>
       </c>
-      <c r="X103" s="8">
+      <c r="X103" s="12">
         <f t="shared" si="29"/>
-        <v>9927.3342835987587</v>
-      </c>
-      <c r="Y103" s="9">
-        <f t="shared" si="37"/>
-        <v>5.1632580447783308E-2</v>
-      </c>
-      <c r="Z103" s="8">
+        <v>652.13710255190688</v>
+      </c>
+      <c r="Y103" s="8">
+        <f t="shared" si="30"/>
+        <v>10579.471386150666</v>
+      </c>
+      <c r="Z103" s="9">
         <f t="shared" si="38"/>
-        <v>182341.46571640123</v>
-      </c>
-    </row>
-    <row r="104" spans="1:26" x14ac:dyDescent="0.25">
+        <v>5.5024379338460876E-2</v>
+      </c>
+      <c r="AA103" s="8">
+        <f t="shared" si="39"/>
+        <v>181689.32861384933</v>
+      </c>
+    </row>
+    <row r="104" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>1</v>
       </c>
@@ -9761,32 +10177,35 @@
         <v>206</v>
       </c>
       <c r="S104" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>326.53323426519341</v>
       </c>
       <c r="T104" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.34054673229931004</v>
       </c>
       <c r="U104" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.36041195835010309</v>
       </c>
       <c r="V104" s="8"/>
-      <c r="X104" s="8">
+      <c r="X104" s="12">
         <f t="shared" si="29"/>
-        <v>326.53323426519341</v>
-      </c>
-      <c r="Y104" s="9">
-        <f t="shared" si="37"/>
-        <v>4.4559483826511821E-2</v>
-      </c>
-      <c r="Z104" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y104" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z104" s="9">
         <f t="shared" si="38"/>
-        <v>7001.4967657348061</v>
-      </c>
-    </row>
-    <row r="105" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="AA104" s="8">
+        <f t="shared" si="39"/>
+        <v>7328.03</v>
+      </c>
+    </row>
+    <row r="105" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>2</v>
       </c>
@@ -9829,7 +10248,7 @@
         <v>705.9</v>
       </c>
       <c r="P105" s="7">
-        <f t="shared" ref="P105:P124" si="39">0.0768385441837987*H105</f>
+        <f t="shared" ref="P105:P124" si="40">0.0768385441837987*H105</f>
         <v>41.723329491802687</v>
       </c>
       <c r="Q105" t="s">
@@ -9839,39 +10258,43 @@
         <v>138</v>
       </c>
       <c r="S105" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>747.62332949180268</v>
       </c>
       <c r="T105" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.3768385441837987</v>
       </c>
       <c r="U105" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.4716994675035486</v>
       </c>
       <c r="V105" s="8">
-        <f t="shared" ref="V105:V125" si="40">H105*0.136067534853132</f>
+        <f t="shared" ref="V105:V125" si="41">H105*0.136067534853132</f>
         <v>73.884671425250673</v>
       </c>
       <c r="W105" s="4">
-        <f t="shared" ref="W105:W125" si="41">H105*0.17</f>
+        <f t="shared" ref="W105:W125" si="42">H105*0.17</f>
         <v>92.31</v>
       </c>
-      <c r="X105" s="8">
+      <c r="X105" s="12">
         <f t="shared" si="29"/>
-        <v>913.81800091705327</v>
-      </c>
-      <c r="Y105" s="9">
-        <f t="shared" si="37"/>
-        <v>4.2542737472860956E-2</v>
-      </c>
-      <c r="Z105" s="8">
+        <v>67.962238347475335</v>
+      </c>
+      <c r="Y105" s="8">
+        <f t="shared" si="30"/>
+        <v>981.78023926452863</v>
+      </c>
+      <c r="Z105" s="9">
         <f t="shared" si="38"/>
-        <v>20566.181999082946</v>
-      </c>
-    </row>
-    <row r="106" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.570671504955906E-2</v>
+      </c>
+      <c r="AA105" s="8">
+        <f t="shared" si="39"/>
+        <v>20498.219760735472</v>
+      </c>
+    </row>
+    <row r="106" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>2</v>
       </c>
@@ -9914,7 +10337,7 @@
         <v>338.97500000000002</v>
       </c>
       <c r="P106" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>20.035650395925508</v>
       </c>
       <c r="Q106" t="s">
@@ -9924,39 +10347,43 @@
         <v>129</v>
       </c>
       <c r="S106" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>359.01065039592555</v>
       </c>
       <c r="T106" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.3768385441837989</v>
       </c>
       <c r="U106" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.4653495934527574</v>
       </c>
       <c r="V106" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>35.479609712954172</v>
       </c>
       <c r="W106" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>44.327500000000001</v>
       </c>
-      <c r="X106" s="8">
+      <c r="X106" s="12">
         <f t="shared" si="29"/>
-        <v>438.81776010887972</v>
-      </c>
-      <c r="Y106" s="9">
-        <f t="shared" si="37"/>
-        <v>4.2537588223039914E-2</v>
-      </c>
-      <c r="Z106" s="8">
+        <v>32.635642079381569</v>
+      </c>
+      <c r="Y106" s="8">
+        <f t="shared" si="30"/>
+        <v>471.45340218826129</v>
+      </c>
+      <c r="Z106" s="9">
         <f t="shared" si="38"/>
-        <v>9877.1822398911208</v>
-      </c>
-    </row>
-    <row r="107" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.570118284104898E-2</v>
+      </c>
+      <c r="AA106" s="8">
+        <f t="shared" si="39"/>
+        <v>9844.546597811739</v>
+      </c>
+    </row>
+    <row r="107" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>2</v>
       </c>
@@ -9999,7 +10426,7 @@
         <v>247.65</v>
       </c>
       <c r="P107" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>14.637742667013651</v>
       </c>
       <c r="Q107" t="s">
@@ -10009,39 +10436,43 @@
         <v>138</v>
       </c>
       <c r="S107" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>262.28774266701367</v>
       </c>
       <c r="T107" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.3768385441837989</v>
       </c>
       <c r="U107" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.4571541259278538</v>
       </c>
       <c r="V107" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>25.920865389521644</v>
       </c>
       <c r="W107" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>32.385000000000005</v>
       </c>
-      <c r="X107" s="8">
+      <c r="X107" s="12">
         <f t="shared" si="29"/>
-        <v>320.59360805653529</v>
-      </c>
-      <c r="Y107" s="9">
-        <f t="shared" si="37"/>
-        <v>6.9167984478216885E-2</v>
-      </c>
-      <c r="Z107" s="8">
+        <v>23.843105718589413</v>
+      </c>
+      <c r="Y107" s="8">
+        <f t="shared" si="30"/>
+        <v>344.4367137751247</v>
+      </c>
+      <c r="Z107" s="9">
         <f t="shared" si="38"/>
-        <v>4314.4063919434648</v>
-      </c>
-    </row>
-    <row r="108" spans="1:26" x14ac:dyDescent="0.25">
+        <v>7.4312128106823028E-2</v>
+      </c>
+      <c r="AA107" s="8">
+        <f t="shared" si="39"/>
+        <v>4290.5632862248749</v>
+      </c>
+    </row>
+    <row r="108" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>2</v>
       </c>
@@ -10084,7 +10515,7 @@
         <v>130.065</v>
       </c>
       <c r="P108" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>7.6876963455890595</v>
       </c>
       <c r="Q108" t="s">
@@ -10094,39 +10525,43 @@
         <v>129</v>
       </c>
       <c r="S108" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>137.75269634558904</v>
       </c>
       <c r="T108" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.3768385441837985</v>
       </c>
       <c r="U108" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.4748682692247219</v>
       </c>
       <c r="V108" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>13.613556862055857</v>
       </c>
       <c r="W108" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>17.008500000000002</v>
       </c>
-      <c r="X108" s="8">
+      <c r="X108" s="12">
         <f t="shared" si="29"/>
-        <v>168.37475320764489</v>
-      </c>
-      <c r="Y108" s="9">
-        <f t="shared" si="37"/>
-        <v>4.0867658545544874E-2</v>
-      </c>
-      <c r="Z108" s="8">
+        <v>12.522324027007194</v>
+      </c>
+      <c r="Y108" s="8">
+        <f t="shared" si="30"/>
+        <v>180.89707723465207</v>
+      </c>
+      <c r="Z108" s="9">
         <f t="shared" si="38"/>
-        <v>3951.625246792355</v>
-      </c>
-    </row>
-    <row r="109" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.3907057581226233E-2</v>
+      </c>
+      <c r="AA108" s="8">
+        <f t="shared" si="39"/>
+        <v>3939.102922765348</v>
+      </c>
+    </row>
+    <row r="109" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>2</v>
       </c>
@@ -10169,7 +10604,7 @@
         <v>222.625</v>
       </c>
       <c r="P109" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>13.158600691475526</v>
       </c>
       <c r="Q109" t="s">
@@ -10179,39 +10614,43 @@
         <v>91</v>
       </c>
       <c r="S109" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>235.78360069147553</v>
       </c>
       <c r="T109" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.3768385441837987</v>
       </c>
       <c r="U109" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.482915727619343</v>
       </c>
       <c r="V109" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>23.301565343598856</v>
       </c>
       <c r="W109" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>29.112500000000001</v>
       </c>
-      <c r="X109" s="8">
+      <c r="X109" s="12">
         <f t="shared" si="29"/>
-        <v>288.19766603507441</v>
-      </c>
-      <c r="Y109" s="9">
-        <f t="shared" si="37"/>
-        <v>4.3999643669477007E-2</v>
-      </c>
-      <c r="Z109" s="8">
+        <v>21.43376301474245</v>
+      </c>
+      <c r="Y109" s="8">
+        <f t="shared" si="30"/>
+        <v>309.63142904981686</v>
+      </c>
+      <c r="Z109" s="9">
         <f t="shared" si="38"/>
-        <v>6261.8023339649253</v>
-      </c>
-    </row>
-    <row r="110" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.7271973900735398E-2</v>
+      </c>
+      <c r="AA109" s="8">
+        <f t="shared" si="39"/>
+        <v>6240.3685709501833</v>
+      </c>
+    </row>
+    <row r="110" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>2</v>
       </c>
@@ -10254,7 +10693,7 @@
         <v>118.625</v>
       </c>
       <c r="P110" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>7.0115171567716308</v>
       </c>
       <c r="Q110" t="s">
@@ -10264,39 +10703,43 @@
         <v>128</v>
       </c>
       <c r="S110" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>125.63651715677163</v>
       </c>
       <c r="T110" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.3768385441837987</v>
       </c>
       <c r="U110" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.4608897343810654</v>
       </c>
       <c r="V110" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>12.416162555348295</v>
       </c>
       <c r="W110" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>15.512500000000001</v>
       </c>
-      <c r="X110" s="8">
+      <c r="X110" s="12">
         <f t="shared" si="29"/>
-        <v>153.56517971211991</v>
-      </c>
-      <c r="Y110" s="9">
-        <f t="shared" si="37"/>
-        <v>4.4728807896925626E-2</v>
-      </c>
-      <c r="Z110" s="8">
+        <v>11.420910219534299</v>
+      </c>
+      <c r="Y110" s="8">
+        <f t="shared" si="30"/>
+        <v>164.98608993165422</v>
+      </c>
+      <c r="Z110" s="9">
         <f t="shared" si="38"/>
-        <v>3279.68482028788</v>
-      </c>
-    </row>
-    <row r="111" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.8055367343378494E-2</v>
+      </c>
+      <c r="AA110" s="8">
+        <f t="shared" si="39"/>
+        <v>3268.2639100683459</v>
+      </c>
+    </row>
+    <row r="111" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>2</v>
       </c>
@@ -10339,7 +10782,7 @@
         <v>176.47499999999999</v>
       </c>
       <c r="P111" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>10.430832372950672</v>
       </c>
       <c r="Q111" t="s">
@@ -10349,39 +10792,43 @@
         <v>91</v>
       </c>
       <c r="S111" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>186.90583237295067</v>
       </c>
       <c r="T111" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.3768385441837987</v>
       </c>
       <c r="U111" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.4716994675035486</v>
       </c>
       <c r="V111" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>18.471167856312668</v>
       </c>
       <c r="W111" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>23.077500000000001</v>
       </c>
-      <c r="X111" s="8">
+      <c r="X111" s="12">
         <f t="shared" si="29"/>
-        <v>228.45450022926332</v>
-      </c>
-      <c r="Y111" s="9">
-        <f t="shared" si="37"/>
-        <v>4.2542737472860956E-2</v>
-      </c>
-      <c r="Z111" s="8">
+        <v>16.990559586868834</v>
+      </c>
+      <c r="Y111" s="8">
+        <f t="shared" si="30"/>
+        <v>245.44505981613216</v>
+      </c>
+      <c r="Z111" s="9">
         <f t="shared" si="38"/>
-        <v>5141.5454997707366</v>
-      </c>
-    </row>
-    <row r="112" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.570671504955906E-2</v>
+      </c>
+      <c r="AA111" s="8">
+        <f t="shared" si="39"/>
+        <v>5124.554940183868</v>
+      </c>
+    </row>
+    <row r="112" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>2</v>
       </c>
@@ -10424,7 +10871,7 @@
         <v>137.80000000000001</v>
       </c>
       <c r="P112" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>8.1448856834826611</v>
       </c>
       <c r="Q112" t="s">
@@ -10434,39 +10881,43 @@
         <v>129</v>
       </c>
       <c r="S112" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>145.94488568348268</v>
       </c>
       <c r="T112" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.3768385441837989</v>
       </c>
       <c r="U112" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.4741907644796231</v>
       </c>
       <c r="V112" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>14.423158694431992</v>
       </c>
       <c r="W112" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>18.02</v>
       </c>
-      <c r="X112" s="8">
+      <c r="X112" s="12">
         <f t="shared" si="29"/>
-        <v>178.3880443779147</v>
-      </c>
-      <c r="Y112" s="9">
-        <f t="shared" si="37"/>
-        <v>3.9249294692610494E-2</v>
-      </c>
-      <c r="Z112" s="8">
+        <v>13.267029953650802</v>
+      </c>
+      <c r="Y112" s="8">
+        <f t="shared" si="30"/>
+        <v>191.65507433156549</v>
+      </c>
+      <c r="Z112" s="9">
         <f t="shared" si="38"/>
-        <v>4366.6119556220856</v>
-      </c>
-    </row>
-    <row r="113" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.2168333186263035E-2</v>
+      </c>
+      <c r="AA112" s="8">
+        <f t="shared" si="39"/>
+        <v>4353.3449256684344</v>
+      </c>
+    </row>
+    <row r="113" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>1</v>
       </c>
@@ -10509,7 +10960,7 @@
         <v>123.30499999999999</v>
       </c>
       <c r="P113" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>7.2881359158333057</v>
       </c>
       <c r="Q113" t="s">
@@ -10519,39 +10970,43 @@
         <v>129</v>
       </c>
       <c r="S113" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>130.5931359158333</v>
       </c>
       <c r="T113" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.3768385441837987</v>
       </c>
       <c r="U113" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.4806477994992437</v>
       </c>
       <c r="V113" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>12.90600568081957</v>
       </c>
       <c r="W113" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>16.124500000000001</v>
       </c>
-      <c r="X113" s="8">
+      <c r="X113" s="12">
         <f t="shared" si="29"/>
-        <v>159.62364159665287</v>
-      </c>
-      <c r="Y113" s="9">
-        <f t="shared" si="37"/>
-        <v>3.9763061600363914E-2</v>
-      </c>
-      <c r="Z113" s="8">
+        <v>11.871488595318665</v>
+      </c>
+      <c r="Y113" s="8">
+        <f t="shared" si="30"/>
+        <v>171.49513019197153</v>
+      </c>
+      <c r="Z113" s="9">
         <f t="shared" si="38"/>
-        <v>3854.7463584033471</v>
-      </c>
-    </row>
-    <row r="114" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.2720309834910965E-2</v>
+      </c>
+      <c r="AA113" s="8">
+        <f t="shared" si="39"/>
+        <v>3842.8748698080285</v>
+      </c>
+    </row>
+    <row r="114" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>1</v>
       </c>
@@ -10594,7 +11049,7 @@
         <v>198.25</v>
       </c>
       <c r="P114" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>11.717877988029301</v>
       </c>
       <c r="Q114" t="s">
@@ -10604,39 +11059,43 @@
         <v>138</v>
       </c>
       <c r="S114" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>209.9678779880293</v>
       </c>
       <c r="T114" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.3768385441837987</v>
       </c>
       <c r="U114" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.4786470280847135</v>
       </c>
       <c r="V114" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>20.750299065102631</v>
       </c>
       <c r="W114" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>25.925000000000001</v>
       </c>
-      <c r="X114" s="8">
+      <c r="X114" s="12">
         <f t="shared" si="29"/>
-        <v>256.64317705313192</v>
-      </c>
-      <c r="Y114" s="9">
-        <f t="shared" si="37"/>
-        <v>3.9611235760355593E-2</v>
-      </c>
-      <c r="Z114" s="8">
+        <v>19.08700064086554</v>
+      </c>
+      <c r="Y114" s="8">
+        <f t="shared" si="30"/>
+        <v>275.73017769399746</v>
+      </c>
+      <c r="Z114" s="9">
         <f t="shared" si="38"/>
-        <v>6222.4068229468685</v>
-      </c>
-    </row>
-    <row r="115" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.2557192442410144E-2</v>
+      </c>
+      <c r="AA114" s="8">
+        <f t="shared" si="39"/>
+        <v>6203.3198223060026</v>
+      </c>
+    </row>
+    <row r="115" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>1</v>
       </c>
@@ -10679,7 +11138,7 @@
         <v>60.45</v>
       </c>
       <c r="P115" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>3.5729923045466392</v>
       </c>
       <c r="Q115" t="s">
@@ -10689,39 +11148,43 @@
         <v>138</v>
       </c>
       <c r="S115" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>64.022992304546648</v>
       </c>
       <c r="T115" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.3768385441837989</v>
       </c>
       <c r="U115" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.4889067977801547</v>
       </c>
       <c r="V115" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>6.3271403706706382</v>
       </c>
       <c r="W115" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>7.9050000000000002</v>
       </c>
-      <c r="X115" s="8">
+      <c r="X115" s="12">
         <f t="shared" si="29"/>
-        <v>78.255132675217283</v>
-      </c>
-      <c r="Y115" s="9">
-        <f t="shared" si="37"/>
-        <v>4.0073296126186646E-2</v>
-      </c>
-      <c r="Z115" s="8">
+        <v>5.819970687214739</v>
+      </c>
+      <c r="Y115" s="8">
+        <f t="shared" si="30"/>
+        <v>84.075103362432017</v>
+      </c>
+      <c r="Z115" s="9">
         <f t="shared" si="38"/>
-        <v>1874.5448673247827</v>
-      </c>
-    </row>
-    <row r="116" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.3053617043441225E-2</v>
+      </c>
+      <c r="AA115" s="8">
+        <f t="shared" si="39"/>
+        <v>1868.724896637568</v>
+      </c>
+    </row>
+    <row r="116" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>1</v>
       </c>
@@ -10764,7 +11227,7 @@
         <v>198.25</v>
       </c>
       <c r="P116" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>11.717877988029301</v>
       </c>
       <c r="Q116" t="s">
@@ -10774,39 +11237,43 @@
         <v>91</v>
       </c>
       <c r="S116" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>209.9678779880293</v>
       </c>
       <c r="T116" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.3768385441837987</v>
       </c>
       <c r="U116" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.4786470280847135</v>
       </c>
       <c r="V116" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>20.750299065102631</v>
       </c>
       <c r="W116" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>25.925000000000001</v>
       </c>
-      <c r="X116" s="8">
+      <c r="X116" s="12">
         <f t="shared" si="29"/>
-        <v>256.64317705313192</v>
-      </c>
-      <c r="Y116" s="9">
-        <f t="shared" si="37"/>
-        <v>3.9688112124508144E-2</v>
-      </c>
-      <c r="Z116" s="8">
+        <v>19.08700064086554</v>
+      </c>
+      <c r="Y116" s="8">
+        <f t="shared" si="30"/>
+        <v>275.73017769399746</v>
+      </c>
+      <c r="Z116" s="9">
         <f t="shared" si="38"/>
-        <v>6209.8568229468683</v>
-      </c>
-    </row>
-    <row r="117" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.2639786235830431E-2</v>
+      </c>
+      <c r="AA116" s="8">
+        <f t="shared" si="39"/>
+        <v>6190.7698223060024</v>
+      </c>
+    </row>
+    <row r="117" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>1</v>
       </c>
@@ -10849,7 +11316,7 @@
         <v>75.92</v>
       </c>
       <c r="P117" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>4.4873709803338437</v>
       </c>
       <c r="Q117" t="s">
@@ -10859,39 +11326,43 @@
         <v>91</v>
       </c>
       <c r="S117" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>80.407370980333852</v>
       </c>
       <c r="T117" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.3768385441837989</v>
       </c>
       <c r="U117" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.4835308298954584</v>
       </c>
       <c r="V117" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>7.9463440354229089</v>
       </c>
       <c r="W117" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>9.9280000000000008</v>
       </c>
-      <c r="X117" s="8">
+      <c r="X117" s="12">
         <f t="shared" si="29"/>
-        <v>98.28171501575676</v>
-      </c>
-      <c r="Y117" s="9">
-        <f t="shared" si="37"/>
-        <v>3.9871201801132974E-2</v>
-      </c>
-      <c r="Z117" s="8">
+        <v>7.309382540501951</v>
+      </c>
+      <c r="Y117" s="8">
+        <f t="shared" si="30"/>
+        <v>105.59109755625872</v>
+      </c>
+      <c r="Z117" s="9">
         <f t="shared" si="38"/>
-        <v>2366.6982849842434</v>
-      </c>
-    </row>
-    <row r="118" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.2836492610998353E-2</v>
+      </c>
+      <c r="AA117" s="8">
+        <f t="shared" si="39"/>
+        <v>2359.3889024437412</v>
+      </c>
+    </row>
+    <row r="118" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>1</v>
       </c>
@@ -10934,7 +11405,7 @@
         <v>54.145000000000003</v>
       </c>
       <c r="P118" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>3.2003253652552153</v>
       </c>
       <c r="Q118" t="s">
@@ -10944,39 +11415,43 @@
         <v>128</v>
       </c>
       <c r="S118" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>57.345325365255221</v>
       </c>
       <c r="T118" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.3768385441837989</v>
       </c>
       <c r="U118" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.4628909531952861</v>
       </c>
       <c r="V118" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>5.667212826632948</v>
       </c>
       <c r="W118" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>7.0805000000000007</v>
       </c>
-      <c r="X118" s="8">
+      <c r="X118" s="12">
         <f t="shared" si="29"/>
-        <v>70.093038191888169</v>
-      </c>
-      <c r="Y118" s="9">
-        <f t="shared" si="37"/>
-        <v>3.948770080554357E-2</v>
-      </c>
-      <c r="Z118" s="8">
+        <v>5.2129414865052448</v>
+      </c>
+      <c r="Y118" s="8">
+        <f t="shared" si="30"/>
+        <v>75.305979678393413</v>
+      </c>
+      <c r="Z118" s="9">
         <f t="shared" si="38"/>
-        <v>1704.9669618081118</v>
-      </c>
-    </row>
-    <row r="119" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.2424469977574514E-2</v>
+      </c>
+      <c r="AA118" s="8">
+        <f t="shared" si="39"/>
+        <v>1699.7540203216065</v>
+      </c>
+    </row>
+    <row r="119" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>1</v>
       </c>
@@ -11019,7 +11494,7 @@
         <v>319.15000000000003</v>
       </c>
       <c r="P119" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>18.86386259712258</v>
       </c>
       <c r="Q119" t="s">
@@ -11029,39 +11504,43 @@
         <v>128</v>
       </c>
       <c r="S119" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>338.01386259712262</v>
       </c>
       <c r="T119" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.3768385441837989</v>
       </c>
       <c r="U119" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.4825169412154502</v>
       </c>
       <c r="V119" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>33.404579806443905</v>
       </c>
       <c r="W119" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>41.735000000000007</v>
       </c>
-      <c r="X119" s="8">
+      <c r="X119" s="12">
         <f t="shared" si="29"/>
-        <v>413.15344240356654</v>
-      </c>
-      <c r="Y119" s="9">
-        <f t="shared" si="37"/>
-        <v>3.9736990959447403E-2</v>
-      </c>
-      <c r="Z119" s="8">
+        <v>30.726942015295016</v>
+      </c>
+      <c r="Y119" s="8">
+        <f t="shared" si="30"/>
+        <v>443.88038441886158</v>
+      </c>
+      <c r="Z119" s="9">
         <f t="shared" si="38"/>
-        <v>9984.0465575964336</v>
-      </c>
-    </row>
-    <row r="120" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.2692300274964561E-2</v>
+      </c>
+      <c r="AA119" s="8">
+        <f t="shared" si="39"/>
+        <v>9953.3196155811384</v>
+      </c>
+    </row>
+    <row r="120" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>1</v>
       </c>
@@ -11104,7 +11583,7 @@
         <v>82.225000000000009</v>
       </c>
       <c r="P120" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>4.8600379196252677</v>
       </c>
       <c r="Q120" t="s">
@@ -11114,39 +11593,43 @@
         <v>138</v>
       </c>
       <c r="S120" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>87.085037919625279</v>
       </c>
       <c r="T120" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.3768385441837989</v>
       </c>
       <c r="U120" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.5014661710280222</v>
       </c>
       <c r="V120" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>8.6062715794605982</v>
       </c>
       <c r="W120" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>10.752500000000001</v>
       </c>
-      <c r="X120" s="8">
+      <c r="X120" s="12">
         <f t="shared" si="29"/>
-        <v>106.44380949908587</v>
-      </c>
-      <c r="Y120" s="9">
-        <f t="shared" si="37"/>
-        <v>4.0354782385823212E-2</v>
-      </c>
-      <c r="Z120" s="8">
+        <v>7.9164117412114452</v>
+      </c>
+      <c r="Y120" s="8">
+        <f t="shared" si="30"/>
+        <v>114.36022124029732</v>
+      </c>
+      <c r="Z120" s="9">
         <f t="shared" si="38"/>
-        <v>2531.2561905009138</v>
-      </c>
-    </row>
-    <row r="121" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.3356037927094561E-2</v>
+      </c>
+      <c r="AA120" s="8">
+        <f t="shared" si="39"/>
+        <v>2523.3397787597023</v>
+      </c>
+    </row>
+    <row r="121" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>1</v>
       </c>
@@ -11189,7 +11672,7 @@
         <v>60.45</v>
       </c>
       <c r="P121" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>3.5729923045466392</v>
       </c>
       <c r="Q121" t="s">
@@ -11199,39 +11682,43 @@
         <v>91</v>
       </c>
       <c r="S121" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>64.022992304546648</v>
       </c>
       <c r="T121" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.3768385441837989</v>
       </c>
       <c r="U121" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.4889067977801547</v>
       </c>
       <c r="V121" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>6.3271403706706382</v>
       </c>
       <c r="W121" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>7.9050000000000002</v>
       </c>
-      <c r="X121" s="8">
+      <c r="X121" s="12">
         <f t="shared" si="29"/>
-        <v>78.255132675217283</v>
-      </c>
-      <c r="Y121" s="9">
-        <f t="shared" si="37"/>
-        <v>4.0073296126186646E-2</v>
-      </c>
-      <c r="Z121" s="8">
+        <v>5.819970687214739</v>
+      </c>
+      <c r="Y121" s="8">
+        <f t="shared" si="30"/>
+        <v>84.075103362432017</v>
+      </c>
+      <c r="Z121" s="9">
         <f t="shared" si="38"/>
-        <v>1874.5448673247827</v>
-      </c>
-    </row>
-    <row r="122" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.3053617043441225E-2</v>
+      </c>
+      <c r="AA121" s="8">
+        <f t="shared" si="39"/>
+        <v>1868.724896637568</v>
+      </c>
+    </row>
+    <row r="122" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>1</v>
       </c>
@@ -11274,7 +11761,7 @@
         <v>75.92</v>
       </c>
       <c r="P122" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>4.4873709803338437</v>
       </c>
       <c r="Q122" t="s">
@@ -11284,39 +11771,43 @@
         <v>91</v>
       </c>
       <c r="S122" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>80.407370980333852</v>
       </c>
       <c r="T122" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.3768385441837989</v>
       </c>
       <c r="U122" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.4835308298954584</v>
       </c>
       <c r="V122" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>7.9463440354229089</v>
       </c>
       <c r="W122" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>9.9280000000000008</v>
       </c>
-      <c r="X122" s="8">
+      <c r="X122" s="12">
         <f t="shared" si="29"/>
-        <v>98.28171501575676</v>
-      </c>
-      <c r="Y122" s="9">
-        <f t="shared" si="37"/>
-        <v>3.9749774527001611E-2</v>
-      </c>
-      <c r="Z122" s="8">
+        <v>7.309382540501951</v>
+      </c>
+      <c r="Y122" s="8">
+        <f t="shared" si="30"/>
+        <v>105.59109755625872</v>
+      </c>
+      <c r="Z122" s="9">
         <f t="shared" si="38"/>
-        <v>2374.2282849842436</v>
-      </c>
-    </row>
-    <row r="123" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.2706034578731213E-2</v>
+      </c>
+      <c r="AA122" s="8">
+        <f t="shared" si="39"/>
+        <v>2366.9189024437414</v>
+      </c>
+    </row>
+    <row r="123" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>1</v>
       </c>
@@ -11359,7 +11850,7 @@
         <v>54.145000000000003</v>
       </c>
       <c r="P123" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>3.2003253652552153</v>
       </c>
       <c r="Q123" t="s">
@@ -11369,39 +11860,43 @@
         <v>128</v>
       </c>
       <c r="S123" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>57.345325365255221</v>
       </c>
       <c r="T123" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.3768385441837989</v>
       </c>
       <c r="U123" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.4628909531952861</v>
       </c>
       <c r="V123" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>5.667212826632948</v>
       </c>
       <c r="W123" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>7.0805000000000007</v>
       </c>
-      <c r="X123" s="8">
+      <c r="X123" s="12">
         <f t="shared" si="29"/>
-        <v>70.093038191888169</v>
-      </c>
-      <c r="Y123" s="9">
-        <f t="shared" si="37"/>
-        <v>3.948770080554357E-2</v>
-      </c>
-      <c r="Z123" s="8">
+        <v>5.2129414865052448</v>
+      </c>
+      <c r="Y123" s="8">
+        <f t="shared" si="30"/>
+        <v>75.305979678393413</v>
+      </c>
+      <c r="Z123" s="9">
         <f t="shared" si="38"/>
-        <v>1704.9669618081118</v>
-      </c>
-    </row>
-    <row r="124" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.2424469977574514E-2</v>
+      </c>
+      <c r="AA123" s="8">
+        <f t="shared" si="39"/>
+        <v>1699.7540203216065</v>
+      </c>
+    </row>
+    <row r="124" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>2</v>
       </c>
@@ -11444,7 +11939,7 @@
         <v>120.9</v>
       </c>
       <c r="P124" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>7.1459846090932784</v>
       </c>
       <c r="Q124" t="s">
@@ -11454,39 +11949,43 @@
         <v>91</v>
       </c>
       <c r="S124" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>128.0459846090933</v>
       </c>
       <c r="T124" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.3768385441837989</v>
       </c>
       <c r="U124" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.4889067977801547</v>
       </c>
       <c r="V124" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>12.654280741341276</v>
       </c>
       <c r="W124" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>15.81</v>
       </c>
-      <c r="X124" s="8">
+      <c r="X124" s="12">
         <f t="shared" si="29"/>
-        <v>156.51026535043457</v>
-      </c>
-      <c r="Y124" s="9">
-        <f t="shared" si="37"/>
-        <v>3.8568325616174119E-2</v>
-      </c>
-      <c r="Z124" s="8">
+        <v>11.639941374429478</v>
+      </c>
+      <c r="Y124" s="8">
+        <f t="shared" si="30"/>
+        <v>168.15020672486403</v>
+      </c>
+      <c r="Z124" s="9">
         <f t="shared" si="38"/>
-        <v>3901.4897346495654</v>
-      </c>
-    </row>
-    <row r="125" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.1436719252061126E-2</v>
+      </c>
+      <c r="AA124" s="8">
+        <f t="shared" si="39"/>
+        <v>3889.8497932751361</v>
+      </c>
+    </row>
+    <row r="125" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>2</v>
       </c>
@@ -11536,39 +12035,43 @@
         <v>129</v>
       </c>
       <c r="S125" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>602.10299999999995</v>
       </c>
       <c r="T125" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>4.4353812154696133</v>
       </c>
       <c r="U125" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>4.7409685039370073</v>
       </c>
       <c r="V125" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>18.471167856312668</v>
       </c>
       <c r="W125" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>23.077500000000001</v>
       </c>
-      <c r="X125" s="8">
+      <c r="X125" s="12">
         <f t="shared" si="29"/>
-        <v>643.65166785631266</v>
-      </c>
-      <c r="Y125" s="9">
-        <f t="shared" si="37"/>
-        <v>0.10585679689762395</v>
-      </c>
-      <c r="Z125" s="8">
+        <v>16.990559586868834</v>
+      </c>
+      <c r="Y125" s="8">
+        <f t="shared" si="30"/>
+        <v>660.64222744318147</v>
+      </c>
+      <c r="Z125" s="9">
         <f t="shared" si="38"/>
-        <v>5436.7483321436866</v>
-      </c>
-    </row>
-    <row r="126" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.10865111299308952</v>
+      </c>
+      <c r="AA125" s="8">
+        <f t="shared" si="39"/>
+        <v>5419.7577725568181</v>
+      </c>
+    </row>
+    <row r="126" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>1</v>
       </c>
@@ -11618,32 +12121,35 @@
         <v>206</v>
       </c>
       <c r="S126" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>773.46676573480784</v>
       </c>
       <c r="T126" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.34054673229930998</v>
       </c>
       <c r="U126" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.36143306810037751</v>
       </c>
       <c r="V126" s="8"/>
-      <c r="X126" s="8">
+      <c r="X126" s="12">
         <f t="shared" si="29"/>
-        <v>773.46676573480784</v>
-      </c>
-      <c r="Y126" s="9">
-        <f t="shared" si="37"/>
-        <v>4.4605926512964696E-2</v>
-      </c>
-      <c r="Z126" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y126" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z126" s="9">
         <f t="shared" si="38"/>
-        <v>16566.533234265193</v>
-      </c>
-    </row>
-    <row r="127" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="AA126" s="8">
+        <f t="shared" si="39"/>
+        <v>17340</v>
+      </c>
+    </row>
+    <row r="127" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>4</v>
       </c>
@@ -11697,7 +12203,7 @@
         <v>41</v>
       </c>
       <c r="S127" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>307.94584381242578</v>
       </c>
       <c r="T127" s="8">
@@ -11705,31 +12211,35 @@
         <v>3.6769652992528452</v>
       </c>
       <c r="U127" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>4.1059445841656768</v>
       </c>
       <c r="V127" s="8">
-        <f t="shared" ref="V127:V163" si="42">H127*0.136067534853132</f>
+        <f t="shared" ref="V127:V163" si="43">H127*0.136067534853132</f>
         <v>11.395656043949804</v>
       </c>
       <c r="W127" s="4">
-        <f t="shared" ref="W127:W163" si="43">H127*0.17</f>
+        <f t="shared" ref="W127:W163" si="44">H127*0.17</f>
         <v>14.237500000000001</v>
       </c>
-      <c r="X127" s="8">
+      <c r="X127" s="12">
         <f t="shared" si="29"/>
-        <v>333.57899985637562</v>
-      </c>
-      <c r="Y127" s="9">
-        <f t="shared" si="37"/>
-        <v>0.10996505681766132</v>
-      </c>
-      <c r="Z127" s="8">
+        <v>10.482205269983535</v>
+      </c>
+      <c r="Y127" s="8">
+        <f t="shared" si="30"/>
+        <v>344.06120512635914</v>
+      </c>
+      <c r="Z127" s="9">
         <f t="shared" si="38"/>
-        <v>2699.9210001436245</v>
-      </c>
-    </row>
-    <row r="128" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.11342053902302922</v>
+      </c>
+      <c r="AA127" s="8">
+        <f t="shared" si="39"/>
+        <v>2689.4387948736407</v>
+      </c>
+    </row>
+    <row r="128" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>4</v>
       </c>
@@ -11783,39 +12293,43 @@
         <v>41</v>
       </c>
       <c r="S128" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>346.20584381242577</v>
       </c>
       <c r="T128" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>4.1338011201483678</v>
       </c>
       <c r="U128" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>4.6160779174990099</v>
       </c>
       <c r="V128" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>11.395656043949804</v>
       </c>
       <c r="W128" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>14.237500000000001</v>
       </c>
-      <c r="X128" s="8">
+      <c r="X128" s="12">
         <f t="shared" si="29"/>
-        <v>371.83899985637561</v>
-      </c>
-      <c r="Y128" s="9">
-        <f t="shared" si="37"/>
-        <v>0.12257755063668226</v>
-      </c>
-      <c r="Z128" s="8">
+        <v>10.482205269983535</v>
+      </c>
+      <c r="Y128" s="8">
+        <f t="shared" si="30"/>
+        <v>382.32120512635913</v>
+      </c>
+      <c r="Z128" s="9">
         <f t="shared" si="38"/>
-        <v>2661.6610001436243</v>
-      </c>
-    </row>
-    <row r="129" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.12603303284205014</v>
+      </c>
+      <c r="AA128" s="8">
+        <f t="shared" si="39"/>
+        <v>2651.178794873641</v>
+      </c>
+    </row>
+    <row r="129" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>4</v>
       </c>
@@ -11869,39 +12383,43 @@
         <v>41</v>
       </c>
       <c r="S129" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>351.86893091703473</v>
       </c>
       <c r="T129" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>3.3849825004043743</v>
       </c>
       <c r="U129" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>3.6961022155150705</v>
       </c>
       <c r="V129" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>14.144220247983071</v>
       </c>
       <c r="W129" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>17.671500000000002</v>
       </c>
-      <c r="X129" s="8">
+      <c r="X129" s="12">
         <f t="shared" si="29"/>
-        <v>383.68465116501778</v>
-      </c>
-      <c r="Y129" s="9">
-        <f t="shared" si="37"/>
-        <v>0.10173749540347087</v>
-      </c>
-      <c r="Z129" s="8">
+        <v>13.010450600773593</v>
+      </c>
+      <c r="Y129" s="8">
+        <f t="shared" si="30"/>
+        <v>396.69510176579138</v>
+      </c>
+      <c r="Z129" s="9">
         <f t="shared" si="38"/>
-        <v>3387.6353488349823</v>
-      </c>
-    </row>
-    <row r="130" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.10518733540664578</v>
+      </c>
+      <c r="AA129" s="8">
+        <f t="shared" si="39"/>
+        <v>3374.6248982342086</v>
+      </c>
+    </row>
+    <row r="130" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>4</v>
       </c>
@@ -11955,39 +12473,43 @@
         <v>41</v>
       </c>
       <c r="S130" s="8">
-        <f t="shared" ref="S130:S163" si="44">SUM(M130+O130+P130)</f>
+        <f t="shared" ref="S130:S163" si="45">SUM(M130+O130+P130)</f>
         <v>486.4086976704084</v>
       </c>
       <c r="T130" s="8">
-        <f t="shared" ref="T130:T163" si="45">SUM(M130+O130+P130)/H130</f>
+        <f t="shared" ref="T130:T163" si="46">SUM(M130+O130+P130)/H130</f>
         <v>3.7852816939331393</v>
       </c>
       <c r="U130" s="8">
-        <f t="shared" ref="U130:U163" si="46">SUM(M130+O130+P130)/I130</f>
+        <f t="shared" ref="U130:U163" si="47">SUM(M130+O130+P130)/I130</f>
         <v>4.1221076073763427</v>
       </c>
       <c r="V130" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>17.484678228627462</v>
       </c>
       <c r="W130" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>21.845000000000002</v>
       </c>
-      <c r="X130" s="8">
+      <c r="X130" s="12">
         <f t="shared" si="29"/>
-        <v>525.73837589903587</v>
-      </c>
-      <c r="Y130" s="9">
-        <f t="shared" ref="Y130:Y161" si="47">X130/J130</f>
-        <v>0.10831033702081497</v>
-      </c>
-      <c r="Z130" s="8">
-        <f t="shared" ref="Z130:Z163" si="48">J130-X130</f>
-        <v>4328.2616241009637</v>
-      </c>
-    </row>
-    <row r="131" spans="1:26" x14ac:dyDescent="0.25">
+        <v>16.083144802303096</v>
+      </c>
+      <c r="Y130" s="8">
+        <f t="shared" si="30"/>
+        <v>541.82152070133895</v>
+      </c>
+      <c r="Z130" s="9">
+        <f t="shared" ref="Z130:Z161" si="48">Y130/J130</f>
+        <v>0.11162371666694251</v>
+      </c>
+      <c r="AA130" s="8">
+        <f t="shared" ref="AA130:AA163" si="49">J130-Y130</f>
+        <v>4312.1784792986609</v>
+      </c>
+    </row>
+    <row r="131" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>4</v>
       </c>
@@ -12041,39 +12563,43 @@
         <v>41</v>
       </c>
       <c r="S131" s="8">
+        <f t="shared" si="45"/>
+        <v>466.07584381242577</v>
+      </c>
+      <c r="T131" s="8">
+        <f t="shared" si="46"/>
+        <v>5.56508470223792</v>
+      </c>
+      <c r="U131" s="8">
+        <f t="shared" si="47"/>
+        <v>6.2143445841656773</v>
+      </c>
+      <c r="V131" s="8">
+        <f t="shared" si="43"/>
+        <v>11.395656043949804</v>
+      </c>
+      <c r="W131" s="4">
         <f t="shared" si="44"/>
-        <v>466.07584381242577</v>
-      </c>
-      <c r="T131" s="8">
-        <f t="shared" si="45"/>
-        <v>5.56508470223792</v>
-      </c>
-      <c r="U131" s="8">
-        <f t="shared" si="46"/>
-        <v>6.2143445841656773</v>
-      </c>
-      <c r="V131" s="8">
-        <f t="shared" si="42"/>
-        <v>11.395656043949804</v>
-      </c>
-      <c r="W131" s="4">
-        <f t="shared" si="43"/>
         <v>14.237500000000001</v>
       </c>
-      <c r="X131" s="8">
-        <f t="shared" ref="X131:X163" si="49">S131+V131+W131</f>
-        <v>491.70899985637561</v>
-      </c>
-      <c r="Y131" s="9">
-        <f t="shared" si="47"/>
-        <v>0.16209296187782285</v>
-      </c>
-      <c r="Z131" s="8">
+      <c r="X131" s="12">
+        <f t="shared" ref="X131:X163" si="50">IFERROR(IF(D131="TRANSFERENCIA",0,H131*(SUMIF(D:D,"TRANSFERENCIA",M:M)+SUMIF(D:D,"TRANSFERENCIA",O:O))/(SUMIF(D:D,"BONIFICAÇÃO",H:H)+SUMIF(D:D,"VENDA",H:H))),0)</f>
+        <v>10.482205269983535</v>
+      </c>
+      <c r="Y131" s="8">
+        <f t="shared" ref="Y131:Y163" si="51">S131+V131+W131+X131</f>
+        <v>502.19120512635914</v>
+      </c>
+      <c r="Z131" s="9">
         <f t="shared" si="48"/>
-        <v>2541.7910001436244</v>
-      </c>
-    </row>
-    <row r="132" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.16554844408319075</v>
+      </c>
+      <c r="AA131" s="8">
+        <f t="shared" si="49"/>
+        <v>2531.3087948736411</v>
+      </c>
+    </row>
+    <row r="132" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>4</v>
       </c>
@@ -12127,39 +12653,43 @@
         <v>41</v>
       </c>
       <c r="S132" s="8">
+        <f t="shared" si="45"/>
+        <v>697.08265036000239</v>
+      </c>
+      <c r="T132" s="8">
+        <f t="shared" si="46"/>
+        <v>3.3570077070069941</v>
+      </c>
+      <c r="U132" s="8">
+        <f t="shared" si="47"/>
+        <v>3.645829761297084</v>
+      </c>
+      <c r="V132" s="8">
+        <f t="shared" si="43"/>
+        <v>28.254423612252861</v>
+      </c>
+      <c r="W132" s="4">
         <f t="shared" si="44"/>
-        <v>697.08265036000239</v>
-      </c>
-      <c r="T132" s="8">
-        <f t="shared" si="45"/>
-        <v>3.3570077070069941</v>
-      </c>
-      <c r="U132" s="8">
-        <f t="shared" si="46"/>
-        <v>3.645829761297084</v>
-      </c>
-      <c r="V132" s="8">
-        <f t="shared" si="42"/>
-        <v>28.254423612252861</v>
-      </c>
-      <c r="W132" s="4">
-        <f t="shared" si="43"/>
         <v>35.300500000000007</v>
       </c>
-      <c r="X132" s="8">
+      <c r="X132" s="12">
+        <f t="shared" si="50"/>
+        <v>25.989611036562163</v>
+      </c>
+      <c r="Y132" s="8">
+        <f t="shared" si="51"/>
+        <v>786.62718500881738</v>
+      </c>
+      <c r="Z132" s="9">
+        <f t="shared" si="48"/>
+        <v>0.10802647491126059</v>
+      </c>
+      <c r="AA132" s="8">
         <f t="shared" si="49"/>
-        <v>760.63757397225527</v>
-      </c>
-      <c r="Y132" s="9">
-        <f t="shared" si="47"/>
-        <v>0.1044573558697376</v>
-      </c>
-      <c r="Z132" s="8">
-        <f t="shared" si="48"/>
-        <v>6521.1624260277449</v>
-      </c>
-    </row>
-    <row r="133" spans="1:26" x14ac:dyDescent="0.25">
+        <v>6495.1728149911833</v>
+      </c>
+    </row>
+    <row r="133" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>4</v>
       </c>
@@ -12213,39 +12743,43 @@
         <v>41</v>
       </c>
       <c r="S133" s="8">
+        <f t="shared" si="45"/>
+        <v>374.35619389793521</v>
+      </c>
+      <c r="T133" s="8">
+        <f t="shared" si="46"/>
+        <v>3.8063669943867335</v>
+      </c>
+      <c r="U133" s="8">
+        <f t="shared" si="47"/>
+        <v>4.1780825211823132</v>
+      </c>
+      <c r="V133" s="8">
+        <f t="shared" si="43"/>
+        <v>13.382242052805532</v>
+      </c>
+      <c r="W133" s="4">
         <f t="shared" si="44"/>
-        <v>374.35619389793521</v>
-      </c>
-      <c r="T133" s="8">
-        <f t="shared" si="45"/>
-        <v>3.8063669943867335</v>
-      </c>
-      <c r="U133" s="8">
-        <f t="shared" si="46"/>
-        <v>4.1780825211823132</v>
-      </c>
-      <c r="V133" s="8">
-        <f t="shared" si="42"/>
-        <v>13.382242052805532</v>
-      </c>
-      <c r="W133" s="4">
-        <f t="shared" si="43"/>
         <v>16.7195</v>
       </c>
-      <c r="X133" s="8">
+      <c r="X133" s="12">
+        <f t="shared" si="50"/>
+        <v>12.309550905109022</v>
+      </c>
+      <c r="Y133" s="8">
+        <f t="shared" si="51"/>
+        <v>416.76748685584971</v>
+      </c>
+      <c r="Z133" s="9">
+        <f t="shared" si="48"/>
+        <v>0.11811262578951462</v>
+      </c>
+      <c r="AA133" s="8">
         <f t="shared" si="49"/>
-        <v>404.4579359507407</v>
-      </c>
-      <c r="Y133" s="9">
-        <f t="shared" si="47"/>
-        <v>0.11462407779681817</v>
-      </c>
-      <c r="Z133" s="8">
-        <f t="shared" si="48"/>
-        <v>3124.1020640492593</v>
-      </c>
-    </row>
-    <row r="134" spans="1:26" x14ac:dyDescent="0.25">
+        <v>3111.7925131441502</v>
+      </c>
+    </row>
+    <row r="134" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>4</v>
       </c>
@@ -12299,39 +12833,43 @@
         <v>41</v>
       </c>
       <c r="S134" s="8">
+        <f t="shared" si="45"/>
+        <v>538.92883376686882</v>
+      </c>
+      <c r="T134" s="8">
+        <f t="shared" si="46"/>
+        <v>4.390458930890988</v>
+      </c>
+      <c r="U134" s="8">
+        <f t="shared" si="47"/>
+        <v>4.7274459102356916</v>
+      </c>
+      <c r="V134" s="8">
+        <f t="shared" si="43"/>
+        <v>16.702289903221953</v>
+      </c>
+      <c r="W134" s="4">
         <f t="shared" si="44"/>
-        <v>538.92883376686882</v>
-      </c>
-      <c r="T134" s="8">
-        <f t="shared" si="45"/>
-        <v>4.390458930890988</v>
-      </c>
-      <c r="U134" s="8">
-        <f t="shared" si="46"/>
-        <v>4.7274459102356916</v>
-      </c>
-      <c r="V134" s="8">
-        <f t="shared" si="42"/>
-        <v>16.702289903221953</v>
-      </c>
-      <c r="W134" s="4">
-        <f t="shared" si="43"/>
         <v>20.867500000000003</v>
       </c>
-      <c r="X134" s="8">
+      <c r="X134" s="12">
+        <f t="shared" si="50"/>
+        <v>15.363471007647508</v>
+      </c>
+      <c r="Y134" s="8">
+        <f t="shared" si="51"/>
+        <v>591.86209467773824</v>
+      </c>
+      <c r="Z134" s="9">
+        <f t="shared" si="48"/>
+        <v>0.14341913702571926</v>
+      </c>
+      <c r="AA134" s="8">
         <f t="shared" si="49"/>
-        <v>576.49862367009075</v>
-      </c>
-      <c r="Y134" s="9">
-        <f t="shared" si="47"/>
-        <v>0.13969628372348811</v>
-      </c>
-      <c r="Z134" s="8">
-        <f t="shared" si="48"/>
-        <v>3550.3013763299095</v>
-      </c>
-    </row>
-    <row r="135" spans="1:26" x14ac:dyDescent="0.25">
+        <v>3534.9379053222619</v>
+      </c>
+    </row>
+    <row r="135" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>4</v>
       </c>
@@ -12385,39 +12923,43 @@
         <v>41</v>
       </c>
       <c r="S135" s="8">
+        <f t="shared" si="45"/>
+        <v>398.11992756851572</v>
+      </c>
+      <c r="T135" s="8">
+        <f t="shared" si="46"/>
+        <v>3.4041892053742258</v>
+      </c>
+      <c r="U135" s="8">
+        <f t="shared" si="47"/>
+        <v>3.6794817705038421</v>
+      </c>
+      <c r="V135" s="8">
+        <f t="shared" si="43"/>
+        <v>15.913098201073788</v>
+      </c>
+      <c r="W135" s="4">
         <f t="shared" si="44"/>
-        <v>398.11992756851572</v>
-      </c>
-      <c r="T135" s="8">
-        <f t="shared" si="45"/>
-        <v>3.4041892053742258</v>
-      </c>
-      <c r="U135" s="8">
-        <f t="shared" si="46"/>
-        <v>3.6794817705038421</v>
-      </c>
-      <c r="V135" s="8">
-        <f t="shared" si="42"/>
-        <v>15.913098201073788</v>
-      </c>
-      <c r="W135" s="4">
-        <f t="shared" si="43"/>
         <v>19.881500000000003</v>
       </c>
-      <c r="X135" s="8">
+      <c r="X135" s="12">
+        <f t="shared" si="50"/>
+        <v>14.637539179994917</v>
+      </c>
+      <c r="Y135" s="8">
+        <f t="shared" si="51"/>
+        <v>448.55206494958446</v>
+      </c>
+      <c r="Z135" s="9">
+        <f t="shared" si="48"/>
+        <v>9.8267120800764246E-2</v>
+      </c>
+      <c r="AA135" s="8">
         <f t="shared" si="49"/>
-        <v>433.91452576958955</v>
-      </c>
-      <c r="Y135" s="9">
-        <f t="shared" si="47"/>
-        <v>9.5060383070132801E-2</v>
-      </c>
-      <c r="Z135" s="8">
-        <f t="shared" si="48"/>
-        <v>4130.7054742304099</v>
-      </c>
-    </row>
-    <row r="136" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4116.0679350504151</v>
+      </c>
+    </row>
+    <row r="136" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>2</v>
       </c>
@@ -12471,39 +13013,43 @@
         <v>41</v>
       </c>
       <c r="S136" s="8">
+        <f t="shared" si="45"/>
+        <v>1404.3764372530152</v>
+      </c>
+      <c r="T136" s="8">
+        <f t="shared" si="46"/>
+        <v>3.3718521902833496</v>
+      </c>
+      <c r="U136" s="8">
+        <f t="shared" si="47"/>
+        <v>3.5825929521760593</v>
+      </c>
+      <c r="V136" s="8">
+        <f t="shared" si="43"/>
+        <v>56.67212826632948</v>
+      </c>
+      <c r="W136" s="4">
         <f t="shared" si="44"/>
-        <v>1404.3764372530152</v>
-      </c>
-      <c r="T136" s="8">
-        <f t="shared" si="45"/>
-        <v>3.3718521902833496</v>
-      </c>
-      <c r="U136" s="8">
-        <f t="shared" si="46"/>
-        <v>3.5825929521760593</v>
-      </c>
-      <c r="V136" s="8">
-        <f t="shared" si="42"/>
-        <v>56.67212826632948</v>
-      </c>
-      <c r="W136" s="4">
-        <f t="shared" si="43"/>
         <v>70.805000000000007</v>
       </c>
-      <c r="X136" s="8">
+      <c r="X136" s="12">
+        <f t="shared" si="50"/>
+        <v>52.129414865052439</v>
+      </c>
+      <c r="Y136" s="8">
+        <f t="shared" si="51"/>
+        <v>1583.9829803843973</v>
+      </c>
+      <c r="Z136" s="9">
+        <f t="shared" si="48"/>
+        <v>9.9125321058374252E-2</v>
+      </c>
+      <c r="AA136" s="8">
         <f t="shared" si="49"/>
-        <v>1531.8535655193448</v>
-      </c>
-      <c r="Y136" s="9">
-        <f t="shared" si="47"/>
-        <v>9.5863073263369847E-2</v>
-      </c>
-      <c r="Z136" s="8">
-        <f t="shared" si="48"/>
-        <v>14447.746434480656</v>
-      </c>
-    </row>
-    <row r="137" spans="1:26" x14ac:dyDescent="0.25">
+        <v>14395.617019615604</v>
+      </c>
+    </row>
+    <row r="137" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>2</v>
       </c>
@@ -12553,39 +13099,43 @@
         <v>41</v>
       </c>
       <c r="S137" s="8">
+        <f t="shared" si="45"/>
+        <v>1504.9652932469171</v>
+      </c>
+      <c r="T137" s="8">
+        <f t="shared" si="46"/>
+        <v>1.5808458962677701</v>
+      </c>
+      <c r="U137" s="8">
+        <f t="shared" si="47"/>
+        <v>1.6796487647845058</v>
+      </c>
+      <c r="V137" s="8">
+        <f t="shared" si="43"/>
+        <v>129.53629318018167</v>
+      </c>
+      <c r="W137" s="4">
         <f t="shared" si="44"/>
-        <v>1504.9652932469171</v>
-      </c>
-      <c r="T137" s="8">
-        <f t="shared" si="45"/>
-        <v>1.5808458962677701</v>
-      </c>
-      <c r="U137" s="8">
-        <f t="shared" si="46"/>
-        <v>1.6796487647845058</v>
-      </c>
-      <c r="V137" s="8">
-        <f t="shared" si="42"/>
-        <v>129.53629318018167</v>
-      </c>
-      <c r="W137" s="4">
-        <f t="shared" si="43"/>
         <v>161.84</v>
       </c>
-      <c r="X137" s="8">
+      <c r="X137" s="12">
+        <f t="shared" si="50"/>
+        <v>119.15294826297701</v>
+      </c>
+      <c r="Y137" s="8">
+        <f t="shared" si="51"/>
+        <v>1915.4945346900756</v>
+      </c>
+      <c r="Z137" s="9">
+        <f t="shared" si="48"/>
+        <v>6.7405692804059322E-2</v>
+      </c>
+      <c r="AA137" s="8">
         <f t="shared" si="49"/>
-        <v>1796.3415864270987</v>
-      </c>
-      <c r="Y137" s="9">
-        <f t="shared" si="47"/>
-        <v>6.3212735381389523E-2</v>
-      </c>
-      <c r="Z137" s="8">
-        <f t="shared" si="48"/>
-        <v>26621.058413572904</v>
-      </c>
-    </row>
-    <row r="138" spans="1:26" x14ac:dyDescent="0.25">
+        <v>26501.905465309927</v>
+      </c>
+    </row>
+    <row r="138" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>2</v>
       </c>
@@ -12639,39 +13189,43 @@
         <v>41</v>
       </c>
       <c r="S138" s="8">
+        <f t="shared" si="45"/>
+        <v>421.16742882600681</v>
+      </c>
+      <c r="T138" s="8">
+        <f t="shared" si="46"/>
+        <v>3.3162789671339121</v>
+      </c>
+      <c r="U138" s="8">
+        <f t="shared" si="47"/>
+        <v>3.5097285735500567</v>
+      </c>
+      <c r="V138" s="8">
+        <f t="shared" si="43"/>
+        <v>17.280576926347763</v>
+      </c>
+      <c r="W138" s="4">
         <f t="shared" si="44"/>
-        <v>421.16742882600681</v>
-      </c>
-      <c r="T138" s="8">
-        <f t="shared" si="45"/>
-        <v>3.3162789671339121</v>
-      </c>
-      <c r="U138" s="8">
-        <f t="shared" si="46"/>
-        <v>3.5097285735500567</v>
-      </c>
-      <c r="V138" s="8">
-        <f t="shared" si="42"/>
-        <v>17.280576926347763</v>
-      </c>
-      <c r="W138" s="4">
-        <f t="shared" si="43"/>
         <v>21.59</v>
       </c>
-      <c r="X138" s="8">
+      <c r="X138" s="12">
+        <f t="shared" si="50"/>
+        <v>15.895403812392942</v>
+      </c>
+      <c r="Y138" s="8">
+        <f t="shared" si="51"/>
+        <v>475.93340956474748</v>
+      </c>
+      <c r="Z138" s="9">
+        <f t="shared" si="48"/>
+        <v>0.12971040269397893</v>
+      </c>
+      <c r="AA138" s="8">
         <f t="shared" si="49"/>
-        <v>460.03800575235454</v>
-      </c>
-      <c r="Y138" s="9">
-        <f t="shared" si="47"/>
-        <v>0.12537828566236633</v>
-      </c>
-      <c r="Z138" s="8">
-        <f t="shared" si="48"/>
-        <v>3209.1619942476455</v>
-      </c>
-    </row>
-    <row r="139" spans="1:26" x14ac:dyDescent="0.25">
+        <v>3193.2665904352525</v>
+      </c>
+    </row>
+    <row r="139" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>2</v>
       </c>
@@ -12725,39 +13279,43 @@
         <v>41</v>
       </c>
       <c r="S139" s="8">
+        <f t="shared" si="45"/>
+        <v>1047.3985720650171</v>
+      </c>
+      <c r="T139" s="8">
+        <f t="shared" si="46"/>
+        <v>3.2988931403622588</v>
+      </c>
+      <c r="U139" s="8">
+        <f t="shared" si="47"/>
+        <v>3.491328573550057</v>
+      </c>
+      <c r="V139" s="8">
+        <f t="shared" si="43"/>
+        <v>43.201442315869407</v>
+      </c>
+      <c r="W139" s="4">
         <f t="shared" si="44"/>
-        <v>1047.3985720650171</v>
-      </c>
-      <c r="T139" s="8">
-        <f t="shared" si="45"/>
-        <v>3.2988931403622588</v>
-      </c>
-      <c r="U139" s="8">
-        <f t="shared" si="46"/>
-        <v>3.491328573550057</v>
-      </c>
-      <c r="V139" s="8">
-        <f t="shared" si="42"/>
-        <v>43.201442315869407</v>
-      </c>
-      <c r="W139" s="4">
-        <f t="shared" si="43"/>
         <v>53.975000000000001</v>
       </c>
-      <c r="X139" s="8">
+      <c r="X139" s="12">
+        <f t="shared" si="50"/>
+        <v>39.738509530982355</v>
+      </c>
+      <c r="Y139" s="8">
+        <f t="shared" si="51"/>
+        <v>1184.3135239118687</v>
+      </c>
+      <c r="Z139" s="9">
+        <f t="shared" si="48"/>
+        <v>0.12910863664143341</v>
+      </c>
+      <c r="AA139" s="8">
         <f t="shared" si="49"/>
-        <v>1144.5750143808864</v>
-      </c>
-      <c r="Y139" s="9">
-        <f t="shared" si="47"/>
-        <v>0.12477651960982082</v>
-      </c>
-      <c r="Z139" s="8">
-        <f t="shared" si="48"/>
-        <v>8028.4249856191136</v>
-      </c>
-    </row>
-    <row r="140" spans="1:26" x14ac:dyDescent="0.25">
+        <v>7988.6864760881308</v>
+      </c>
+    </row>
+    <row r="140" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>2</v>
       </c>
@@ -12809,39 +13367,43 @@
         <v>41</v>
       </c>
       <c r="S140" s="8">
+        <f t="shared" si="45"/>
+        <v>360.05049624189849</v>
+      </c>
+      <c r="T140" s="8">
+        <f t="shared" si="46"/>
+        <v>4.0341792296011034</v>
+      </c>
+      <c r="U140" s="8">
+        <f t="shared" si="47"/>
+        <v>4.2863154314511727</v>
+      </c>
+      <c r="V140" s="8">
+        <f t="shared" si="43"/>
+        <v>12.144027485642031</v>
+      </c>
+      <c r="W140" s="4">
         <f t="shared" si="44"/>
-        <v>360.05049624189849</v>
-      </c>
-      <c r="T140" s="8">
-        <f t="shared" si="45"/>
-        <v>4.0341792296011034</v>
-      </c>
-      <c r="U140" s="8">
-        <f t="shared" si="46"/>
-        <v>4.2863154314511727</v>
-      </c>
-      <c r="V140" s="8">
-        <f t="shared" si="42"/>
-        <v>12.144027485642031</v>
-      </c>
-      <c r="W140" s="4">
-        <f t="shared" si="43"/>
         <v>15.172500000000001</v>
       </c>
-      <c r="X140" s="8">
+      <c r="X140" s="12">
+        <f t="shared" si="50"/>
+        <v>11.170588899654096</v>
+      </c>
+      <c r="Y140" s="8">
+        <f t="shared" si="51"/>
+        <v>398.53761262719462</v>
+      </c>
+      <c r="Z140" s="9">
+        <f t="shared" si="48"/>
+        <v>0.11270063276838306</v>
+      </c>
+      <c r="AA140" s="8">
         <f t="shared" si="49"/>
-        <v>387.36702372754053</v>
-      </c>
-      <c r="Y140" s="9">
-        <f t="shared" si="47"/>
-        <v>0.1095417529098736</v>
-      </c>
-      <c r="Z140" s="8">
-        <f t="shared" si="48"/>
-        <v>3148.8829762724595</v>
-      </c>
-    </row>
-    <row r="141" spans="1:26" x14ac:dyDescent="0.25">
+        <v>3137.7123873728056</v>
+      </c>
+    </row>
+    <row r="141" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>2</v>
       </c>
@@ -12895,39 +13457,43 @@
         <v>41</v>
       </c>
       <c r="S141" s="8">
+        <f t="shared" si="45"/>
+        <v>701.57114323901021</v>
+      </c>
+      <c r="T141" s="8">
+        <f t="shared" si="46"/>
+        <v>3.6827881534856179</v>
+      </c>
+      <c r="U141" s="8">
+        <f t="shared" si="47"/>
+        <v>3.8976174624389457</v>
+      </c>
+      <c r="V141" s="8">
+        <f t="shared" si="43"/>
+        <v>25.920865389521644</v>
+      </c>
+      <c r="W141" s="4">
         <f t="shared" si="44"/>
-        <v>701.57114323901021</v>
-      </c>
-      <c r="T141" s="8">
-        <f t="shared" si="45"/>
-        <v>3.6827881534856179</v>
-      </c>
-      <c r="U141" s="8">
-        <f t="shared" si="46"/>
-        <v>3.8976174624389457</v>
-      </c>
-      <c r="V141" s="8">
-        <f t="shared" si="42"/>
-        <v>25.920865389521644</v>
-      </c>
-      <c r="W141" s="4">
-        <f t="shared" si="43"/>
         <v>32.385000000000005</v>
       </c>
-      <c r="X141" s="8">
+      <c r="X141" s="12">
+        <f t="shared" si="50"/>
+        <v>23.843105718589413</v>
+      </c>
+      <c r="Y141" s="8">
+        <f t="shared" si="51"/>
+        <v>783.72011434712124</v>
+      </c>
+      <c r="Z141" s="9">
+        <f t="shared" si="48"/>
+        <v>0.14239618342729046</v>
+      </c>
+      <c r="AA141" s="8">
         <f t="shared" si="49"/>
-        <v>759.87700862853183</v>
-      </c>
-      <c r="Y141" s="9">
-        <f t="shared" si="47"/>
-        <v>0.13806406639567786</v>
-      </c>
-      <c r="Z141" s="8">
-        <f t="shared" si="48"/>
-        <v>4743.922991371468</v>
-      </c>
-    </row>
-    <row r="142" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4720.0798856528791</v>
+      </c>
+    </row>
+    <row r="142" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>2</v>
       </c>
@@ -12977,39 +13543,43 @@
         <v>41</v>
       </c>
       <c r="S142" s="8">
+        <f t="shared" si="45"/>
+        <v>3840</v>
+      </c>
+      <c r="T142" s="8">
+        <f t="shared" si="46"/>
+        <v>0.7469654528478058</v>
+      </c>
+      <c r="U142" s="8">
+        <f t="shared" si="47"/>
+        <v>0.79365079365079372</v>
+      </c>
+      <c r="V142" s="8">
+        <f t="shared" si="43"/>
+        <v>699.49598317298103</v>
+      </c>
+      <c r="W142" s="4">
         <f t="shared" si="44"/>
-        <v>3840</v>
-      </c>
-      <c r="T142" s="8">
-        <f t="shared" si="45"/>
-        <v>0.7469654528478058</v>
-      </c>
-      <c r="U142" s="8">
-        <f t="shared" si="46"/>
-        <v>0.79365079365079372</v>
-      </c>
-      <c r="V142" s="8">
-        <f t="shared" si="42"/>
-        <v>699.49598317298103</v>
-      </c>
-      <c r="W142" s="4">
-        <f t="shared" si="43"/>
         <v>873.93600000000015</v>
       </c>
-      <c r="X142" s="8">
+      <c r="X142" s="12">
+        <f t="shared" si="50"/>
+        <v>643.42592062007589</v>
+      </c>
+      <c r="Y142" s="8">
+        <f t="shared" si="51"/>
+        <v>6056.8579037930567</v>
+      </c>
+      <c r="Z142" s="9">
+        <f t="shared" si="48"/>
+        <v>3.5476984835345074E-2</v>
+      </c>
+      <c r="AA142" s="8">
         <f t="shared" si="49"/>
-        <v>5413.4319831729808</v>
-      </c>
-      <c r="Y142" s="9">
-        <f t="shared" si="47"/>
-        <v>3.1708230145853139E-2</v>
-      </c>
-      <c r="Z142" s="8">
-        <f t="shared" si="48"/>
-        <v>165312.96801682701</v>
-      </c>
-    </row>
-    <row r="143" spans="1:26" x14ac:dyDescent="0.25">
+        <v>164669.54209620695</v>
+      </c>
+    </row>
+    <row r="143" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>2</v>
       </c>
@@ -13059,39 +13629,43 @@
         <v>41</v>
       </c>
       <c r="S143" s="8">
+        <f t="shared" si="45"/>
+        <v>4160.0000000000009</v>
+      </c>
+      <c r="T143" s="8">
+        <f t="shared" si="46"/>
+        <v>0.74696545284780602</v>
+      </c>
+      <c r="U143" s="8">
+        <f t="shared" si="47"/>
+        <v>0.79365079365079372</v>
+      </c>
+      <c r="V143" s="8">
+        <f t="shared" si="43"/>
+        <v>757.78731510406271</v>
+      </c>
+      <c r="W143" s="4">
         <f t="shared" si="44"/>
-        <v>4160.0000000000009</v>
-      </c>
-      <c r="T143" s="8">
-        <f t="shared" si="45"/>
-        <v>0.74696545284780602</v>
-      </c>
-      <c r="U143" s="8">
-        <f t="shared" si="46"/>
-        <v>0.79365079365079372</v>
-      </c>
-      <c r="V143" s="8">
-        <f t="shared" si="42"/>
-        <v>757.78731510406271</v>
-      </c>
-      <c r="W143" s="4">
-        <f t="shared" si="43"/>
         <v>946.76400000000001</v>
       </c>
-      <c r="X143" s="8">
+      <c r="X143" s="12">
+        <f t="shared" si="50"/>
+        <v>697.0447473384155</v>
+      </c>
+      <c r="Y143" s="8">
+        <f t="shared" si="51"/>
+        <v>6561.5960624424797</v>
+      </c>
+      <c r="Z143" s="9">
+        <f t="shared" si="48"/>
+        <v>3.2957210561635482E-2</v>
+      </c>
+      <c r="AA143" s="8">
         <f t="shared" si="49"/>
-        <v>5864.5513151040641</v>
-      </c>
-      <c r="Y143" s="9">
-        <f t="shared" si="47"/>
-        <v>2.9456133950046131E-2</v>
-      </c>
-      <c r="Z143" s="8">
-        <f t="shared" si="48"/>
-        <v>193229.84868489593</v>
-      </c>
-    </row>
-    <row r="144" spans="1:26" x14ac:dyDescent="0.25">
+        <v>192532.8039375575</v>
+      </c>
+    </row>
+    <row r="144" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>2</v>
       </c>
@@ -13145,39 +13719,43 @@
         <v>41</v>
       </c>
       <c r="S144" s="8">
+        <f t="shared" si="45"/>
+        <v>1203.7512319311559</v>
+      </c>
+      <c r="T144" s="8">
+        <f t="shared" si="46"/>
+        <v>3.3718521902833496</v>
+      </c>
+      <c r="U144" s="8">
+        <f t="shared" si="47"/>
+        <v>3.5825929521760593</v>
+      </c>
+      <c r="V144" s="8">
+        <f t="shared" si="43"/>
+        <v>48.576109942568124</v>
+      </c>
+      <c r="W144" s="4">
         <f t="shared" si="44"/>
-        <v>1203.7512319311559</v>
-      </c>
-      <c r="T144" s="8">
-        <f t="shared" si="45"/>
-        <v>3.3718521902833496</v>
-      </c>
-      <c r="U144" s="8">
-        <f t="shared" si="46"/>
-        <v>3.5825929521760593</v>
-      </c>
-      <c r="V144" s="8">
-        <f t="shared" si="42"/>
-        <v>48.576109942568124</v>
-      </c>
-      <c r="W144" s="4">
-        <f t="shared" si="43"/>
         <v>60.690000000000005</v>
       </c>
-      <c r="X144" s="8">
+      <c r="X144" s="12">
+        <f t="shared" si="50"/>
+        <v>44.682355598616383</v>
+      </c>
+      <c r="Y144" s="8">
+        <f t="shared" si="51"/>
+        <v>1357.6996974723404</v>
+      </c>
+      <c r="Z144" s="9">
+        <f t="shared" si="48"/>
+        <v>9.9125321058374252E-2</v>
+      </c>
+      <c r="AA144" s="8">
         <f t="shared" si="49"/>
-        <v>1313.017341873724</v>
-      </c>
-      <c r="Y144" s="9">
-        <f t="shared" si="47"/>
-        <v>9.5863073263369847E-2</v>
-      </c>
-      <c r="Z144" s="8">
-        <f t="shared" si="48"/>
-        <v>12383.782658126274</v>
-      </c>
-    </row>
-    <row r="145" spans="1:26" x14ac:dyDescent="0.25">
+        <v>12339.100302527659</v>
+      </c>
+    </row>
+    <row r="145" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>2</v>
       </c>
@@ -13231,39 +13809,43 @@
         <v>65</v>
       </c>
       <c r="S145" s="8">
+        <f t="shared" si="45"/>
+        <v>653.04084350246194</v>
+      </c>
+      <c r="T145" s="8">
+        <f t="shared" si="46"/>
+        <v>5.4877381806929577</v>
+      </c>
+      <c r="U145" s="8">
+        <f t="shared" si="47"/>
+        <v>5.8307218169862676</v>
+      </c>
+      <c r="V145" s="8">
+        <f t="shared" si="43"/>
+        <v>16.192036647522709</v>
+      </c>
+      <c r="W145" s="4">
         <f t="shared" si="44"/>
-        <v>653.04084350246194</v>
-      </c>
-      <c r="T145" s="8">
-        <f t="shared" si="45"/>
-        <v>5.4877381806929577</v>
-      </c>
-      <c r="U145" s="8">
-        <f t="shared" si="46"/>
-        <v>5.8307218169862676</v>
-      </c>
-      <c r="V145" s="8">
-        <f t="shared" si="42"/>
-        <v>16.192036647522709</v>
-      </c>
-      <c r="W145" s="4">
-        <f t="shared" si="43"/>
         <v>20.23</v>
       </c>
-      <c r="X145" s="8">
+      <c r="X145" s="12">
+        <f t="shared" si="50"/>
+        <v>14.894118532872126</v>
+      </c>
+      <c r="Y145" s="8">
+        <f t="shared" si="51"/>
+        <v>704.35699868285678</v>
+      </c>
+      <c r="Z145" s="9">
+        <f t="shared" si="48"/>
+        <v>0.15047405182802884</v>
+      </c>
+      <c r="AA145" s="8">
         <f t="shared" si="49"/>
-        <v>689.4628801499847</v>
-      </c>
-      <c r="Y145" s="9">
-        <f t="shared" si="47"/>
-        <v>0.14729217336548897</v>
-      </c>
-      <c r="Z145" s="8">
-        <f t="shared" si="48"/>
-        <v>3991.4571198500153</v>
-      </c>
-    </row>
-    <row r="146" spans="1:26" x14ac:dyDescent="0.25">
+        <v>3976.5630013171431</v>
+      </c>
+    </row>
+    <row r="146" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>2</v>
       </c>
@@ -13317,39 +13899,43 @@
         <v>65</v>
       </c>
       <c r="S146" s="8">
+        <f t="shared" si="45"/>
+        <v>535.01563262684647</v>
+      </c>
+      <c r="T146" s="8">
+        <f t="shared" si="46"/>
+        <v>5.9945729145865148</v>
+      </c>
+      <c r="U146" s="8">
+        <f t="shared" si="47"/>
+        <v>6.3692337217481718</v>
+      </c>
+      <c r="V146" s="8">
+        <f t="shared" si="43"/>
+        <v>12.144027485642031</v>
+      </c>
+      <c r="W146" s="4">
         <f t="shared" si="44"/>
-        <v>535.01563262684647</v>
-      </c>
-      <c r="T146" s="8">
-        <f t="shared" si="45"/>
-        <v>5.9945729145865148</v>
-      </c>
-      <c r="U146" s="8">
-        <f t="shared" si="46"/>
-        <v>6.3692337217481718</v>
-      </c>
-      <c r="V146" s="8">
-        <f t="shared" si="42"/>
-        <v>12.144027485642031</v>
-      </c>
-      <c r="W146" s="4">
-        <f t="shared" si="43"/>
         <v>15.172500000000001</v>
       </c>
-      <c r="X146" s="8">
+      <c r="X146" s="12">
+        <f t="shared" si="50"/>
+        <v>11.170588899654096</v>
+      </c>
+      <c r="Y146" s="8">
+        <f t="shared" si="51"/>
+        <v>573.50274901214266</v>
+      </c>
+      <c r="Z146" s="9">
+        <f t="shared" si="48"/>
+        <v>0.16322043590096469</v>
+      </c>
+      <c r="AA146" s="8">
         <f t="shared" si="49"/>
-        <v>562.33216011248851</v>
-      </c>
-      <c r="Y146" s="9">
-        <f t="shared" si="47"/>
-        <v>0.16004125604068922</v>
-      </c>
-      <c r="Z146" s="8">
-        <f t="shared" si="48"/>
-        <v>2951.3378398875116</v>
-      </c>
-    </row>
-    <row r="147" spans="1:26" x14ac:dyDescent="0.25">
+        <v>2940.1672509878572</v>
+      </c>
+    </row>
+    <row r="147" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>2</v>
       </c>
@@ -13403,39 +13989,43 @@
         <v>65</v>
       </c>
       <c r="S147" s="8">
+        <f t="shared" si="45"/>
+        <v>534.94563262684653</v>
+      </c>
+      <c r="T147" s="8">
+        <f t="shared" si="46"/>
+        <v>5.9937886008610253</v>
+      </c>
+      <c r="U147" s="8">
+        <f t="shared" si="47"/>
+        <v>6.3684003884148392</v>
+      </c>
+      <c r="V147" s="8">
+        <f t="shared" si="43"/>
+        <v>12.144027485642031</v>
+      </c>
+      <c r="W147" s="4">
         <f t="shared" si="44"/>
-        <v>534.94563262684653</v>
-      </c>
-      <c r="T147" s="8">
-        <f t="shared" si="45"/>
-        <v>5.9937886008610253</v>
-      </c>
-      <c r="U147" s="8">
-        <f t="shared" si="46"/>
-        <v>6.3684003884148392</v>
-      </c>
-      <c r="V147" s="8">
-        <f t="shared" si="42"/>
-        <v>12.144027485642031</v>
-      </c>
-      <c r="W147" s="4">
-        <f t="shared" si="43"/>
         <v>15.172500000000001</v>
       </c>
-      <c r="X147" s="8">
+      <c r="X147" s="12">
+        <f t="shared" si="50"/>
+        <v>11.170588899654096</v>
+      </c>
+      <c r="Y147" s="8">
+        <f t="shared" si="51"/>
+        <v>573.43274901214272</v>
+      </c>
+      <c r="Z147" s="9">
+        <f t="shared" si="48"/>
+        <v>0.1637560502640516</v>
+      </c>
+      <c r="AA147" s="8">
         <f t="shared" si="49"/>
-        <v>562.26216011248857</v>
-      </c>
-      <c r="Y147" s="9">
-        <f t="shared" si="47"/>
-        <v>0.16056604843649278</v>
-      </c>
-      <c r="Z147" s="8">
-        <f t="shared" si="48"/>
-        <v>2939.4878398875117</v>
-      </c>
-    </row>
-    <row r="148" spans="1:26" x14ac:dyDescent="0.25">
+        <v>2928.3172509878573</v>
+      </c>
+    </row>
+    <row r="148" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>2</v>
       </c>
@@ -13489,39 +14079,43 @@
         <v>65</v>
       </c>
       <c r="S148" s="8">
+        <f t="shared" si="45"/>
+        <v>490.53042175123102</v>
+      </c>
+      <c r="T148" s="8">
+        <f t="shared" si="46"/>
+        <v>8.2442087689282531</v>
+      </c>
+      <c r="U148" s="8">
+        <f t="shared" si="47"/>
+        <v>8.7594718169862684</v>
+      </c>
+      <c r="V148" s="8">
+        <f t="shared" si="43"/>
+        <v>8.0960183237613546</v>
+      </c>
+      <c r="W148" s="4">
         <f t="shared" si="44"/>
-        <v>490.53042175123102</v>
-      </c>
-      <c r="T148" s="8">
-        <f t="shared" si="45"/>
-        <v>8.2442087689282531</v>
-      </c>
-      <c r="U148" s="8">
-        <f t="shared" si="46"/>
-        <v>8.7594718169862684</v>
-      </c>
-      <c r="V148" s="8">
-        <f t="shared" si="42"/>
-        <v>8.0960183237613546</v>
-      </c>
-      <c r="W148" s="4">
-        <f t="shared" si="43"/>
         <v>10.115</v>
       </c>
-      <c r="X148" s="8">
+      <c r="X148" s="12">
+        <f t="shared" si="50"/>
+        <v>7.4470592664360629</v>
+      </c>
+      <c r="Y148" s="8">
+        <f t="shared" si="51"/>
+        <v>516.1884993414285</v>
+      </c>
+      <c r="Z148" s="9">
+        <f t="shared" si="48"/>
+        <v>0.2202695607062389</v>
+      </c>
+      <c r="AA148" s="8">
         <f t="shared" si="49"/>
-        <v>508.7414400749924</v>
-      </c>
-      <c r="Y148" s="9">
-        <f t="shared" si="47"/>
-        <v>0.21709172843127725</v>
-      </c>
-      <c r="Z148" s="8">
-        <f t="shared" si="48"/>
-        <v>1834.6985599250077</v>
-      </c>
-    </row>
-    <row r="149" spans="1:26" x14ac:dyDescent="0.25">
+        <v>1827.2515006585716</v>
+      </c>
+    </row>
+    <row r="149" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>2</v>
       </c>
@@ -13575,39 +14169,43 @@
         <v>65</v>
       </c>
       <c r="S149" s="8">
+        <f t="shared" si="45"/>
+        <v>534.94563262684653</v>
+      </c>
+      <c r="T149" s="8">
+        <f t="shared" si="46"/>
+        <v>5.9937886008610253</v>
+      </c>
+      <c r="U149" s="8">
+        <f t="shared" si="47"/>
+        <v>6.3684003884148392</v>
+      </c>
+      <c r="V149" s="8">
+        <f t="shared" si="43"/>
+        <v>12.144027485642031</v>
+      </c>
+      <c r="W149" s="4">
         <f t="shared" si="44"/>
-        <v>534.94563262684653</v>
-      </c>
-      <c r="T149" s="8">
-        <f t="shared" si="45"/>
-        <v>5.9937886008610253</v>
-      </c>
-      <c r="U149" s="8">
-        <f t="shared" si="46"/>
-        <v>6.3684003884148392</v>
-      </c>
-      <c r="V149" s="8">
-        <f t="shared" si="42"/>
-        <v>12.144027485642031</v>
-      </c>
-      <c r="W149" s="4">
-        <f t="shared" si="43"/>
         <v>15.172500000000001</v>
       </c>
-      <c r="X149" s="8">
+      <c r="X149" s="12">
+        <f t="shared" si="50"/>
+        <v>11.170588899654096</v>
+      </c>
+      <c r="Y149" s="8">
+        <f t="shared" si="51"/>
+        <v>573.43274901214272</v>
+      </c>
+      <c r="Z149" s="9">
+        <f t="shared" si="48"/>
+        <v>0.1637560502640516</v>
+      </c>
+      <c r="AA149" s="8">
         <f t="shared" si="49"/>
-        <v>562.26216011248857</v>
-      </c>
-      <c r="Y149" s="9">
-        <f t="shared" si="47"/>
-        <v>0.16056604843649278</v>
-      </c>
-      <c r="Z149" s="8">
-        <f t="shared" si="48"/>
-        <v>2939.4878398875117</v>
-      </c>
-    </row>
-    <row r="150" spans="1:26" x14ac:dyDescent="0.25">
+        <v>2928.3172509878573</v>
+      </c>
+    </row>
+    <row r="150" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>2</v>
       </c>
@@ -13661,39 +14259,43 @@
         <v>65</v>
       </c>
       <c r="S150" s="8">
+        <f t="shared" si="45"/>
+        <v>490.51042175123098</v>
+      </c>
+      <c r="T150" s="8">
+        <f t="shared" si="46"/>
+        <v>8.2438726344744708</v>
+      </c>
+      <c r="U150" s="8">
+        <f t="shared" si="47"/>
+        <v>8.7591146741291244</v>
+      </c>
+      <c r="V150" s="8">
+        <f t="shared" si="43"/>
+        <v>8.0960183237613546</v>
+      </c>
+      <c r="W150" s="4">
         <f t="shared" si="44"/>
-        <v>490.51042175123098</v>
-      </c>
-      <c r="T150" s="8">
-        <f t="shared" si="45"/>
-        <v>8.2438726344744708</v>
-      </c>
-      <c r="U150" s="8">
-        <f t="shared" si="46"/>
-        <v>8.7591146741291244</v>
-      </c>
-      <c r="V150" s="8">
-        <f t="shared" si="42"/>
-        <v>8.0960183237613546</v>
-      </c>
-      <c r="W150" s="4">
-        <f t="shared" si="43"/>
         <v>10.115</v>
       </c>
-      <c r="X150" s="8">
+      <c r="X150" s="12">
+        <f t="shared" si="50"/>
+        <v>7.4470592664360629</v>
+      </c>
+      <c r="Y150" s="8">
+        <f t="shared" si="51"/>
+        <v>516.1684993414284</v>
+      </c>
+      <c r="Z150" s="9">
+        <f t="shared" si="48"/>
+        <v>0.22054147447144082</v>
+      </c>
+      <c r="AA150" s="8">
         <f t="shared" si="49"/>
-        <v>508.72144007499236</v>
-      </c>
-      <c r="Y150" s="9">
-        <f t="shared" si="47"/>
-        <v>0.21735959600890095</v>
-      </c>
-      <c r="Z150" s="8">
-        <f t="shared" si="48"/>
-        <v>1831.7385599250076</v>
-      </c>
-    </row>
-    <row r="151" spans="1:26" x14ac:dyDescent="0.25">
+        <v>1824.2915006585717</v>
+      </c>
+    </row>
+    <row r="151" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>2</v>
       </c>
@@ -13745,39 +14347,43 @@
         <v>65</v>
       </c>
       <c r="S151" s="8">
+        <f t="shared" si="45"/>
+        <v>490.57042175123098</v>
+      </c>
+      <c r="T151" s="8">
+        <f t="shared" si="46"/>
+        <v>8.2448810378358139</v>
+      </c>
+      <c r="U151" s="8">
+        <f t="shared" si="47"/>
+        <v>8.760186102700553</v>
+      </c>
+      <c r="V151" s="8">
+        <f t="shared" si="43"/>
+        <v>8.0960183237613546</v>
+      </c>
+      <c r="W151" s="4">
         <f t="shared" si="44"/>
-        <v>490.57042175123098</v>
-      </c>
-      <c r="T151" s="8">
-        <f t="shared" si="45"/>
-        <v>8.2448810378358139</v>
-      </c>
-      <c r="U151" s="8">
-        <f t="shared" si="46"/>
-        <v>8.760186102700553</v>
-      </c>
-      <c r="V151" s="8">
-        <f t="shared" si="42"/>
-        <v>8.0960183237613546</v>
-      </c>
-      <c r="W151" s="4">
-        <f t="shared" si="43"/>
         <v>10.115</v>
       </c>
-      <c r="X151" s="8">
+      <c r="X151" s="12">
+        <f t="shared" si="50"/>
+        <v>7.4470592664360629</v>
+      </c>
+      <c r="Y151" s="8">
+        <f t="shared" si="51"/>
+        <v>516.22849934142846</v>
+      </c>
+      <c r="Z151" s="9">
+        <f t="shared" si="48"/>
+        <v>0.21972780256296434</v>
+      </c>
+      <c r="AA151" s="8">
         <f t="shared" si="49"/>
-        <v>508.78144007499236</v>
-      </c>
-      <c r="Y151" s="9">
-        <f t="shared" si="47"/>
-        <v>0.21655803186983585</v>
-      </c>
-      <c r="Z151" s="8">
-        <f t="shared" si="48"/>
-        <v>1840.6185599250077</v>
-      </c>
-    </row>
-    <row r="152" spans="1:26" x14ac:dyDescent="0.25">
+        <v>1833.1715006585716</v>
+      </c>
+    </row>
+    <row r="152" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>2</v>
       </c>
@@ -13831,39 +14437,43 @@
         <v>65</v>
       </c>
       <c r="S152" s="8">
+        <f t="shared" si="45"/>
+        <v>534.94563262684653</v>
+      </c>
+      <c r="T152" s="8">
+        <f t="shared" si="46"/>
+        <v>5.9937886008610253</v>
+      </c>
+      <c r="U152" s="8">
+        <f t="shared" si="47"/>
+        <v>6.3684003884148392</v>
+      </c>
+      <c r="V152" s="8">
+        <f t="shared" si="43"/>
+        <v>12.144027485642031</v>
+      </c>
+      <c r="W152" s="4">
         <f t="shared" si="44"/>
-        <v>534.94563262684653</v>
-      </c>
-      <c r="T152" s="8">
-        <f t="shared" si="45"/>
-        <v>5.9937886008610253</v>
-      </c>
-      <c r="U152" s="8">
-        <f t="shared" si="46"/>
-        <v>6.3684003884148392</v>
-      </c>
-      <c r="V152" s="8">
-        <f t="shared" si="42"/>
-        <v>12.144027485642031</v>
-      </c>
-      <c r="W152" s="4">
-        <f t="shared" si="43"/>
         <v>15.172500000000001</v>
       </c>
-      <c r="X152" s="8">
+      <c r="X152" s="12">
+        <f t="shared" si="50"/>
+        <v>11.170588899654096</v>
+      </c>
+      <c r="Y152" s="8">
+        <f t="shared" si="51"/>
+        <v>573.43274901214272</v>
+      </c>
+      <c r="Z152" s="9">
+        <f t="shared" si="48"/>
+        <v>0.1637560502640516</v>
+      </c>
+      <c r="AA152" s="8">
         <f t="shared" si="49"/>
-        <v>562.26216011248857</v>
-      </c>
-      <c r="Y152" s="9">
-        <f t="shared" si="47"/>
-        <v>0.16056604843649278</v>
-      </c>
-      <c r="Z152" s="8">
-        <f t="shared" si="48"/>
-        <v>2939.4878398875117</v>
-      </c>
-    </row>
-    <row r="153" spans="1:26" x14ac:dyDescent="0.25">
+        <v>2928.3172509878573</v>
+      </c>
+    </row>
+    <row r="153" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>2</v>
       </c>
@@ -13915,39 +14525,43 @@
         <v>65</v>
       </c>
       <c r="S153" s="8">
+        <f t="shared" si="45"/>
+        <v>534.96563262684651</v>
+      </c>
+      <c r="T153" s="8">
+        <f t="shared" si="46"/>
+        <v>5.9940126904968798</v>
+      </c>
+      <c r="U153" s="8">
+        <f t="shared" si="47"/>
+        <v>6.3686384836529344</v>
+      </c>
+      <c r="V153" s="8">
+        <f t="shared" si="43"/>
+        <v>12.144027485642031</v>
+      </c>
+      <c r="W153" s="4">
         <f t="shared" si="44"/>
-        <v>534.96563262684651</v>
-      </c>
-      <c r="T153" s="8">
-        <f t="shared" si="45"/>
-        <v>5.9940126904968798</v>
-      </c>
-      <c r="U153" s="8">
-        <f t="shared" si="46"/>
-        <v>6.3686384836529344</v>
-      </c>
-      <c r="V153" s="8">
-        <f t="shared" si="42"/>
-        <v>12.144027485642031</v>
-      </c>
-      <c r="W153" s="4">
-        <f t="shared" si="43"/>
         <v>15.172500000000001</v>
       </c>
-      <c r="X153" s="8">
+      <c r="X153" s="12">
+        <f t="shared" si="50"/>
+        <v>11.170588899654096</v>
+      </c>
+      <c r="Y153" s="8">
+        <f t="shared" si="51"/>
+        <v>573.4527490121427</v>
+      </c>
+      <c r="Z153" s="9">
+        <f t="shared" si="48"/>
+        <v>0.16362158470993443</v>
+      </c>
+      <c r="AA153" s="8">
         <f t="shared" si="49"/>
-        <v>562.28216011248855</v>
-      </c>
-      <c r="Y153" s="9">
-        <f t="shared" si="47"/>
-        <v>0.16043431346386719</v>
-      </c>
-      <c r="Z153" s="8">
-        <f t="shared" si="48"/>
-        <v>2942.4678398875112</v>
-      </c>
-    </row>
-    <row r="154" spans="1:26" x14ac:dyDescent="0.25">
+        <v>2931.2972509878573</v>
+      </c>
+    </row>
+    <row r="154" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>2</v>
       </c>
@@ -14001,39 +14615,43 @@
         <v>65</v>
       </c>
       <c r="S154" s="8">
+        <f t="shared" si="45"/>
+        <v>535.07563262684653</v>
+      </c>
+      <c r="T154" s="8">
+        <f t="shared" si="46"/>
+        <v>5.9952451834940783</v>
+      </c>
+      <c r="U154" s="8">
+        <f t="shared" si="47"/>
+        <v>6.369948007462459</v>
+      </c>
+      <c r="V154" s="8">
+        <f t="shared" si="43"/>
+        <v>12.144027485642031</v>
+      </c>
+      <c r="W154" s="4">
         <f t="shared" si="44"/>
-        <v>535.07563262684653</v>
-      </c>
-      <c r="T154" s="8">
-        <f t="shared" si="45"/>
-        <v>5.9952451834940783</v>
-      </c>
-      <c r="U154" s="8">
-        <f t="shared" si="46"/>
-        <v>6.369948007462459</v>
-      </c>
-      <c r="V154" s="8">
-        <f t="shared" si="42"/>
-        <v>12.144027485642031</v>
-      </c>
-      <c r="W154" s="4">
-        <f t="shared" si="43"/>
         <v>15.172500000000001</v>
       </c>
-      <c r="X154" s="8">
+      <c r="X154" s="12">
+        <f t="shared" si="50"/>
+        <v>11.170588899654096</v>
+      </c>
+      <c r="Y154" s="8">
+        <f t="shared" si="51"/>
+        <v>573.56274901214272</v>
+      </c>
+      <c r="Z154" s="9">
+        <f t="shared" si="48"/>
+        <v>0.16282323306075402</v>
+      </c>
+      <c r="AA154" s="8">
         <f t="shared" si="49"/>
-        <v>562.39216011248857</v>
-      </c>
-      <c r="Y154" s="9">
-        <f t="shared" si="47"/>
-        <v>0.1596521216122388</v>
-      </c>
-      <c r="Z154" s="8">
-        <f t="shared" si="48"/>
-        <v>2960.2178398875117</v>
-      </c>
-    </row>
-    <row r="155" spans="1:26" x14ac:dyDescent="0.25">
+        <v>2949.0472509878573</v>
+      </c>
+    </row>
+    <row r="155" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>2</v>
       </c>
@@ -14087,39 +14705,43 @@
         <v>65</v>
       </c>
       <c r="S155" s="8">
+        <f t="shared" si="45"/>
+        <v>535.01563262684647</v>
+      </c>
+      <c r="T155" s="8">
+        <f t="shared" si="46"/>
+        <v>5.9945729145865148</v>
+      </c>
+      <c r="U155" s="8">
+        <f t="shared" si="47"/>
+        <v>6.3692337217481718</v>
+      </c>
+      <c r="V155" s="8">
+        <f t="shared" si="43"/>
+        <v>12.144027485642031</v>
+      </c>
+      <c r="W155" s="4">
         <f t="shared" si="44"/>
-        <v>535.01563262684647</v>
-      </c>
-      <c r="T155" s="8">
-        <f t="shared" si="45"/>
-        <v>5.9945729145865148</v>
-      </c>
-      <c r="U155" s="8">
-        <f t="shared" si="46"/>
-        <v>6.3692337217481718</v>
-      </c>
-      <c r="V155" s="8">
-        <f t="shared" si="42"/>
-        <v>12.144027485642031</v>
-      </c>
-      <c r="W155" s="4">
-        <f t="shared" si="43"/>
         <v>15.172500000000001</v>
       </c>
-      <c r="X155" s="8">
+      <c r="X155" s="12">
+        <f t="shared" si="50"/>
+        <v>11.170588899654096</v>
+      </c>
+      <c r="Y155" s="8">
+        <f t="shared" si="51"/>
+        <v>573.50274901214266</v>
+      </c>
+      <c r="Z155" s="9">
+        <f t="shared" si="48"/>
+        <v>0.16322043590096469</v>
+      </c>
+      <c r="AA155" s="8">
         <f t="shared" si="49"/>
-        <v>562.33216011248851</v>
-      </c>
-      <c r="Y155" s="9">
-        <f t="shared" si="47"/>
-        <v>0.16004125604068922</v>
-      </c>
-      <c r="Z155" s="8">
-        <f t="shared" si="48"/>
-        <v>2951.3378398875116</v>
-      </c>
-    </row>
-    <row r="156" spans="1:26" x14ac:dyDescent="0.25">
+        <v>2940.1672509878572</v>
+      </c>
+    </row>
+    <row r="156" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>2</v>
       </c>
@@ -14171,39 +14793,43 @@
         <v>65</v>
       </c>
       <c r="S156" s="8">
+        <f t="shared" si="45"/>
+        <v>3050.5504753988939</v>
+      </c>
+      <c r="T156" s="8">
+        <f t="shared" si="46"/>
+        <v>1.2798080531124745</v>
+      </c>
+      <c r="U156" s="8">
+        <f t="shared" si="47"/>
+        <v>1.3785929480291457</v>
+      </c>
+      <c r="V156" s="8">
+        <f t="shared" si="43"/>
+        <v>324.33057607592542</v>
+      </c>
+      <c r="W156" s="4">
         <f t="shared" si="44"/>
-        <v>3050.5504753988939</v>
-      </c>
-      <c r="T156" s="8">
-        <f t="shared" si="45"/>
-        <v>1.2798080531124745</v>
-      </c>
-      <c r="U156" s="8">
-        <f t="shared" si="46"/>
-        <v>1.3785929480291457</v>
-      </c>
-      <c r="V156" s="8">
-        <f t="shared" si="42"/>
-        <v>324.33057607592542</v>
-      </c>
-      <c r="W156" s="4">
-        <f t="shared" si="43"/>
         <v>405.21199999999999</v>
       </c>
-      <c r="X156" s="8">
+      <c r="X156" s="12">
+        <f t="shared" si="50"/>
+        <v>298.33294903322684</v>
+      </c>
+      <c r="Y156" s="8">
+        <f t="shared" si="51"/>
+        <v>4078.4260005080459</v>
+      </c>
+      <c r="Z156" s="9">
+        <f t="shared" si="48"/>
+        <v>5.1081978142854853E-2</v>
+      </c>
+      <c r="AA156" s="8">
         <f t="shared" si="49"/>
-        <v>3780.0930514748193</v>
-      </c>
-      <c r="Y156" s="9">
-        <f t="shared" si="47"/>
-        <v>4.7345380450531799E-2</v>
-      </c>
-      <c r="Z156" s="8">
-        <f t="shared" si="48"/>
-        <v>76060.706948525185</v>
-      </c>
-    </row>
-    <row r="157" spans="1:26" x14ac:dyDescent="0.25">
+        <v>75762.37399949196</v>
+      </c>
+    </row>
+    <row r="157" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>2</v>
       </c>
@@ -14257,39 +14883,43 @@
         <v>65</v>
       </c>
       <c r="S157" s="8">
+        <f t="shared" si="45"/>
+        <v>703.62692785270815</v>
+      </c>
+      <c r="T157" s="8">
+        <f t="shared" si="46"/>
+        <v>5.3753012059030416</v>
+      </c>
+      <c r="U157" s="8">
+        <f t="shared" si="47"/>
+        <v>5.7112575312719818</v>
+      </c>
+      <c r="V157" s="8">
+        <f t="shared" si="43"/>
+        <v>17.811240312274979</v>
+      </c>
+      <c r="W157" s="4">
         <f t="shared" si="44"/>
-        <v>703.62692785270815</v>
-      </c>
-      <c r="T157" s="8">
-        <f t="shared" si="45"/>
-        <v>5.3753012059030416</v>
-      </c>
-      <c r="U157" s="8">
-        <f t="shared" si="46"/>
-        <v>5.7112575312719818</v>
-      </c>
-      <c r="V157" s="8">
-        <f t="shared" si="42"/>
-        <v>17.811240312274979</v>
-      </c>
-      <c r="W157" s="4">
-        <f t="shared" si="43"/>
         <v>22.253000000000004</v>
       </c>
-      <c r="X157" s="8">
+      <c r="X157" s="12">
+        <f t="shared" si="50"/>
+        <v>16.38353038615934</v>
+      </c>
+      <c r="Y157" s="8">
+        <f t="shared" si="51"/>
+        <v>760.07469855114255</v>
+      </c>
+      <c r="Z157" s="9">
+        <f t="shared" si="48"/>
+        <v>0.14782096333839168</v>
+      </c>
+      <c r="AA157" s="8">
         <f t="shared" si="49"/>
-        <v>743.6911681649832</v>
-      </c>
-      <c r="Y157" s="9">
-        <f t="shared" si="47"/>
-        <v>0.14463465908542497</v>
-      </c>
-      <c r="Z157" s="8">
-        <f t="shared" si="48"/>
-        <v>4398.1688318350161</v>
-      </c>
-    </row>
-    <row r="158" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4381.7853014488574</v>
+      </c>
+    </row>
+    <row r="158" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>2</v>
       </c>
@@ -14343,39 +14973,43 @@
         <v>65</v>
       </c>
       <c r="S158" s="8">
+        <f t="shared" si="45"/>
+        <v>508.29650610147718</v>
+      </c>
+      <c r="T158" s="8">
+        <f t="shared" si="46"/>
+        <v>7.1189986848946374</v>
+      </c>
+      <c r="U158" s="8">
+        <f t="shared" si="47"/>
+        <v>7.5639361027005529</v>
+      </c>
+      <c r="V158" s="8">
+        <f t="shared" si="43"/>
+        <v>9.7152219885136262</v>
+      </c>
+      <c r="W158" s="4">
         <f t="shared" si="44"/>
-        <v>508.29650610147718</v>
-      </c>
-      <c r="T158" s="8">
-        <f t="shared" si="45"/>
-        <v>7.1189986848946374</v>
-      </c>
-      <c r="U158" s="8">
-        <f t="shared" si="46"/>
-        <v>7.5639361027005529</v>
-      </c>
-      <c r="V158" s="8">
-        <f t="shared" si="42"/>
-        <v>9.7152219885136262</v>
-      </c>
-      <c r="W158" s="4">
-        <f t="shared" si="43"/>
         <v>12.138000000000002</v>
       </c>
-      <c r="X158" s="8">
+      <c r="X158" s="12">
+        <f t="shared" si="50"/>
+        <v>8.9364711197232776</v>
+      </c>
+      <c r="Y158" s="8">
+        <f t="shared" si="51"/>
+        <v>539.0861992097141</v>
+      </c>
+      <c r="Z158" s="9">
+        <f t="shared" si="48"/>
+        <v>0.19202603129264292</v>
+      </c>
+      <c r="AA158" s="8">
         <f t="shared" si="49"/>
-        <v>530.14972808999084</v>
-      </c>
-      <c r="Y158" s="9">
-        <f t="shared" si="47"/>
-        <v>0.18884280181023838</v>
-      </c>
-      <c r="Z158" s="8">
-        <f t="shared" si="48"/>
-        <v>2277.2102719100094</v>
-      </c>
-    </row>
-    <row r="159" spans="1:26" x14ac:dyDescent="0.25">
+        <v>2268.2738007902863</v>
+      </c>
+    </row>
+    <row r="159" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>2</v>
       </c>
@@ -14429,39 +15063,43 @@
         <v>65</v>
       </c>
       <c r="S159" s="8">
+        <f t="shared" si="45"/>
+        <v>481.63737957610789</v>
+      </c>
+      <c r="T159" s="8">
+        <f t="shared" si="46"/>
+        <v>8.9941620835874492</v>
+      </c>
+      <c r="U159" s="8">
+        <f t="shared" si="47"/>
+        <v>9.5562972138116642</v>
+      </c>
+      <c r="V159" s="8">
+        <f t="shared" si="43"/>
+        <v>7.2864164913852179</v>
+      </c>
+      <c r="W159" s="4">
         <f t="shared" si="44"/>
-        <v>481.63737957610789</v>
-      </c>
-      <c r="T159" s="8">
-        <f t="shared" si="45"/>
-        <v>8.9941620835874492</v>
-      </c>
-      <c r="U159" s="8">
-        <f t="shared" si="46"/>
-        <v>9.5562972138116642</v>
-      </c>
-      <c r="V159" s="8">
-        <f t="shared" si="42"/>
-        <v>7.2864164913852179</v>
-      </c>
-      <c r="W159" s="4">
-        <f t="shared" si="43"/>
         <v>9.1035000000000004</v>
       </c>
-      <c r="X159" s="8">
+      <c r="X159" s="12">
+        <f t="shared" si="50"/>
+        <v>6.7023533397924568</v>
+      </c>
+      <c r="Y159" s="8">
+        <f t="shared" si="51"/>
+        <v>504.72964940728559</v>
+      </c>
+      <c r="Z159" s="9">
+        <f t="shared" si="48"/>
+        <v>0.23920949834230762</v>
+      </c>
+      <c r="AA159" s="8">
         <f t="shared" si="49"/>
-        <v>498.02729606749313</v>
-      </c>
-      <c r="Y159" s="9">
-        <f t="shared" si="47"/>
-        <v>0.23603301251071956</v>
-      </c>
-      <c r="Z159" s="8">
-        <f t="shared" si="48"/>
-        <v>1611.9627039325067</v>
-      </c>
-    </row>
-    <row r="160" spans="1:26" x14ac:dyDescent="0.25">
+        <v>1605.2603505927141</v>
+      </c>
+    </row>
+    <row r="160" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>2</v>
       </c>
@@ -14515,39 +15153,43 @@
         <v>65</v>
       </c>
       <c r="S160" s="8">
+        <f t="shared" si="45"/>
+        <v>534.96563262684651</v>
+      </c>
+      <c r="T160" s="8">
+        <f t="shared" si="46"/>
+        <v>5.9940126904968798</v>
+      </c>
+      <c r="U160" s="8">
+        <f t="shared" si="47"/>
+        <v>6.3686384836529344</v>
+      </c>
+      <c r="V160" s="8">
+        <f t="shared" si="43"/>
+        <v>12.144027485642031</v>
+      </c>
+      <c r="W160" s="4">
         <f t="shared" si="44"/>
-        <v>534.96563262684651</v>
-      </c>
-      <c r="T160" s="8">
-        <f t="shared" si="45"/>
-        <v>5.9940126904968798</v>
-      </c>
-      <c r="U160" s="8">
-        <f t="shared" si="46"/>
-        <v>6.3686384836529344</v>
-      </c>
-      <c r="V160" s="8">
-        <f t="shared" si="42"/>
-        <v>12.144027485642031</v>
-      </c>
-      <c r="W160" s="4">
-        <f t="shared" si="43"/>
         <v>15.172500000000001</v>
       </c>
-      <c r="X160" s="8">
+      <c r="X160" s="12">
+        <f t="shared" si="50"/>
+        <v>11.170588899654096</v>
+      </c>
+      <c r="Y160" s="8">
+        <f t="shared" si="51"/>
+        <v>573.4527490121427</v>
+      </c>
+      <c r="Z160" s="9">
+        <f t="shared" si="48"/>
+        <v>0.16362251842856446</v>
+      </c>
+      <c r="AA160" s="8">
         <f t="shared" si="49"/>
-        <v>562.28216011248855</v>
-      </c>
-      <c r="Y160" s="9">
-        <f t="shared" si="47"/>
-        <v>0.16043522899409898</v>
-      </c>
-      <c r="Z160" s="8">
-        <f t="shared" si="48"/>
-        <v>2942.4478398875117</v>
-      </c>
-    </row>
-    <row r="161" spans="1:26" x14ac:dyDescent="0.25">
+        <v>2931.2772509878573</v>
+      </c>
+    </row>
+    <row r="161" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>2</v>
       </c>
@@ -14601,39 +15243,43 @@
         <v>65</v>
       </c>
       <c r="S161" s="8">
+        <f t="shared" si="45"/>
+        <v>535.03563262684645</v>
+      </c>
+      <c r="T161" s="8">
+        <f t="shared" si="46"/>
+        <v>5.9947970042223693</v>
+      </c>
+      <c r="U161" s="8">
+        <f t="shared" si="47"/>
+        <v>6.369471816986267</v>
+      </c>
+      <c r="V161" s="8">
+        <f t="shared" si="43"/>
+        <v>12.144027485642031</v>
+      </c>
+      <c r="W161" s="4">
         <f t="shared" si="44"/>
-        <v>535.03563262684645</v>
-      </c>
-      <c r="T161" s="8">
-        <f t="shared" si="45"/>
-        <v>5.9947970042223693</v>
-      </c>
-      <c r="U161" s="8">
-        <f t="shared" si="46"/>
-        <v>6.369471816986267</v>
-      </c>
-      <c r="V161" s="8">
-        <f t="shared" si="42"/>
-        <v>12.144027485642031</v>
-      </c>
-      <c r="W161" s="4">
-        <f t="shared" si="43"/>
         <v>15.172500000000001</v>
       </c>
-      <c r="X161" s="8">
+      <c r="X161" s="12">
+        <f t="shared" si="50"/>
+        <v>11.170588899654096</v>
+      </c>
+      <c r="Y161" s="8">
+        <f t="shared" si="51"/>
+        <v>573.52274901214264</v>
+      </c>
+      <c r="Z161" s="9">
+        <f t="shared" si="48"/>
+        <v>0.16308781056179678</v>
+      </c>
+      <c r="AA161" s="8">
         <f t="shared" si="49"/>
-        <v>562.35216011248849</v>
-      </c>
-      <c r="Y161" s="9">
-        <f t="shared" si="47"/>
-        <v>0.15991132473020872</v>
-      </c>
-      <c r="Z161" s="8">
-        <f t="shared" si="48"/>
-        <v>2954.2978398875116</v>
-      </c>
-    </row>
-    <row r="162" spans="1:26" x14ac:dyDescent="0.25">
+        <v>2943.1272509878572</v>
+      </c>
+    </row>
+    <row r="162" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>2</v>
       </c>
@@ -14687,39 +15333,43 @@
         <v>65</v>
       </c>
       <c r="S162" s="8">
+        <f t="shared" si="45"/>
+        <v>508.29650610147718</v>
+      </c>
+      <c r="T162" s="8">
+        <f t="shared" si="46"/>
+        <v>7.1189986848946374</v>
+      </c>
+      <c r="U162" s="8">
+        <f t="shared" si="47"/>
+        <v>7.5639361027005529</v>
+      </c>
+      <c r="V162" s="8">
+        <f t="shared" si="43"/>
+        <v>9.7152219885136262</v>
+      </c>
+      <c r="W162" s="4">
         <f t="shared" si="44"/>
-        <v>508.29650610147718</v>
-      </c>
-      <c r="T162" s="8">
-        <f t="shared" si="45"/>
-        <v>7.1189986848946374</v>
-      </c>
-      <c r="U162" s="8">
-        <f t="shared" si="46"/>
-        <v>7.5639361027005529</v>
-      </c>
-      <c r="V162" s="8">
-        <f t="shared" si="42"/>
-        <v>9.7152219885136262</v>
-      </c>
-      <c r="W162" s="4">
-        <f t="shared" si="43"/>
         <v>12.138000000000002</v>
       </c>
-      <c r="X162" s="8">
+      <c r="X162" s="12">
+        <f t="shared" si="50"/>
+        <v>8.9364711197232776</v>
+      </c>
+      <c r="Y162" s="8">
+        <f t="shared" si="51"/>
+        <v>539.0861992097141</v>
+      </c>
+      <c r="Z162" s="9">
+        <f t="shared" ref="Z162:Z163" si="52">Y162/J162</f>
+        <v>0.19202603129264292</v>
+      </c>
+      <c r="AA162" s="8">
         <f t="shared" si="49"/>
-        <v>530.14972808999084</v>
-      </c>
-      <c r="Y162" s="9">
-        <f t="shared" ref="Y162:Y163" si="50">X162/J162</f>
-        <v>0.18884280181023838</v>
-      </c>
-      <c r="Z162" s="8">
-        <f t="shared" si="48"/>
-        <v>2277.2102719100094</v>
-      </c>
-    </row>
-    <row r="163" spans="1:26" x14ac:dyDescent="0.25">
+        <v>2268.2738007902863</v>
+      </c>
+    </row>
+    <row r="163" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>2</v>
       </c>
@@ -14773,52 +15423,61 @@
         <v>65</v>
       </c>
       <c r="S163" s="8">
+        <f t="shared" si="45"/>
+        <v>603.18940257156169</v>
+      </c>
+      <c r="T163" s="8">
+        <f t="shared" si="46"/>
+        <v>3.7996182839153492</v>
+      </c>
+      <c r="U163" s="8">
+        <f t="shared" si="47"/>
+        <v>4.0212626838104111</v>
+      </c>
+      <c r="V163" s="8">
+        <f t="shared" si="43"/>
+        <v>21.600721157934704</v>
+      </c>
+      <c r="W163" s="4">
         <f t="shared" si="44"/>
-        <v>603.18940257156169</v>
-      </c>
-      <c r="T163" s="8">
-        <f t="shared" si="45"/>
-        <v>3.7996182839153492</v>
-      </c>
-      <c r="U163" s="8">
-        <f t="shared" si="46"/>
-        <v>4.0212626838104111</v>
-      </c>
-      <c r="V163" s="8">
-        <f t="shared" si="42"/>
-        <v>21.600721157934704</v>
-      </c>
-      <c r="W163" s="4">
-        <f t="shared" si="43"/>
         <v>26.987500000000001</v>
       </c>
-      <c r="X163" s="8">
+      <c r="X163" s="12">
+        <f t="shared" si="50"/>
+        <v>19.869254765491178</v>
+      </c>
+      <c r="Y163" s="8">
+        <f t="shared" si="51"/>
+        <v>671.6468784949875</v>
+      </c>
+      <c r="Z163" s="9">
+        <f t="shared" si="52"/>
+        <v>0.14839745437361632</v>
+      </c>
+      <c r="AA163" s="8">
         <f t="shared" si="49"/>
-        <v>651.77762372949633</v>
-      </c>
-      <c r="Y163" s="9">
-        <f t="shared" si="50"/>
-        <v>0.14400742901668059</v>
-      </c>
-      <c r="Z163" s="8">
-        <f t="shared" si="48"/>
-        <v>3874.2223762705034</v>
-      </c>
-    </row>
-    <row r="165" spans="1:26" x14ac:dyDescent="0.25">
+        <v>3854.3531215050125</v>
+      </c>
+    </row>
+    <row r="165" spans="1:27" x14ac:dyDescent="0.25">
       <c r="I165" s="3"/>
     </row>
-    <row r="168" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:27" x14ac:dyDescent="0.25">
       <c r="H168" s="3"/>
-    </row>
-    <row r="169" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="V168" s="3"/>
+    </row>
+    <row r="169" spans="1:27" x14ac:dyDescent="0.25">
       <c r="H169" s="3"/>
-    </row>
-    <row r="171" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="V169" s="10"/>
+    </row>
+    <row r="170" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="V170" s="9"/>
+    </row>
+    <row r="171" spans="1:27" x14ac:dyDescent="0.25">
       <c r="H171" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z163" xr:uid="{10D4F1C6-370D-4261-953A-B02E0B54CF5A}"/>
+  <autoFilter ref="A1:AA163" xr:uid="{10D4F1C6-370D-4261-953A-B02E0B54CF5A}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>